--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -617,10 +617,10 @@
         <v>4267</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>22662</v>
+        <v>27950</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>20827</v>
+        <v>26221</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>14390</v>
@@ -652,10 +652,10 @@
         <v>2528</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>21977</v>
+        <v>27579</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>20992</v>
+        <v>26311</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>13714</v>
@@ -677,23 +677,23 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>T-35</t>
+          <t>T-40A</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>240.66</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>6211</v>
+        <v>3658</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>21797</v>
+        <v>27300</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>18693</v>
+        <v>25219</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>16499</v>
+        <v>13732</v>
       </c>
       <c r="G7" s="8">
         <f>D7/1000</f>
@@ -722,10 +722,10 @@
         <v>2363</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>21706</v>
+        <v>27052</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>20537</v>
+        <v>25862</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>14034</v>
@@ -747,23 +747,23 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>T-40A</t>
+          <t>T-37A</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>85.18000000000001</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>3658</v>
+        <v>4182</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>21691</v>
+        <v>27017</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>19900</v>
+        <v>25425</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>13732</v>
+        <v>15781</v>
       </c>
       <c r="G9" s="8">
         <f>D9/1000</f>
@@ -782,23 +782,23 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>T-37A</t>
+          <t>T-39D</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>85.98999999999999</v>
+        <v>23.73</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>4182</v>
+        <v>2148</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>21354</v>
+        <v>26588</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>19425</v>
+        <v>25652</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>15781</v>
+        <v>14710</v>
       </c>
       <c r="G10" s="15">
         <f>D10/1000</f>
@@ -817,23 +817,23 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>T-39D</t>
+          <t>T-39A</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>23.73</v>
+        <v>34.07</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2148</v>
+        <v>2376</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>21138</v>
+        <v>26587</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>20367</v>
+        <v>25024</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>14710</v>
+        <v>15101</v>
       </c>
       <c r="G11" s="8">
         <f>D11/1000</f>
@@ -852,23 +852,23 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>T-39A</t>
+          <t>T-41A</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>34.07</v>
+        <v>150.53</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>2376</v>
+        <v>4897</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>20959</v>
+        <v>26474</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>19828</v>
+        <v>23740</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>15101</v>
+        <v>12769</v>
       </c>
       <c r="G12" s="15">
         <f>D12/1000</f>
@@ -887,23 +887,23 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>T-41A</t>
+          <t>T-37</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>150.53</v>
+        <v>182.45</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4897</v>
+        <v>5565</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>20883</v>
+        <v>26297</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>18506</v>
+        <v>23151</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>12769</v>
+        <v>15705</v>
       </c>
       <c r="G13" s="8">
         <f>D13/1000</f>
@@ -922,23 +922,23 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>T-37</t>
+          <t>T-39C</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>182.45</v>
+        <v>20.03</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>5565</v>
+        <v>1858</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>20833</v>
+        <v>26246</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>18407</v>
+        <v>25125</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>15705</v>
+        <v>14553</v>
       </c>
       <c r="G14" s="15">
         <f>D14/1000</f>
@@ -957,23 +957,23 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>T-39C</t>
+          <t>T-37B</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>20.03</v>
+        <v>108.01</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1858</v>
+        <v>4183</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>20697</v>
+        <v>26018</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>19930</v>
+        <v>24170</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>14553</v>
+        <v>15031</v>
       </c>
       <c r="G15" s="8">
         <f>D15/1000</f>
@@ -992,23 +992,23 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>T-39B</t>
+          <t>T-38C</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>27.21</v>
+        <v>27.75</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>2143</v>
+        <v>2368</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>20395</v>
+        <v>25793</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>19344</v>
+        <v>24522</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>14837</v>
+        <v>14263</v>
       </c>
       <c r="G16" s="15">
         <f>D16/1000</f>
@@ -1027,23 +1027,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>T-37B</t>
+          <t>T-39B</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>108.01</v>
+        <v>27.21</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>4183</v>
+        <v>2143</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>20380</v>
+        <v>25723</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>18384</v>
+        <v>24540</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>15031</v>
+        <v>14837</v>
       </c>
       <c r="G17" s="8">
         <f>D17/1000</f>
@@ -1072,10 +1072,10 @@
         <v>2973</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>20245</v>
+        <v>25479</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>18649</v>
+        <v>23883</v>
       </c>
       <c r="F18" s="14" t="n">
         <v>12971</v>
@@ -1097,23 +1097,23 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>T-38C</t>
+          <t>T-35</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>27.75</v>
+        <v>240.66</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>2368</v>
+        <v>6211</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>20206</v>
+        <v>25051</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>19209</v>
+        <v>22104</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>14263</v>
+        <v>16499</v>
       </c>
       <c r="G19" s="8">
         <f>D19/1000</f>
@@ -1132,23 +1132,23 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>T-34</t>
+          <t>T-38B</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>228.96</v>
+        <v>25.33</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>6152</v>
+        <v>2313</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>20094</v>
+        <v>24878</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>17026</v>
+        <v>23590</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>15117</v>
+        <v>14244</v>
       </c>
       <c r="G20" s="15">
         <f>D20/1000</f>
@@ -1167,23 +1167,23 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>T-38B</t>
+          <t>T-38A</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>25.33</v>
+        <v>52.93</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>2313</v>
+        <v>3201</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>19538</v>
+        <v>24691</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>18389</v>
+        <v>22817</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>14244</v>
+        <v>13857</v>
       </c>
       <c r="G21" s="8">
         <f>D21/1000</f>
@@ -1202,23 +1202,23 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>T-38A</t>
+          <t>T-36A</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>52.93</v>
+        <v>36.89</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>3201</v>
+        <v>2563</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>19196</v>
+        <v>24666</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>17619</v>
+        <v>22853</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>13857</v>
+        <v>14740</v>
       </c>
       <c r="G22" s="15">
         <f>D22/1000</f>
@@ -1237,23 +1237,23 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>T-36A</t>
+          <t>T-36</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>36.89</v>
+        <v>93.86</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>2563</v>
+        <v>4450</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>19133</v>
+        <v>24453</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>17992</v>
+        <v>21485</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>14740</v>
+        <v>14968</v>
       </c>
       <c r="G23" s="8">
         <f>D23/1000</f>
@@ -1272,23 +1272,23 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>T-36</t>
+          <t>T-36B</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>93.86</v>
+        <v>39.71</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>4450</v>
+        <v>2648</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>19032</v>
+        <v>24331</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>16823</v>
+        <v>22454</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>14968</v>
+        <v>14442</v>
       </c>
       <c r="G24" s="15">
         <f>D24/1000</f>
@@ -1307,23 +1307,23 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>T-36B</t>
+          <t>T-36C</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>39.71</v>
+        <v>42.33</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>2648</v>
+        <v>3171</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>18678</v>
+        <v>23702</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>17592</v>
+        <v>21683</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>14442</v>
+        <v>14233</v>
       </c>
       <c r="G25" s="8">
         <f>D25/1000</f>
@@ -1342,23 +1342,23 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>T-33</t>
+          <t>T-34</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>187.06</v>
+        <v>228.96</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>5526</v>
+        <v>6152</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>18644</v>
+        <v>23548</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>16352</v>
+        <v>20246</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>13729</v>
+        <v>15117</v>
       </c>
       <c r="G26" s="15">
         <f>D26/1000</f>
@@ -1377,23 +1377,23 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>T-36C</t>
+          <t>T-33A</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>42.33</v>
+        <v>28.72</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>3171</v>
+        <v>2599</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>18227</v>
+        <v>22107</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>16669</v>
+        <v>20418</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>14233</v>
+        <v>14141</v>
       </c>
       <c r="G27" s="8">
         <f>D27/1000</f>
@@ -1412,23 +1412,23 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>T-32</t>
+          <t>T-33</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>82.03</v>
+        <v>187.06</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>3674</v>
+        <v>5526</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>18002</v>
+        <v>21561</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>16775</v>
+        <v>18746</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>13042</v>
+        <v>13729</v>
       </c>
       <c r="G28" s="15">
         <f>D28/1000</f>
@@ -1447,23 +1447,23 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>T-33A</t>
+          <t>T-33C</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>28.72</v>
+        <v>17.32</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>2599</v>
+        <v>1739</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>17481</v>
+        <v>21402</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>16246</v>
+        <v>20532</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>14141</v>
+        <v>13605</v>
       </c>
       <c r="G29" s="8">
         <f>D29/1000</f>
@@ -1482,23 +1482,23 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>T-32A</t>
+          <t>T-33B</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>49.81</v>
+        <v>28.89</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>3183</v>
+        <v>2630</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>17436</v>
+        <v>21151</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>16203</v>
+        <v>19934</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>12736</v>
+        <v>13724</v>
       </c>
       <c r="G30" s="15">
         <f>D30/1000</f>
@@ -1517,23 +1517,23 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>T-32B</t>
+          <t>T-33E</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>56.22</v>
+        <v>25.66</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>3219</v>
+        <v>2270</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>16889</v>
+        <v>21128</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>15702</v>
+        <v>20215</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>12386</v>
+        <v>13030</v>
       </c>
       <c r="G31" s="8">
         <f>D31/1000</f>
@@ -1552,23 +1552,23 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>T-33B</t>
+          <t>T-33F</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>28.89</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>2630</v>
+        <v>3934</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>16889</v>
+        <v>21062</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>15890</v>
+        <v>19582</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>13724</v>
+        <v>12932</v>
       </c>
       <c r="G32" s="15">
         <f>D32/1000</f>
@@ -1587,23 +1587,23 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>T-32C</t>
+          <t>T-33D</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>73.53</v>
+        <v>20.33</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>3551</v>
+        <v>1825</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>16885</v>
+        <v>20626</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>15493</v>
+        <v>19784</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>12059</v>
+        <v>13381</v>
       </c>
       <c r="G33" s="8">
         <f>D33/1000</f>
@@ -1622,23 +1622,23 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>T-33D</t>
+          <t>T-32A</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>20.33</v>
+        <v>49.81</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>1825</v>
+        <v>3183</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>16659</v>
+        <v>20277</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>15771</v>
+        <v>18507</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>13381</v>
+        <v>12736</v>
       </c>
       <c r="G34" s="15">
         <f>D34/1000</f>
@@ -1657,23 +1657,23 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>T-33F</t>
+          <t>T-32C</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>83.54000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>3934</v>
+        <v>3551</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>16659</v>
+        <v>20220</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>14725</v>
+        <v>18538</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>12932</v>
+        <v>12059</v>
       </c>
       <c r="G35" s="8">
         <f>D35/1000</f>
@@ -1692,23 +1692,23 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>T-33C</t>
+          <t>T-32B</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>17.32</v>
+        <v>56.22</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>1739</v>
+        <v>3219</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>16464</v>
+        <v>20086</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>15594</v>
+        <v>18366</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>13605</v>
+        <v>12386</v>
       </c>
       <c r="G36" s="15">
         <f>D36/1000</f>
@@ -1727,23 +1727,23 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>T-33E</t>
+          <t>T-30C</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>25.66</v>
+        <v>135.7</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>2270</v>
+        <v>5466</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>15858</v>
+        <v>19728</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>14728</v>
+        <v>16542</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>13030</v>
+        <v>9364</v>
       </c>
       <c r="G37" s="8">
         <f>D37/1000</f>
@@ -1762,23 +1762,23 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>T-29B</t>
+          <t>T-30D</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>51.46</v>
+        <v>27.34</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>3211</v>
+        <v>2417</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>13930</v>
+        <v>19728</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>12627</v>
+        <v>17921</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>10413</v>
+        <v>10355</v>
       </c>
       <c r="G38" s="15">
         <f>D38/1000</f>
@@ -1797,23 +1797,23 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>T-29D</t>
+          <t>T-32</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>204.97</v>
+        <v>82.03</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>6009</v>
+        <v>3674</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>13839</v>
+        <v>19625</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>11057</v>
+        <v>17734</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>9361</v>
+        <v>13042</v>
       </c>
       <c r="G39" s="8">
         <f>D39/1000</f>
@@ -1832,23 +1832,23 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>T-29A</t>
+          <t>T-29B</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>55.07</v>
+        <v>51.46</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>3294</v>
+        <v>3211</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>13665</v>
+        <v>19552</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>12020</v>
+        <v>18119</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>10324</v>
+        <v>10413</v>
       </c>
       <c r="G40" s="15">
         <f>D40/1000</f>
@@ -1867,23 +1867,23 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>T-30C</t>
+          <t>T-29A</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>135.7</v>
+        <v>55.07</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>5466</v>
+        <v>3294</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>13455</v>
+        <v>19442</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>11056</v>
+        <v>17507</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>9364</v>
+        <v>10324</v>
       </c>
       <c r="G41" s="8">
         <f>D41/1000</f>
@@ -1902,23 +1902,23 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>T-30D</t>
+          <t>T-29D</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>27.34</v>
+        <v>204.97</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>2417</v>
+        <v>6009</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>13375</v>
+        <v>19364</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>12338</v>
+        <v>16549</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>10355</v>
+        <v>9361</v>
       </c>
       <c r="G42" s="15">
         <f>D42/1000</f>
@@ -1947,10 +1947,10 @@
         <v>3031</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>13364</v>
+        <v>19197</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>11984</v>
+        <v>17468</v>
       </c>
       <c r="F43" s="7" t="n">
         <v>10293</v>
@@ -1982,10 +1982,10 @@
         <v>2710</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>12779</v>
+        <v>18606</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>11441</v>
+        <v>16936</v>
       </c>
       <c r="F44" s="14" t="n">
         <v>9510</v>
@@ -2007,23 +2007,23 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>T-26B</t>
+          <t>T-30B</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>24.59</v>
+        <v>40.19</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>3289</v>
+        <v>2657</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>12401</v>
+        <v>18126</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>10554</v>
+        <v>16542</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>8560</v>
+        <v>9367</v>
       </c>
       <c r="G45" s="8">
         <f>D45/1000</f>
@@ -2042,23 +2042,23 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>T-26C</t>
+          <t>T-27C</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>30.09</v>
+        <v>160.22</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>3233</v>
+        <v>5695</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>12401</v>
+        <v>17712</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>10128</v>
+        <v>14636</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>8180</v>
+        <v>7303</v>
       </c>
       <c r="G46" s="15">
         <f>D46/1000</f>
@@ -2077,23 +2077,23 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>T-30B</t>
+          <t>T-26B</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>40.19</v>
+        <v>24.59</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>2657</v>
+        <v>3289</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>12387</v>
+        <v>17263</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>11059</v>
+        <v>15487</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>9367</v>
+        <v>8560</v>
       </c>
       <c r="G47" s="8">
         <f>D47/1000</f>
@@ -2122,10 +2122,10 @@
         <v>6277</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>12275</v>
+        <v>17114</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>9145</v>
+        <v>14627</v>
       </c>
       <c r="F48" s="14" t="n">
         <v>7560</v>
@@ -2147,23 +2147,23 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>T-27C</t>
+          <t>T-27B</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>160.22</v>
+        <v>26.89</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>5695</v>
+        <v>2114</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>11940</v>
+        <v>16992</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>9142</v>
+        <v>15703</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>7303</v>
+        <v>7664</v>
       </c>
       <c r="G49" s="8">
         <f>D49/1000</f>
@@ -2182,23 +2182,23 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>T-27B</t>
+          <t>T-26C</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>26.89</v>
+        <v>30.09</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>2114</v>
+        <v>3233</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>11267</v>
+        <v>16887</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>10221</v>
+        <v>15487</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>7664</v>
+        <v>8180</v>
       </c>
       <c r="G50" s="15">
         <f>D50/1000</f>
@@ -2227,10 +2227,10 @@
         <v>2414</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>11062</v>
+        <v>16757</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>9862</v>
+        <v>15346</v>
       </c>
       <c r="F51" s="7" t="n">
         <v>8238</v>
@@ -2252,23 +2252,23 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>T-17</t>
+          <t>T-27A</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>190.66</v>
+        <v>48.43</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>7672</v>
+        <v>2895</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>10723</v>
+        <v>16275</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>8195</v>
+        <v>14636</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>5896</v>
+        <v>7306</v>
       </c>
       <c r="G52" s="15">
         <f>D52/1000</f>
@@ -2287,23 +2287,23 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>T-27A</t>
+          <t>T-17</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>48.43</v>
+        <v>190.66</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>2895</v>
+        <v>7672</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>10707</v>
+        <v>13805</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>9142</v>
+        <v>8926</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>7306</v>
+        <v>5896</v>
       </c>
       <c r="G53" s="8">
         <f>D53/1000</f>
@@ -2322,23 +2322,23 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>T-22</t>
+          <t>T-05C</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>303.58</v>
+        <v>41.44</v>
       </c>
       <c r="C54" s="13" t="n">
-        <v>7626</v>
+        <v>2838</v>
       </c>
       <c r="D54" s="14" t="n">
-        <v>10570</v>
+        <v>12508</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>6766</v>
+        <v>4965</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>6059</v>
+        <v>4215</v>
       </c>
       <c r="G54" s="15">
         <f>D54/1000</f>
@@ -2355,60 +2355,60 @@
       <c r="J54" s="17" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>T-21</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>189.65</v>
-      </c>
-      <c r="C55" s="6" t="n">
-        <v>6663</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>9885</v>
-      </c>
-      <c r="E55" s="7" t="n">
-        <v>6570</v>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>5929</v>
-      </c>
-      <c r="G55" s="8">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>T-05D</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="C55" s="20" t="n">
+        <v>2696</v>
+      </c>
+      <c r="D55" s="21" t="n">
+        <v>12497</v>
+      </c>
+      <c r="E55" s="21" t="n">
+        <v>4711</v>
+      </c>
+      <c r="F55" s="21" t="n">
+        <v>3966</v>
+      </c>
+      <c r="G55" s="22">
         <f>D55/1000</f>
         <v/>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="22">
         <f>E55/1000</f>
         <v/>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="23">
         <f>IFERROR(D55/F55,"")</f>
         <v/>
       </c>
-      <c r="J55" s="10" t="inlineStr"/>
+      <c r="J55" s="24" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>T-16</t>
+          <t>T-05B</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>46.34</v>
+        <v>31.8</v>
       </c>
       <c r="C56" s="13" t="n">
-        <v>2872</v>
+        <v>2339</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>8546</v>
+        <v>11794</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>7115</v>
+        <v>10412</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>5202</v>
+        <v>4262</v>
       </c>
       <c r="G56" s="15">
         <f>D56/1000</f>
@@ -2427,23 +2427,23 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>T-05C</t>
+          <t>T-CON</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>41.44</v>
+        <v>3.24</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>2838</v>
+        <v>1056</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>6384</v>
+        <v>11187</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>4965</v>
+        <v>4712</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>4215</v>
+        <v>3969</v>
       </c>
       <c r="G57" s="8">
         <f>D57/1000</f>
@@ -2460,60 +2460,60 @@
       <c r="J57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>T-03</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="n">
-        <v>286.07</v>
-      </c>
-      <c r="C58" s="13" t="n">
-        <v>6866</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>6353</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>2981</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>2661</v>
-      </c>
-      <c r="G58" s="15">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>T-05A</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="C58" s="20" t="n">
+        <v>3023</v>
+      </c>
+      <c r="D58" s="21" t="n">
+        <v>11041</v>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>4159</v>
+      </c>
+      <c r="F58" s="21" t="n">
+        <v>3629</v>
+      </c>
+      <c r="G58" s="22">
         <f>D58/1000</f>
         <v/>
       </c>
-      <c r="H58" s="15">
+      <c r="H58" s="22">
         <f>E58/1000</f>
         <v/>
       </c>
-      <c r="I58" s="16">
+      <c r="I58" s="23">
         <f>IFERROR(D58/F58,"")</f>
         <v/>
       </c>
-      <c r="J58" s="17" t="inlineStr"/>
+      <c r="J58" s="24" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>T-05B</t>
+          <t>T-22</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>31.8</v>
+        <v>303.58</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>2339</v>
+        <v>7626</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>6082</v>
+        <v>10633</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>5019</v>
+        <v>6784</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>4262</v>
+        <v>6059</v>
       </c>
       <c r="G59" s="8">
         <f>D59/1000</f>
@@ -2530,60 +2530,60 @@
       <c r="J59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="B60" s="12" t="n">
+      <c r="B60" s="19" t="n">
         <v>172.75</v>
       </c>
-      <c r="C60" s="13" t="n">
+      <c r="C60" s="20" t="n">
         <v>5905</v>
       </c>
-      <c r="D60" s="14" t="n">
-        <v>5956</v>
-      </c>
-      <c r="E60" s="14" t="n">
+      <c r="D60" s="21" t="n">
+        <v>10420</v>
+      </c>
+      <c r="E60" s="21" t="n">
         <v>3033</v>
       </c>
-      <c r="F60" s="14" t="n">
+      <c r="F60" s="21" t="n">
         <v>2656</v>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="22">
         <f>D60/1000</f>
         <v/>
       </c>
-      <c r="H60" s="15">
+      <c r="H60" s="22">
         <f>E60/1000</f>
         <v/>
       </c>
-      <c r="I60" s="16">
+      <c r="I60" s="23">
         <f>IFERROR(D60/F60,"")</f>
         <v/>
       </c>
-      <c r="J60" s="17" t="inlineStr"/>
+      <c r="J60" s="24" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>T-05D</t>
+          <t>T-21</t>
         </is>
       </c>
       <c r="B61" s="5" t="n">
-        <v>33.87</v>
+        <v>189.65</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>2696</v>
+        <v>6663</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>5870</v>
+        <v>9935</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>4711</v>
+        <v>6580</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>3966</v>
+        <v>5929</v>
       </c>
       <c r="G61" s="8">
         <f>D61/1000</f>
@@ -2600,60 +2600,60 @@
       <c r="J61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>T-05A</t>
-        </is>
-      </c>
-      <c r="B62" s="12" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>3023</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>5667</v>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v>4159</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>3629</v>
-      </c>
-      <c r="G62" s="15">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>T-03</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>286.07</v>
+      </c>
+      <c r="C62" s="20" t="n">
+        <v>6866</v>
+      </c>
+      <c r="D62" s="21" t="n">
+        <v>9641</v>
+      </c>
+      <c r="E62" s="21" t="n">
+        <v>3577</v>
+      </c>
+      <c r="F62" s="21" t="n">
+        <v>2661</v>
+      </c>
+      <c r="G62" s="22">
         <f>D62/1000</f>
         <v/>
       </c>
-      <c r="H62" s="15">
+      <c r="H62" s="22">
         <f>E62/1000</f>
         <v/>
       </c>
-      <c r="I62" s="16">
+      <c r="I62" s="23">
         <f>IFERROR(D62/F62,"")</f>
         <v/>
       </c>
-      <c r="J62" s="17" t="inlineStr"/>
+      <c r="J62" s="24" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>T-06C</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>36.46</v>
+        <v>46.34</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>2605</v>
+        <v>2872</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>5345</v>
+        <v>9077</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>4334</v>
+        <v>7136</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>3603</v>
+        <v>5202</v>
       </c>
       <c r="G63" s="8">
         <f>D63/1000</f>
@@ -2670,130 +2670,130 @@
       <c r="J63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>T-CON</t>
-        </is>
-      </c>
-      <c r="B64" s="12" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="C64" s="13" t="n">
-        <v>1056</v>
-      </c>
-      <c r="D64" s="14" t="n">
-        <v>5145</v>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v>4712</v>
-      </c>
-      <c r="F64" s="14" t="n">
-        <v>3969</v>
-      </c>
-      <c r="G64" s="15">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>T-07B</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="C64" s="20" t="n">
+        <v>3558</v>
+      </c>
+      <c r="D64" s="21" t="n">
+        <v>6604</v>
+      </c>
+      <c r="E64" s="21" t="n">
+        <v>2090</v>
+      </c>
+      <c r="F64" s="21" t="n">
+        <v>1840</v>
+      </c>
+      <c r="G64" s="22">
         <f>D64/1000</f>
         <v/>
       </c>
-      <c r="H64" s="15">
+      <c r="H64" s="22">
         <f>E64/1000</f>
         <v/>
       </c>
-      <c r="I64" s="16">
+      <c r="I64" s="23">
         <f>IFERROR(D64/F64,"")</f>
         <v/>
       </c>
-      <c r="J64" s="17" t="inlineStr"/>
+      <c r="J64" s="24" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>T-06B</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>40.44</v>
-      </c>
-      <c r="C65" s="6" t="n">
-        <v>2957</v>
-      </c>
-      <c r="D65" s="7" t="n">
-        <v>4739</v>
-      </c>
-      <c r="E65" s="7" t="n">
-        <v>3329</v>
-      </c>
-      <c r="F65" s="7" t="n">
-        <v>2698</v>
-      </c>
-      <c r="G65" s="8">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>T-02</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>159.81</v>
+      </c>
+      <c r="C65" s="20" t="n">
+        <v>5989</v>
+      </c>
+      <c r="D65" s="21" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E65" s="21" t="n">
+        <v>788</v>
+      </c>
+      <c r="F65" s="21" t="n">
+        <v>623</v>
+      </c>
+      <c r="G65" s="22">
         <f>D65/1000</f>
         <v/>
       </c>
-      <c r="H65" s="8">
+      <c r="H65" s="22">
         <f>E65/1000</f>
         <v/>
       </c>
-      <c r="I65" s="9">
+      <c r="I65" s="23">
         <f>IFERROR(D65/F65,"")</f>
         <v/>
       </c>
-      <c r="J65" s="10" t="inlineStr"/>
+      <c r="J65" s="24" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="inlineStr">
-        <is>
-          <t>T-09</t>
-        </is>
-      </c>
-      <c r="B66" s="19" t="n">
-        <v>226.37</v>
-      </c>
-      <c r="C66" s="20" t="n">
-        <v>7413</v>
-      </c>
-      <c r="D66" s="21" t="n">
-        <v>4410</v>
-      </c>
-      <c r="E66" s="21" t="n">
-        <v>762</v>
-      </c>
-      <c r="F66" s="21" t="n">
-        <v>554</v>
-      </c>
-      <c r="G66" s="22">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>T-06C</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>2605</v>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>5345</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>4334</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>3603</v>
+      </c>
+      <c r="G66" s="15">
         <f>D66/1000</f>
         <v/>
       </c>
-      <c r="H66" s="22">
+      <c r="H66" s="15">
         <f>E66/1000</f>
         <v/>
       </c>
-      <c r="I66" s="23">
+      <c r="I66" s="16">
         <f>IFERROR(D66/F66,"")</f>
         <v/>
       </c>
-      <c r="J66" s="24" t="inlineStr"/>
+      <c r="J66" s="17" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-09</t>
         </is>
       </c>
       <c r="B67" s="19" t="n">
-        <v>159.81</v>
+        <v>226.37</v>
       </c>
       <c r="C67" s="20" t="n">
-        <v>5989</v>
+        <v>7413</v>
       </c>
       <c r="D67" s="21" t="n">
-        <v>3775</v>
+        <v>5130</v>
       </c>
       <c r="E67" s="21" t="n">
-        <v>788</v>
+        <v>762</v>
       </c>
       <c r="F67" s="21" t="n">
-        <v>623</v>
+        <v>554</v>
       </c>
       <c r="G67" s="22">
         <f>D67/1000</f>
@@ -2812,23 +2812,23 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>T-06A</t>
+          <t>T-06B</t>
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>39.74</v>
+        <v>40.44</v>
       </c>
       <c r="C68" s="13" t="n">
-        <v>3355</v>
+        <v>2957</v>
       </c>
       <c r="D68" s="14" t="n">
-        <v>3737</v>
+        <v>4739</v>
       </c>
       <c r="E68" s="14" t="n">
-        <v>2075</v>
+        <v>3329</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>1816</v>
+        <v>2698</v>
       </c>
       <c r="G68" s="15">
         <f>D68/1000</f>
@@ -2847,23 +2847,23 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>T-07B</t>
+          <t>T-06A</t>
         </is>
       </c>
       <c r="B69" s="5" t="n">
-        <v>72.52</v>
+        <v>39.74</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>3558</v>
+        <v>3355</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>3625</v>
+        <v>3737</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>2090</v>
+        <v>2075</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>1840</v>
+        <v>1816</v>
       </c>
       <c r="G69" s="8">
         <f>D69/1000</f>
@@ -2892,7 +2892,7 @@
         <v>5228</v>
       </c>
       <c r="D70" s="21" t="n">
-        <v>2986</v>
+        <v>3575</v>
       </c>
       <c r="E70" s="21" t="n">
         <v>409</v>
@@ -2917,23 +2917,23 @@
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="B71" s="19" t="n">
-        <v>93.41</v>
+        <v>110.29</v>
       </c>
       <c r="C71" s="20" t="n">
-        <v>4212</v>
+        <v>5351</v>
       </c>
       <c r="D71" s="21" t="n">
-        <v>2666</v>
+        <v>3453</v>
       </c>
       <c r="E71" s="21" t="n">
-        <v>720</v>
+        <v>172</v>
       </c>
       <c r="F71" s="21" t="n">
-        <v>539</v>
+        <v>172</v>
       </c>
       <c r="G71" s="22">
         <f>D71/1000</f>
@@ -2952,23 +2952,23 @@
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>T-07</t>
         </is>
       </c>
       <c r="B72" s="19" t="n">
-        <v>110.29</v>
+        <v>93.41</v>
       </c>
       <c r="C72" s="20" t="n">
-        <v>5351</v>
+        <v>4212</v>
       </c>
       <c r="D72" s="21" t="n">
-        <v>2527</v>
+        <v>2692</v>
       </c>
       <c r="E72" s="21" t="n">
-        <v>172</v>
+        <v>720</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>172</v>
+        <v>539</v>
       </c>
       <c r="G72" s="22">
         <f>D72/1000</f>
@@ -3032,7 +3032,7 @@
         <v>2527</v>
       </c>
       <c r="D74" s="21" t="n">
-        <v>1502</v>
+        <v>1885</v>
       </c>
       <c r="E74" s="21" t="n">
         <v>250</v>

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B83E0D9-7976-4C83-9750-1B887F816F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB84FE12-A9C6-4D52-8FAC-C228946F7195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34755" yWindow="2610" windowWidth="17625" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB84FE12-A9C6-4D52-8FAC-C228946F7195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1550036D-F4CC-4D75-890A-FB0532FB7AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,6 +72,9 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-41B</t>
+  </si>
+  <si>
     <t>T-41A</t>
   </si>
   <si>
@@ -81,6 +84,15 @@
     <t>T-40A</t>
   </si>
   <si>
+    <t>T-33A</t>
+  </si>
+  <si>
+    <t>T-33B</t>
+  </si>
+  <si>
+    <t>T-33</t>
+  </si>
+  <si>
     <t>T-39</t>
   </si>
   <si>
@@ -93,15 +105,6 @@
     <t>T-36C</t>
   </si>
   <si>
-    <t>T-33A</t>
-  </si>
-  <si>
-    <t>T-33</t>
-  </si>
-  <si>
-    <t>T-41B</t>
-  </si>
-  <si>
     <t>T-39B</t>
   </si>
   <si>
@@ -114,9 +117,6 @@
     <t>T-36</t>
   </si>
   <si>
-    <t>T-33B</t>
-  </si>
-  <si>
     <t>T-34</t>
   </si>
   <si>
@@ -147,6 +147,54 @@
     <t>T-36A</t>
   </si>
   <si>
+    <t>T-33C</t>
+  </si>
+  <si>
+    <t>T-33F</t>
+  </si>
+  <si>
+    <t>T-33E</t>
+  </si>
+  <si>
+    <t>T-29A</t>
+  </si>
+  <si>
+    <t>T-29B</t>
+  </si>
+  <si>
+    <t>T-29D</t>
+  </si>
+  <si>
+    <t>T-30C</t>
+  </si>
+  <si>
+    <t>T-30A</t>
+  </si>
+  <si>
+    <t>T-32C</t>
+  </si>
+  <si>
+    <t>T-30D</t>
+  </si>
+  <si>
+    <t>T-32B</t>
+  </si>
+  <si>
+    <t>T-27C</t>
+  </si>
+  <si>
+    <t>T-26B</t>
+  </si>
+  <si>
+    <t>T-26A</t>
+  </si>
+  <si>
+    <t>T-30B</t>
+  </si>
+  <si>
+    <t>T-27D</t>
+  </si>
+  <si>
     <t>T-33D</t>
   </si>
   <si>
@@ -156,127 +204,79 @@
     <t>T-32A</t>
   </si>
   <si>
-    <t>T-33F</t>
-  </si>
-  <si>
-    <t>T-32B</t>
-  </si>
-  <si>
-    <t>T-33C</t>
-  </si>
-  <si>
-    <t>T-33E</t>
-  </si>
-  <si>
-    <t>T-32C</t>
-  </si>
-  <si>
-    <t>T-30C</t>
-  </si>
-  <si>
-    <t>T-30D</t>
-  </si>
-  <si>
-    <t>T-29A</t>
-  </si>
-  <si>
-    <t>T-29B</t>
+    <t>T-29C</t>
+  </si>
+  <si>
+    <t>T-27A</t>
+  </si>
+  <si>
+    <t>T-26C</t>
   </si>
   <si>
     <t>T-27B</t>
   </si>
   <si>
-    <t>T-27C</t>
-  </si>
-  <si>
-    <t>T-30A</t>
-  </si>
-  <si>
-    <t>T-29D</t>
-  </si>
-  <si>
-    <t>T-27A</t>
+    <t>T-06C</t>
   </si>
   <si>
     <t>T-17</t>
   </si>
   <si>
-    <t>T-26B</t>
-  </si>
-  <si>
-    <t>T-30B</t>
-  </si>
-  <si>
-    <t>T-26A</t>
-  </si>
-  <si>
-    <t>T-27D</t>
-  </si>
-  <si>
-    <t>T-29C</t>
+    <t>T-05D</t>
+  </si>
+  <si>
+    <t>T-05C</t>
+  </si>
+  <si>
+    <t>T-CON</t>
+  </si>
+  <si>
+    <t>T-05B</t>
+  </si>
+  <si>
+    <t>T-21</t>
+  </si>
+  <si>
+    <t>T-22</t>
+  </si>
+  <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>T-07B</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-05A</t>
+  </si>
+  <si>
+    <t>T-06B</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-06A</t>
   </si>
   <si>
     <t>T-16</t>
   </si>
   <si>
-    <t>T-26C</t>
-  </si>
-  <si>
-    <t>T-06B</t>
-  </si>
-  <si>
-    <t>T-06C</t>
-  </si>
-  <si>
-    <t>T-05D</t>
-  </si>
-  <si>
-    <t>T-06A</t>
-  </si>
-  <si>
-    <t>T-05C</t>
-  </si>
-  <si>
-    <t>T-CON</t>
-  </si>
-  <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>T-05B</t>
-  </si>
-  <si>
-    <t>T-21</t>
-  </si>
-  <si>
-    <t>T-22</t>
-  </si>
-  <si>
-    <t>T-05A</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-07B</t>
-  </si>
-  <si>
     <t>T-07</t>
   </si>
   <si>
-    <t>T-02</t>
-  </si>
-  <si>
     <t>T-09</t>
   </si>
   <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-10B</t>
+  </si>
+  <si>
     <t>T-01</t>
-  </si>
-  <si>
-    <t>T-10B</t>
-  </si>
-  <si>
-    <t>T-08</t>
   </si>
   <si>
     <t>T-10</t>
@@ -862,31 +862,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>150.53</v>
+        <v>38.03</v>
       </c>
       <c r="C5" s="6">
-        <v>4897</v>
+        <v>2973</v>
       </c>
       <c r="D5" s="7">
-        <v>30800</v>
+        <v>32882</v>
       </c>
       <c r="E5" s="7">
-        <v>27839</v>
+        <v>27982</v>
       </c>
       <c r="F5" s="7">
-        <v>12769</v>
+        <v>12971</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G36" si="0">D5/1000</f>
-        <v>30.8</v>
+        <v>32.881999999999998</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H36" si="1">E5/1000</f>
-        <v>27.838999999999999</v>
+        <v>27.981999999999999</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I36" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.4120917847912913</v>
+        <v>2.5350397039549764</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -895,31 +895,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>39.65</v>
+        <v>150.53</v>
       </c>
       <c r="C6" s="13">
-        <v>2528</v>
+        <v>4897</v>
       </c>
       <c r="D6" s="14">
-        <v>30679</v>
+        <v>32336</v>
       </c>
       <c r="E6" s="14">
-        <v>28951</v>
+        <v>27839</v>
       </c>
       <c r="F6" s="14">
-        <v>13714</v>
+        <v>12769</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>30.678999999999998</v>
+        <v>32.335999999999999</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>28.951000000000001</v>
+        <v>27.838999999999999</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>2.237057022021292</v>
+        <v>2.5323831153575065</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -928,31 +928,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>85.18</v>
+        <v>39.65</v>
       </c>
       <c r="C7" s="6">
-        <v>3658</v>
+        <v>2528</v>
       </c>
       <c r="D7" s="7">
-        <v>30391</v>
+        <v>30679</v>
       </c>
       <c r="E7" s="7">
-        <v>28133</v>
+        <v>28951</v>
       </c>
       <c r="F7" s="7">
-        <v>13732</v>
+        <v>13714</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>30.390999999999998</v>
+        <v>30.678999999999998</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>28.132999999999999</v>
+        <v>28.951000000000001</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>2.21315176230702</v>
+        <v>2.237057022021292</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -961,31 +961,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="12">
-        <v>96.66</v>
+        <v>85.18</v>
       </c>
       <c r="C8" s="13">
-        <v>4267</v>
+        <v>3658</v>
       </c>
       <c r="D8" s="14">
-        <v>29879</v>
+        <v>30391</v>
       </c>
       <c r="E8" s="14">
-        <v>27380</v>
+        <v>28133</v>
       </c>
       <c r="F8" s="14">
-        <v>14390</v>
+        <v>13732</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>29.879000000000001</v>
+        <v>30.390999999999998</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>27.38</v>
+        <v>28.132999999999999</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.0763724808895065</v>
+        <v>2.21315176230702</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -994,31 +994,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>27.75</v>
+        <v>28.72</v>
       </c>
       <c r="C9" s="6">
-        <v>2368</v>
+        <v>2599</v>
       </c>
       <c r="D9" s="7">
-        <v>29667</v>
+        <v>30093</v>
       </c>
       <c r="E9" s="7">
-        <v>25730</v>
+        <v>24978</v>
       </c>
       <c r="F9" s="7">
-        <v>14263</v>
+        <v>14141</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>29.667000000000002</v>
+        <v>30.093</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>25.73</v>
+        <v>24.978000000000002</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>2.0799971955409102</v>
+        <v>2.1280673219715722</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -1027,31 +1027,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="12">
-        <v>39.71</v>
+        <v>28.89</v>
       </c>
       <c r="C10" s="13">
-        <v>2648</v>
+        <v>2630</v>
       </c>
       <c r="D10" s="14">
-        <v>29611</v>
+        <v>30092</v>
       </c>
       <c r="E10" s="14">
-        <v>24960</v>
+        <v>20166</v>
       </c>
       <c r="F10" s="14">
-        <v>14442</v>
+        <v>13724</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>29.611000000000001</v>
+        <v>30.091999999999999</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>24.96</v>
+        <v>20.166</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>2.0503392881872315</v>
+        <v>2.19265520256485</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -1060,31 +1060,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>42.33</v>
+        <v>187.06</v>
       </c>
       <c r="C11" s="6">
-        <v>3171</v>
+        <v>5526</v>
       </c>
       <c r="D11" s="7">
-        <v>29609</v>
+        <v>30008</v>
       </c>
       <c r="E11" s="7">
-        <v>26483</v>
+        <v>18746</v>
       </c>
       <c r="F11" s="7">
-        <v>14233</v>
+        <v>13729</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>29.609000000000002</v>
+        <v>30.007999999999999</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>26.483000000000001</v>
+        <v>18.745999999999999</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>2.0803063303590248</v>
+        <v>2.1857382183698739</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1093,31 +1093,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>28.72</v>
+        <v>96.66</v>
       </c>
       <c r="C12" s="13">
-        <v>2599</v>
+        <v>4267</v>
       </c>
       <c r="D12" s="14">
-        <v>29589</v>
+        <v>29879</v>
       </c>
       <c r="E12" s="14">
-        <v>23424</v>
+        <v>27380</v>
       </c>
       <c r="F12" s="14">
-        <v>14141</v>
+        <v>14390</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>29.588999999999999</v>
+        <v>29.879000000000001</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>23.423999999999999</v>
+        <v>27.38</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>2.0924262781981473</v>
+        <v>2.0763724808895065</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1126,31 +1126,31 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>187.06</v>
+        <v>27.75</v>
       </c>
       <c r="C13" s="6">
-        <v>5526</v>
+        <v>2368</v>
       </c>
       <c r="D13" s="7">
-        <v>29579</v>
+        <v>29667</v>
       </c>
       <c r="E13" s="7">
-        <v>18746</v>
+        <v>25730</v>
       </c>
       <c r="F13" s="7">
-        <v>13729</v>
+        <v>14263</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>29.579000000000001</v>
+        <v>29.667000000000002</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>18.745999999999999</v>
+        <v>25.73</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>2.1544904945735306</v>
+        <v>2.0799971955409102</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1159,31 +1159,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>38.03</v>
+        <v>39.71</v>
       </c>
       <c r="C14" s="13">
-        <v>2973</v>
+        <v>2648</v>
       </c>
       <c r="D14" s="14">
-        <v>29578</v>
+        <v>29611</v>
       </c>
       <c r="E14" s="14">
-        <v>27982</v>
+        <v>24960</v>
       </c>
       <c r="F14" s="14">
-        <v>12971</v>
+        <v>14442</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>29.577999999999999</v>
+        <v>29.611000000000001</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>27.981999999999999</v>
+        <v>24.96</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>2.2803176316398117</v>
+        <v>2.0503392881872315</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1192,31 +1192,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>27.21</v>
+        <v>42.33</v>
       </c>
       <c r="C15" s="6">
-        <v>2143</v>
+        <v>3171</v>
       </c>
       <c r="D15" s="7">
-        <v>29573</v>
+        <v>29609</v>
       </c>
       <c r="E15" s="7">
-        <v>25688</v>
+        <v>25397</v>
       </c>
       <c r="F15" s="7">
-        <v>14837</v>
+        <v>14233</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>29.573</v>
+        <v>29.609000000000002</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>25.687999999999999</v>
+        <v>25.396999999999998</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>1.9931926939408235</v>
+        <v>2.0803063303590248</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1225,31 +1225,31 @@
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>20.03</v>
+        <v>27.21</v>
       </c>
       <c r="C16" s="13">
-        <v>1858</v>
+        <v>2143</v>
       </c>
       <c r="D16" s="14">
-        <v>29572</v>
+        <v>29573</v>
       </c>
       <c r="E16" s="14">
-        <v>27963</v>
+        <v>25688</v>
       </c>
       <c r="F16" s="14">
-        <v>14553</v>
+        <v>14837</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>29.571999999999999</v>
+        <v>29.573</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>27.963000000000001</v>
+        <v>25.687999999999999</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>2.0320208891637463</v>
+        <v>1.9931926939408235</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1258,19 +1258,19 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>31</v>
+        <v>20.03</v>
       </c>
       <c r="C17" s="6">
-        <v>2363</v>
+        <v>1858</v>
       </c>
       <c r="D17" s="7">
         <v>29572</v>
       </c>
       <c r="E17" s="7">
-        <v>28321</v>
+        <v>27963</v>
       </c>
       <c r="F17" s="7">
-        <v>14034</v>
+        <v>14553</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
@@ -1278,11 +1278,11 @@
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>28.321000000000002</v>
+        <v>27.963000000000001</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.1071683055436798</v>
+        <v>2.0320208891637463</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1291,31 +1291,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>93.86</v>
+        <v>31</v>
       </c>
       <c r="C18" s="13">
-        <v>4450</v>
+        <v>2363</v>
       </c>
       <c r="D18" s="14">
-        <v>29570</v>
+        <v>29572</v>
       </c>
       <c r="E18" s="14">
-        <v>23553</v>
+        <v>28321</v>
       </c>
       <c r="F18" s="14">
-        <v>14968</v>
+        <v>14034</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>29.57</v>
+        <v>29.571999999999999</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>23.553000000000001</v>
+        <v>28.321000000000002</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>1.9755478353821485</v>
+        <v>2.1071683055436798</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1324,31 +1324,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>28.89</v>
+        <v>93.86</v>
       </c>
       <c r="C19" s="6">
-        <v>2630</v>
+        <v>4450</v>
       </c>
       <c r="D19" s="7">
-        <v>29560</v>
+        <v>29570</v>
       </c>
       <c r="E19" s="7">
-        <v>22421</v>
+        <v>23553</v>
       </c>
       <c r="F19" s="7">
-        <v>13724</v>
+        <v>14968</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>29.56</v>
+        <v>29.57</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>22.420999999999999</v>
+        <v>23.553000000000001</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>2.1538909938793354</v>
+        <v>1.9755478353821485</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1687,31 +1687,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>20.329999999999998</v>
+        <v>17.32</v>
       </c>
       <c r="C30" s="13">
-        <v>1825</v>
+        <v>1739</v>
       </c>
       <c r="D30" s="14">
-        <v>23706</v>
+        <v>25342</v>
       </c>
       <c r="E30" s="14">
-        <v>21448</v>
+        <v>24343</v>
       </c>
       <c r="F30" s="14">
-        <v>13381</v>
+        <v>13605</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>23.706</v>
+        <v>25.341999999999999</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>21.448</v>
+        <v>24.343</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.7716164711157611</v>
+        <v>1.8626975376699744</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1720,31 +1720,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>82.03</v>
+        <v>83.54</v>
       </c>
       <c r="C31" s="6">
-        <v>3674</v>
+        <v>3934</v>
       </c>
       <c r="D31" s="7">
-        <v>23688</v>
+        <v>25160</v>
       </c>
       <c r="E31" s="7">
-        <v>17734</v>
+        <v>20006</v>
       </c>
       <c r="F31" s="7">
-        <v>13042</v>
+        <v>12932</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>23.687999999999999</v>
+        <v>25.16</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>17.734000000000002</v>
+        <v>20.006</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.8162858457291826</v>
+        <v>1.9455613980822766</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1753,31 +1753,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>49.81</v>
+        <v>25.66</v>
       </c>
       <c r="C32" s="13">
-        <v>3183</v>
+        <v>2270</v>
       </c>
       <c r="D32" s="14">
-        <v>23688</v>
+        <v>25048</v>
       </c>
       <c r="E32" s="14">
-        <v>18507</v>
+        <v>23468</v>
       </c>
       <c r="F32" s="14">
-        <v>12736</v>
+        <v>13030</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>23.687999999999999</v>
+        <v>25.047999999999998</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>18.507000000000001</v>
+        <v>23.468</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>1.8599246231155779</v>
+        <v>1.9223330775134306</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1786,31 +1786,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>83.54</v>
+        <v>55.07</v>
       </c>
       <c r="C33" s="6">
-        <v>3934</v>
+        <v>3294</v>
       </c>
       <c r="D33" s="7">
-        <v>23667</v>
+        <v>24700</v>
       </c>
       <c r="E33" s="7">
-        <v>21175</v>
+        <v>20755</v>
       </c>
       <c r="F33" s="7">
-        <v>12932</v>
+        <v>10324</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>23.667000000000002</v>
+        <v>24.7</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>21.175000000000001</v>
+        <v>20.754999999999999</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.8301113516857408</v>
+        <v>2.3924835335141417</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1819,31 +1819,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>56.22</v>
+        <v>51.46</v>
       </c>
       <c r="C34" s="13">
-        <v>3219</v>
+        <v>3211</v>
       </c>
       <c r="D34" s="14">
-        <v>23139</v>
+        <v>24671</v>
       </c>
       <c r="E34" s="14">
-        <v>19961</v>
+        <v>20063</v>
       </c>
       <c r="F34" s="14">
-        <v>12386</v>
+        <v>10413</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>23.138999999999999</v>
+        <v>24.670999999999999</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>19.960999999999999</v>
+        <v>20.062999999999999</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.8681575972872597</v>
+        <v>2.3692499759915489</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1852,31 +1852,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>17.32</v>
+        <v>204.97</v>
       </c>
       <c r="C35" s="6">
-        <v>1739</v>
+        <v>6009</v>
       </c>
       <c r="D35" s="7">
-        <v>22995</v>
+        <v>24566</v>
       </c>
       <c r="E35" s="7">
-        <v>22125</v>
+        <v>18872</v>
       </c>
       <c r="F35" s="7">
-        <v>13605</v>
+        <v>9361</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>22.995000000000001</v>
+        <v>24.565999999999999</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>22.125</v>
+        <v>18.872</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>1.6901874310915104</v>
+        <v>2.6242922764661896</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1885,31 +1885,31 @@
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>25.66</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C36" s="13">
-        <v>2270</v>
+        <v>5466</v>
       </c>
       <c r="D36" s="14">
-        <v>22785</v>
+        <v>23415</v>
       </c>
       <c r="E36" s="14">
-        <v>22024</v>
+        <v>19769</v>
       </c>
       <c r="F36" s="14">
-        <v>13030</v>
+        <v>9364</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>22.785</v>
+        <v>23.414999999999999</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>22.024000000000001</v>
+        <v>19.768999999999998</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.7486569455103607</v>
+        <v>2.5005339598462197</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1918,31 +1918,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>73.53</v>
+        <v>36.369999999999997</v>
       </c>
       <c r="C37" s="6">
-        <v>3551</v>
+        <v>3031</v>
       </c>
       <c r="D37" s="7">
-        <v>21967</v>
+        <v>23413</v>
       </c>
       <c r="E37" s="7">
-        <v>20449</v>
+        <v>20695</v>
       </c>
       <c r="F37" s="7">
-        <v>12059</v>
+        <v>10293</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" ref="G37:G68" si="3">D37/1000</f>
-        <v>21.966999999999999</v>
+        <v>23.413</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" ref="H37:H68" si="4">E37/1000</f>
-        <v>20.449000000000002</v>
+        <v>20.695</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" ref="I37:I68" si="5">IFERROR(D37/F37,"")</f>
-        <v>1.8216270005804793</v>
+        <v>2.2746526765763142</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1951,31 +1951,31 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>135.69999999999999</v>
+        <v>73.53</v>
       </c>
       <c r="C38" s="13">
-        <v>5466</v>
+        <v>3551</v>
       </c>
       <c r="D38" s="14">
-        <v>21879</v>
+        <v>23341</v>
       </c>
       <c r="E38" s="14">
-        <v>18355</v>
+        <v>20000</v>
       </c>
       <c r="F38" s="14">
-        <v>9364</v>
+        <v>12059</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="3"/>
-        <v>21.879000000000001</v>
+        <v>23.341000000000001</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="4"/>
-        <v>18.355</v>
+        <v>20</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="5"/>
-        <v>2.3365014950875693</v>
+        <v>1.9355667965834646</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -1990,25 +1990,25 @@
         <v>2417</v>
       </c>
       <c r="D39" s="7">
-        <v>21879</v>
+        <v>23005</v>
       </c>
       <c r="E39" s="7">
-        <v>19734</v>
+        <v>21148</v>
       </c>
       <c r="F39" s="7">
         <v>10355</v>
       </c>
       <c r="G39" s="8">
         <f t="shared" si="3"/>
-        <v>21.879000000000001</v>
+        <v>23.004999999999999</v>
       </c>
       <c r="H39" s="8">
         <f t="shared" si="4"/>
-        <v>19.734000000000002</v>
+        <v>21.148</v>
       </c>
       <c r="I39" s="9">
         <f t="shared" si="5"/>
-        <v>2.1128923225494929</v>
+        <v>2.2216320618058907</v>
       </c>
       <c r="J39" s="10"/>
     </row>
@@ -2017,97 +2017,97 @@
         <v>47</v>
       </c>
       <c r="B40" s="12">
-        <v>55.07</v>
+        <v>56.22</v>
       </c>
       <c r="C40" s="13">
-        <v>3294</v>
+        <v>3219</v>
       </c>
       <c r="D40" s="14">
-        <v>21459</v>
+        <v>22962</v>
       </c>
       <c r="E40" s="14">
-        <v>19341</v>
+        <v>18956</v>
       </c>
       <c r="F40" s="14">
-        <v>10324</v>
+        <v>12386</v>
       </c>
       <c r="G40" s="15">
         <f t="shared" si="3"/>
-        <v>21.459</v>
+        <v>22.962</v>
       </c>
       <c r="H40" s="15">
         <f t="shared" si="4"/>
-        <v>19.341000000000001</v>
+        <v>18.956</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="5"/>
-        <v>2.0785548237117397</v>
+        <v>1.8538672694978202</v>
       </c>
       <c r="J40" s="17"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="5">
-        <v>51.46</v>
-      </c>
-      <c r="C41" s="6">
-        <v>3211</v>
-      </c>
-      <c r="D41" s="7">
-        <v>21418</v>
-      </c>
-      <c r="E41" s="7">
-        <v>18648</v>
-      </c>
-      <c r="F41" s="7">
-        <v>10413</v>
-      </c>
-      <c r="G41" s="8">
+      <c r="B41" s="19">
+        <v>160.22</v>
+      </c>
+      <c r="C41" s="20">
+        <v>5695</v>
+      </c>
+      <c r="D41" s="21">
+        <v>22099</v>
+      </c>
+      <c r="E41" s="21">
+        <v>14636</v>
+      </c>
+      <c r="F41" s="21">
+        <v>7303</v>
+      </c>
+      <c r="G41" s="22">
         <f t="shared" si="3"/>
-        <v>21.417999999999999</v>
-      </c>
-      <c r="H41" s="8">
+        <v>22.099</v>
+      </c>
+      <c r="H41" s="22">
         <f t="shared" si="4"/>
-        <v>18.648</v>
-      </c>
-      <c r="I41" s="9">
+        <v>14.635999999999999</v>
+      </c>
+      <c r="I41" s="23">
         <f t="shared" si="5"/>
-        <v>2.0568520119081919</v>
-      </c>
-      <c r="J41" s="10"/>
+        <v>3.0260167054635083</v>
+      </c>
+      <c r="J41" s="24"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>49</v>
       </c>
       <c r="B42" s="12">
-        <v>26.89</v>
+        <v>24.59</v>
       </c>
       <c r="C42" s="13">
-        <v>2114</v>
+        <v>3289</v>
       </c>
       <c r="D42" s="14">
-        <v>21390</v>
+        <v>21676</v>
       </c>
       <c r="E42" s="14">
-        <v>20184</v>
+        <v>16887</v>
       </c>
       <c r="F42" s="14">
-        <v>7664</v>
+        <v>8560</v>
       </c>
       <c r="G42" s="15">
         <f t="shared" si="3"/>
-        <v>21.39</v>
+        <v>21.675999999999998</v>
       </c>
       <c r="H42" s="15">
         <f t="shared" si="4"/>
-        <v>20.184000000000001</v>
+        <v>16.887</v>
       </c>
       <c r="I42" s="16">
         <f t="shared" si="5"/>
-        <v>2.7909707724425887</v>
+        <v>2.5322429906542054</v>
       </c>
       <c r="J42" s="17"/>
     </row>
@@ -2116,31 +2116,31 @@
         <v>50</v>
       </c>
       <c r="B43" s="5">
-        <v>160.22</v>
+        <v>161.05000000000001</v>
       </c>
       <c r="C43" s="6">
-        <v>5695</v>
+        <v>6277</v>
       </c>
       <c r="D43" s="7">
-        <v>21390</v>
+        <v>21505</v>
       </c>
       <c r="E43" s="7">
-        <v>14636</v>
+        <v>14627</v>
       </c>
       <c r="F43" s="7">
-        <v>7303</v>
+        <v>7560</v>
       </c>
       <c r="G43" s="8">
         <f t="shared" si="3"/>
-        <v>21.39</v>
+        <v>21.504999999999999</v>
       </c>
       <c r="H43" s="8">
         <f t="shared" si="4"/>
-        <v>14.635999999999999</v>
+        <v>14.627000000000001</v>
       </c>
       <c r="I43" s="9">
         <f t="shared" si="5"/>
-        <v>2.9289333150759962</v>
+        <v>2.8445767195767195</v>
       </c>
       <c r="J43" s="10"/>
     </row>
@@ -2149,31 +2149,31 @@
         <v>51</v>
       </c>
       <c r="B44" s="12">
-        <v>36.369999999999997</v>
+        <v>40.19</v>
       </c>
       <c r="C44" s="13">
-        <v>3031</v>
+        <v>2657</v>
       </c>
       <c r="D44" s="14">
-        <v>21245</v>
+        <v>21328</v>
       </c>
       <c r="E44" s="14">
-        <v>19281</v>
+        <v>19769</v>
       </c>
       <c r="F44" s="14">
-        <v>10293</v>
+        <v>9367</v>
       </c>
       <c r="G44" s="15">
         <f t="shared" si="3"/>
-        <v>21.245000000000001</v>
+        <v>21.327999999999999</v>
       </c>
       <c r="H44" s="15">
         <f t="shared" si="4"/>
-        <v>19.280999999999999</v>
+        <v>19.768999999999998</v>
       </c>
       <c r="I44" s="16">
         <f t="shared" si="5"/>
-        <v>2.064024094044496</v>
+        <v>2.2769296466317925</v>
       </c>
       <c r="J44" s="17"/>
     </row>
@@ -2182,31 +2182,31 @@
         <v>52</v>
       </c>
       <c r="B45" s="5">
-        <v>204.97</v>
+        <v>33.869999999999997</v>
       </c>
       <c r="C45" s="6">
-        <v>6009</v>
+        <v>2414</v>
       </c>
       <c r="D45" s="7">
-        <v>20858</v>
+        <v>21104</v>
       </c>
       <c r="E45" s="7">
-        <v>17457</v>
+        <v>15393</v>
       </c>
       <c r="F45" s="7">
-        <v>9361</v>
+        <v>8238</v>
       </c>
       <c r="G45" s="8">
         <f t="shared" si="3"/>
-        <v>20.858000000000001</v>
+        <v>21.103999999999999</v>
       </c>
       <c r="H45" s="8">
         <f t="shared" si="4"/>
-        <v>17.457000000000001</v>
+        <v>15.393000000000001</v>
       </c>
       <c r="I45" s="9">
         <f t="shared" si="5"/>
-        <v>2.2281807499198805</v>
+        <v>2.5617868414663754</v>
       </c>
       <c r="J45" s="10"/>
     </row>
@@ -2215,97 +2215,97 @@
         <v>53</v>
       </c>
       <c r="B46" s="12">
-        <v>48.43</v>
+        <v>20.329999999999998</v>
       </c>
       <c r="C46" s="13">
-        <v>2895</v>
+        <v>1825</v>
       </c>
       <c r="D46" s="14">
-        <v>20670</v>
+        <v>20990</v>
       </c>
       <c r="E46" s="14">
-        <v>14636</v>
+        <v>20016</v>
       </c>
       <c r="F46" s="14">
-        <v>7306</v>
+        <v>13381</v>
       </c>
       <c r="G46" s="15">
         <f t="shared" si="3"/>
-        <v>20.67</v>
+        <v>20.99</v>
       </c>
       <c r="H46" s="15">
         <f t="shared" si="4"/>
-        <v>14.635999999999999</v>
+        <v>20.015999999999998</v>
       </c>
       <c r="I46" s="16">
         <f t="shared" si="5"/>
-        <v>2.8291814946619218</v>
+        <v>1.5686421044764964</v>
       </c>
       <c r="J46" s="17"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="19">
-        <v>190.66</v>
-      </c>
-      <c r="C47" s="20">
-        <v>7672</v>
-      </c>
-      <c r="D47" s="21">
-        <v>20271</v>
-      </c>
-      <c r="E47" s="21">
-        <v>14688</v>
-      </c>
-      <c r="F47" s="21">
-        <v>5896</v>
-      </c>
-      <c r="G47" s="22">
+      <c r="B47" s="5">
+        <v>82.03</v>
+      </c>
+      <c r="C47" s="6">
+        <v>3674</v>
+      </c>
+      <c r="D47" s="7">
+        <v>20920</v>
+      </c>
+      <c r="E47" s="7">
+        <v>17734</v>
+      </c>
+      <c r="F47" s="7">
+        <v>13042</v>
+      </c>
+      <c r="G47" s="8">
         <f t="shared" si="3"/>
-        <v>20.271000000000001</v>
-      </c>
-      <c r="H47" s="22">
+        <v>20.92</v>
+      </c>
+      <c r="H47" s="8">
         <f t="shared" si="4"/>
-        <v>14.688000000000001</v>
-      </c>
-      <c r="I47" s="23">
+        <v>17.734000000000002</v>
+      </c>
+      <c r="I47" s="9">
         <f t="shared" si="5"/>
-        <v>3.4380936227951153</v>
-      </c>
-      <c r="J47" s="24"/>
+        <v>1.6040484588253336</v>
+      </c>
+      <c r="J47" s="10"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B48" s="12">
-        <v>24.59</v>
+        <v>49.81</v>
       </c>
       <c r="C48" s="13">
-        <v>3289</v>
+        <v>3183</v>
       </c>
       <c r="D48" s="14">
-        <v>20261</v>
+        <v>20920</v>
       </c>
       <c r="E48" s="14">
-        <v>15487</v>
+        <v>18507</v>
       </c>
       <c r="F48" s="14">
-        <v>8560</v>
+        <v>12736</v>
       </c>
       <c r="G48" s="15">
         <f t="shared" si="3"/>
-        <v>20.260999999999999</v>
+        <v>20.92</v>
       </c>
       <c r="H48" s="15">
         <f t="shared" si="4"/>
-        <v>15.487</v>
+        <v>18.507000000000001</v>
       </c>
       <c r="I48" s="16">
         <f t="shared" si="5"/>
-        <v>2.3669392523364485</v>
+        <v>1.6425879396984924</v>
       </c>
       <c r="J48" s="17"/>
     </row>
@@ -2314,31 +2314,31 @@
         <v>56</v>
       </c>
       <c r="B49" s="5">
-        <v>40.19</v>
+        <v>43.21</v>
       </c>
       <c r="C49" s="6">
-        <v>2657</v>
+        <v>2710</v>
       </c>
       <c r="D49" s="7">
-        <v>20142</v>
+        <v>20728</v>
       </c>
       <c r="E49" s="7">
-        <v>18355</v>
+        <v>18872</v>
       </c>
       <c r="F49" s="7">
-        <v>9367</v>
+        <v>9510</v>
       </c>
       <c r="G49" s="8">
         <f t="shared" si="3"/>
-        <v>20.141999999999999</v>
+        <v>20.728000000000002</v>
       </c>
       <c r="H49" s="8">
         <f t="shared" si="4"/>
-        <v>18.355</v>
+        <v>18.872</v>
       </c>
       <c r="I49" s="9">
         <f t="shared" si="5"/>
-        <v>2.1503149354115512</v>
+        <v>2.1796004206098845</v>
       </c>
       <c r="J49" s="10"/>
     </row>
@@ -2347,31 +2347,31 @@
         <v>57</v>
       </c>
       <c r="B50" s="12">
-        <v>161.05000000000001</v>
+        <v>48.43</v>
       </c>
       <c r="C50" s="13">
-        <v>6277</v>
+        <v>2895</v>
       </c>
       <c r="D50" s="14">
-        <v>20090</v>
+        <v>19229</v>
       </c>
       <c r="E50" s="14">
-        <v>14627</v>
+        <v>14636</v>
       </c>
       <c r="F50" s="14">
-        <v>7560</v>
+        <v>7306</v>
       </c>
       <c r="G50" s="15">
         <f t="shared" si="3"/>
-        <v>20.09</v>
+        <v>19.228999999999999</v>
       </c>
       <c r="H50" s="15">
         <f t="shared" si="4"/>
-        <v>14.627000000000001</v>
+        <v>14.635999999999999</v>
       </c>
       <c r="I50" s="16">
         <f t="shared" si="5"/>
-        <v>2.6574074074074074</v>
+        <v>2.6319463454694771</v>
       </c>
       <c r="J50" s="17"/>
     </row>
@@ -2380,31 +2380,31 @@
         <v>58</v>
       </c>
       <c r="B51" s="5">
-        <v>33.869999999999997</v>
+        <v>30.09</v>
       </c>
       <c r="C51" s="6">
-        <v>2414</v>
+        <v>3233</v>
       </c>
       <c r="D51" s="7">
-        <v>19530</v>
+        <v>19077</v>
       </c>
       <c r="E51" s="7">
-        <v>17807</v>
+        <v>16887</v>
       </c>
       <c r="F51" s="7">
-        <v>8238</v>
+        <v>8180</v>
       </c>
       <c r="G51" s="8">
         <f t="shared" si="3"/>
-        <v>19.53</v>
+        <v>19.077000000000002</v>
       </c>
       <c r="H51" s="8">
         <f t="shared" si="4"/>
-        <v>17.806999999999999</v>
+        <v>16.887</v>
       </c>
       <c r="I51" s="9">
         <f t="shared" si="5"/>
-        <v>2.3707210487982522</v>
+        <v>2.3321515892420539</v>
       </c>
       <c r="J51" s="10"/>
     </row>
@@ -2413,31 +2413,31 @@
         <v>59</v>
       </c>
       <c r="B52" s="12">
-        <v>43.21</v>
+        <v>26.89</v>
       </c>
       <c r="C52" s="13">
-        <v>2710</v>
+        <v>2114</v>
       </c>
       <c r="D52" s="14">
-        <v>19313</v>
+        <v>17148</v>
       </c>
       <c r="E52" s="14">
-        <v>17457</v>
+        <v>15942</v>
       </c>
       <c r="F52" s="14">
-        <v>9510</v>
+        <v>7664</v>
       </c>
       <c r="G52" s="15">
         <f t="shared" si="3"/>
-        <v>19.312999999999999</v>
+        <v>17.148</v>
       </c>
       <c r="H52" s="15">
         <f t="shared" si="4"/>
-        <v>17.457000000000001</v>
+        <v>15.942</v>
       </c>
       <c r="I52" s="16">
         <f t="shared" si="5"/>
-        <v>2.0308096740273398</v>
+        <v>2.2374739039665972</v>
       </c>
       <c r="J52" s="17"/>
     </row>
@@ -2446,31 +2446,31 @@
         <v>60</v>
       </c>
       <c r="B53" s="19">
-        <v>46.34</v>
+        <v>36.46</v>
       </c>
       <c r="C53" s="20">
-        <v>2872</v>
+        <v>2605</v>
       </c>
       <c r="D53" s="21">
-        <v>18767</v>
+        <v>13582</v>
       </c>
       <c r="E53" s="21">
-        <v>7196</v>
+        <v>10484</v>
       </c>
       <c r="F53" s="21">
-        <v>5202</v>
+        <v>3603</v>
       </c>
       <c r="G53" s="22">
         <f t="shared" si="3"/>
-        <v>18.766999999999999</v>
+        <v>13.582000000000001</v>
       </c>
       <c r="H53" s="22">
         <f t="shared" si="4"/>
-        <v>7.1959999999999997</v>
+        <v>10.484</v>
       </c>
       <c r="I53" s="23">
         <f t="shared" si="5"/>
-        <v>3.6076509034986546</v>
+        <v>3.7696364140993617</v>
       </c>
       <c r="J53" s="24"/>
     </row>
@@ -2479,31 +2479,31 @@
         <v>61</v>
       </c>
       <c r="B54" s="12">
-        <v>30.09</v>
+        <v>190.66</v>
       </c>
       <c r="C54" s="13">
-        <v>3233</v>
+        <v>7672</v>
       </c>
       <c r="D54" s="14">
-        <v>17676</v>
+        <v>13441</v>
       </c>
       <c r="E54" s="14">
-        <v>15487</v>
+        <v>8605</v>
       </c>
       <c r="F54" s="14">
-        <v>8180</v>
+        <v>5896</v>
       </c>
       <c r="G54" s="15">
         <f t="shared" si="3"/>
-        <v>17.675999999999998</v>
+        <v>13.441000000000001</v>
       </c>
       <c r="H54" s="15">
         <f t="shared" si="4"/>
-        <v>15.487</v>
+        <v>8.6050000000000004</v>
       </c>
       <c r="I54" s="16">
         <f t="shared" si="5"/>
-        <v>2.160880195599022</v>
+        <v>2.2796811397557666</v>
       </c>
       <c r="J54" s="17"/>
     </row>
@@ -2512,31 +2512,31 @@
         <v>62</v>
       </c>
       <c r="B55" s="19">
-        <v>40.44</v>
+        <v>33.869999999999997</v>
       </c>
       <c r="C55" s="20">
-        <v>2957</v>
+        <v>2696</v>
       </c>
       <c r="D55" s="21">
-        <v>14536</v>
+        <v>13311</v>
       </c>
       <c r="E55" s="21">
-        <v>11876</v>
+        <v>11507</v>
       </c>
       <c r="F55" s="21">
-        <v>2698</v>
+        <v>3966</v>
       </c>
       <c r="G55" s="22">
         <f t="shared" si="3"/>
-        <v>14.536</v>
+        <v>13.311</v>
       </c>
       <c r="H55" s="22">
         <f t="shared" si="4"/>
-        <v>11.875999999999999</v>
+        <v>11.507</v>
       </c>
       <c r="I55" s="23">
         <f t="shared" si="5"/>
-        <v>5.3876945885841367</v>
+        <v>3.3562783661119515</v>
       </c>
       <c r="J55" s="24"/>
     </row>
@@ -2545,31 +2545,31 @@
         <v>63</v>
       </c>
       <c r="B56" s="19">
-        <v>36.46</v>
+        <v>41.44</v>
       </c>
       <c r="C56" s="20">
-        <v>2605</v>
+        <v>2838</v>
       </c>
       <c r="D56" s="21">
-        <v>13780</v>
+        <v>12888</v>
       </c>
       <c r="E56" s="21">
-        <v>11508</v>
+        <v>11162</v>
       </c>
       <c r="F56" s="21">
-        <v>3603</v>
+        <v>4215</v>
       </c>
       <c r="G56" s="22">
         <f t="shared" si="3"/>
-        <v>13.78</v>
+        <v>12.888</v>
       </c>
       <c r="H56" s="22">
         <f t="shared" si="4"/>
-        <v>11.507999999999999</v>
+        <v>11.162000000000001</v>
       </c>
       <c r="I56" s="23">
         <f t="shared" si="5"/>
-        <v>3.8245906189286707</v>
+        <v>3.0576512455516016</v>
       </c>
       <c r="J56" s="24"/>
     </row>
@@ -2578,295 +2578,295 @@
         <v>64</v>
       </c>
       <c r="B57" s="19">
-        <v>33.869999999999997</v>
+        <v>3.24</v>
       </c>
       <c r="C57" s="20">
-        <v>2696</v>
+        <v>1056</v>
       </c>
       <c r="D57" s="21">
-        <v>13311</v>
+        <v>12251</v>
       </c>
       <c r="E57" s="21">
-        <v>11507</v>
+        <v>11025</v>
       </c>
       <c r="F57" s="21">
-        <v>3966</v>
+        <v>3969</v>
       </c>
       <c r="G57" s="22">
         <f t="shared" si="3"/>
-        <v>13.311</v>
+        <v>12.250999999999999</v>
       </c>
       <c r="H57" s="22">
         <f t="shared" si="4"/>
-        <v>11.507</v>
+        <v>11.025</v>
       </c>
       <c r="I57" s="23">
         <f t="shared" si="5"/>
-        <v>3.3562783661119515</v>
+        <v>3.0866717057193247</v>
       </c>
       <c r="J57" s="24"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B58" s="19">
-        <v>39.74</v>
-      </c>
-      <c r="C58" s="20">
-        <v>3355</v>
-      </c>
-      <c r="D58" s="21">
-        <v>13145</v>
-      </c>
-      <c r="E58" s="21">
-        <v>2075</v>
-      </c>
-      <c r="F58" s="21">
-        <v>1816</v>
-      </c>
-      <c r="G58" s="22">
+      <c r="B58" s="12">
+        <v>31.8</v>
+      </c>
+      <c r="C58" s="13">
+        <v>2339</v>
+      </c>
+      <c r="D58" s="14">
+        <v>11950</v>
+      </c>
+      <c r="E58" s="14">
+        <v>10412</v>
+      </c>
+      <c r="F58" s="14">
+        <v>4262</v>
+      </c>
+      <c r="G58" s="15">
         <f t="shared" si="3"/>
-        <v>13.145</v>
-      </c>
-      <c r="H58" s="22">
+        <v>11.95</v>
+      </c>
+      <c r="H58" s="15">
         <f t="shared" si="4"/>
-        <v>2.0750000000000002</v>
-      </c>
-      <c r="I58" s="23">
+        <v>10.412000000000001</v>
+      </c>
+      <c r="I58" s="16">
         <f t="shared" si="5"/>
-        <v>7.2384361233480172</v>
-      </c>
-      <c r="J58" s="24"/>
+        <v>2.8038479587048335</v>
+      </c>
+      <c r="J58" s="17"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="18" t="s">
+      <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B59" s="19">
-        <v>41.44</v>
-      </c>
-      <c r="C59" s="20">
-        <v>2838</v>
-      </c>
-      <c r="D59" s="21">
-        <v>12888</v>
-      </c>
-      <c r="E59" s="21">
-        <v>11162</v>
-      </c>
-      <c r="F59" s="21">
-        <v>4215</v>
-      </c>
-      <c r="G59" s="22">
+      <c r="B59" s="5">
+        <v>189.65</v>
+      </c>
+      <c r="C59" s="6">
+        <v>6663</v>
+      </c>
+      <c r="D59" s="7">
+        <v>11895</v>
+      </c>
+      <c r="E59" s="7">
+        <v>6633</v>
+      </c>
+      <c r="F59" s="7">
+        <v>5929</v>
+      </c>
+      <c r="G59" s="8">
         <f t="shared" si="3"/>
-        <v>12.888</v>
-      </c>
-      <c r="H59" s="22">
+        <v>11.895</v>
+      </c>
+      <c r="H59" s="8">
         <f t="shared" si="4"/>
-        <v>11.162000000000001</v>
-      </c>
-      <c r="I59" s="23">
+        <v>6.633</v>
+      </c>
+      <c r="I59" s="9">
         <f t="shared" si="5"/>
-        <v>3.0576512455516016</v>
-      </c>
-      <c r="J59" s="24"/>
+        <v>2.0062405127340193</v>
+      </c>
+      <c r="J59" s="10"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B60" s="19">
-        <v>3.24</v>
-      </c>
-      <c r="C60" s="20">
-        <v>1056</v>
-      </c>
-      <c r="D60" s="21">
-        <v>12251</v>
-      </c>
-      <c r="E60" s="21">
-        <v>11025</v>
-      </c>
-      <c r="F60" s="21">
-        <v>3969</v>
-      </c>
-      <c r="G60" s="22">
+      <c r="B60" s="12">
+        <v>303.58</v>
+      </c>
+      <c r="C60" s="13">
+        <v>7626</v>
+      </c>
+      <c r="D60" s="14">
+        <v>11692</v>
+      </c>
+      <c r="E60" s="14">
+        <v>6784</v>
+      </c>
+      <c r="F60" s="14">
+        <v>6059</v>
+      </c>
+      <c r="G60" s="15">
         <f t="shared" si="3"/>
-        <v>12.250999999999999</v>
-      </c>
-      <c r="H60" s="22">
+        <v>11.692</v>
+      </c>
+      <c r="H60" s="15">
         <f t="shared" si="4"/>
-        <v>11.025</v>
-      </c>
-      <c r="I60" s="23">
+        <v>6.7839999999999998</v>
+      </c>
+      <c r="I60" s="16">
         <f t="shared" si="5"/>
-        <v>3.0866717057193247</v>
-      </c>
-      <c r="J60" s="24"/>
+        <v>1.9296913682125763</v>
+      </c>
+      <c r="J60" s="17"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
         <v>68</v>
       </c>
       <c r="B61" s="19">
-        <v>172.75</v>
+        <v>159.81</v>
       </c>
       <c r="C61" s="20">
-        <v>5905</v>
+        <v>5989</v>
       </c>
       <c r="D61" s="21">
-        <v>11968</v>
+        <v>11676</v>
       </c>
       <c r="E61" s="21">
-        <v>6680</v>
+        <v>3270</v>
       </c>
       <c r="F61" s="21">
-        <v>2656</v>
+        <v>623</v>
       </c>
       <c r="G61" s="22">
         <f t="shared" si="3"/>
-        <v>11.968</v>
+        <v>11.676</v>
       </c>
       <c r="H61" s="22">
         <f t="shared" si="4"/>
-        <v>6.68</v>
+        <v>3.27</v>
       </c>
       <c r="I61" s="23">
         <f t="shared" si="5"/>
-        <v>4.5060240963855422</v>
+        <v>18.741573033707866</v>
       </c>
       <c r="J61" s="24"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="12">
-        <v>31.8</v>
-      </c>
-      <c r="C62" s="13">
-        <v>2339</v>
-      </c>
-      <c r="D62" s="14">
-        <v>11950</v>
-      </c>
-      <c r="E62" s="14">
-        <v>10412</v>
-      </c>
-      <c r="F62" s="14">
-        <v>4262</v>
-      </c>
-      <c r="G62" s="15">
+      <c r="B62" s="19">
+        <v>72.52</v>
+      </c>
+      <c r="C62" s="20">
+        <v>3558</v>
+      </c>
+      <c r="D62" s="21">
+        <v>11672</v>
+      </c>
+      <c r="E62" s="21">
+        <v>8228</v>
+      </c>
+      <c r="F62" s="21">
+        <v>1840</v>
+      </c>
+      <c r="G62" s="22">
         <f t="shared" si="3"/>
-        <v>11.95</v>
-      </c>
-      <c r="H62" s="15">
+        <v>11.672000000000001</v>
+      </c>
+      <c r="H62" s="22">
         <f t="shared" si="4"/>
-        <v>10.412000000000001</v>
-      </c>
-      <c r="I62" s="16">
+        <v>8.2279999999999998</v>
+      </c>
+      <c r="I62" s="23">
         <f t="shared" si="5"/>
-        <v>2.8038479587048335</v>
-      </c>
-      <c r="J62" s="17"/>
+        <v>6.3434782608695652</v>
+      </c>
+      <c r="J62" s="24"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B63" s="5">
-        <v>189.65</v>
-      </c>
-      <c r="C63" s="6">
-        <v>6663</v>
-      </c>
-      <c r="D63" s="7">
-        <v>11895</v>
-      </c>
-      <c r="E63" s="7">
-        <v>6606</v>
-      </c>
-      <c r="F63" s="7">
-        <v>5929</v>
-      </c>
-      <c r="G63" s="8">
+      <c r="B63" s="19">
+        <v>286.07</v>
+      </c>
+      <c r="C63" s="20">
+        <v>6866</v>
+      </c>
+      <c r="D63" s="21">
+        <v>11368</v>
+      </c>
+      <c r="E63" s="21">
+        <v>5235</v>
+      </c>
+      <c r="F63" s="21">
+        <v>2661</v>
+      </c>
+      <c r="G63" s="22">
         <f t="shared" si="3"/>
-        <v>11.895</v>
-      </c>
-      <c r="H63" s="8">
+        <v>11.368</v>
+      </c>
+      <c r="H63" s="22">
         <f t="shared" si="4"/>
-        <v>6.6059999999999999</v>
-      </c>
-      <c r="I63" s="9">
+        <v>5.2350000000000003</v>
+      </c>
+      <c r="I63" s="23">
         <f t="shared" si="5"/>
-        <v>2.0062405127340193</v>
-      </c>
-      <c r="J63" s="10"/>
+        <v>4.2720781661029692</v>
+      </c>
+      <c r="J63" s="24"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B64" s="12">
-        <v>303.58</v>
-      </c>
-      <c r="C64" s="13">
-        <v>7626</v>
-      </c>
-      <c r="D64" s="14">
-        <v>11692</v>
-      </c>
-      <c r="E64" s="14">
-        <v>6784</v>
-      </c>
-      <c r="F64" s="14">
-        <v>6059</v>
-      </c>
-      <c r="G64" s="15">
+      <c r="B64" s="19">
+        <v>49.08</v>
+      </c>
+      <c r="C64" s="20">
+        <v>3023</v>
+      </c>
+      <c r="D64" s="21">
+        <v>11350</v>
+      </c>
+      <c r="E64" s="21">
+        <v>9910</v>
+      </c>
+      <c r="F64" s="21">
+        <v>3629</v>
+      </c>
+      <c r="G64" s="22">
         <f t="shared" si="3"/>
-        <v>11.692</v>
-      </c>
-      <c r="H64" s="15">
+        <v>11.35</v>
+      </c>
+      <c r="H64" s="22">
         <f t="shared" si="4"/>
-        <v>6.7839999999999998</v>
-      </c>
-      <c r="I64" s="16">
+        <v>9.91</v>
+      </c>
+      <c r="I64" s="23">
         <f t="shared" si="5"/>
-        <v>1.9296913682125763</v>
-      </c>
-      <c r="J64" s="17"/>
+        <v>3.1275833562965003</v>
+      </c>
+      <c r="J64" s="24"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
         <v>72</v>
       </c>
       <c r="B65" s="19">
-        <v>49.08</v>
+        <v>40.44</v>
       </c>
       <c r="C65" s="20">
-        <v>3023</v>
+        <v>2957</v>
       </c>
       <c r="D65" s="21">
-        <v>11664</v>
+        <v>11286</v>
       </c>
       <c r="E65" s="21">
-        <v>9910</v>
+        <v>9890</v>
       </c>
       <c r="F65" s="21">
-        <v>3629</v>
+        <v>2698</v>
       </c>
       <c r="G65" s="22">
         <f t="shared" si="3"/>
-        <v>11.664</v>
+        <v>11.286</v>
       </c>
       <c r="H65" s="22">
         <f t="shared" si="4"/>
-        <v>9.91</v>
+        <v>9.89</v>
       </c>
       <c r="I65" s="23">
         <f t="shared" si="5"/>
-        <v>3.2141085698539542</v>
+        <v>4.183098591549296</v>
       </c>
       <c r="J65" s="24"/>
     </row>
@@ -2875,31 +2875,31 @@
         <v>73</v>
       </c>
       <c r="B66" s="19">
-        <v>286.07</v>
+        <v>172.75</v>
       </c>
       <c r="C66" s="20">
-        <v>6866</v>
+        <v>5905</v>
       </c>
       <c r="D66" s="21">
-        <v>10399</v>
+        <v>11112</v>
       </c>
       <c r="E66" s="21">
-        <v>5235</v>
+        <v>8708</v>
       </c>
       <c r="F66" s="21">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="G66" s="22">
         <f t="shared" si="3"/>
-        <v>10.398999999999999</v>
+        <v>11.112</v>
       </c>
       <c r="H66" s="22">
         <f t="shared" si="4"/>
-        <v>5.2350000000000003</v>
+        <v>8.7080000000000002</v>
       </c>
       <c r="I66" s="23">
         <f t="shared" si="5"/>
-        <v>3.9079293498684704</v>
+        <v>4.1837349397590362</v>
       </c>
       <c r="J66" s="24"/>
     </row>
@@ -2908,97 +2908,97 @@
         <v>74</v>
       </c>
       <c r="B67" s="19">
-        <v>72.52</v>
+        <v>39.74</v>
       </c>
       <c r="C67" s="20">
-        <v>3558</v>
+        <v>3355</v>
       </c>
       <c r="D67" s="21">
-        <v>7613</v>
+        <v>10475</v>
       </c>
       <c r="E67" s="21">
-        <v>2090</v>
+        <v>8192</v>
       </c>
       <c r="F67" s="21">
-        <v>1840</v>
+        <v>1816</v>
       </c>
       <c r="G67" s="22">
         <f t="shared" si="3"/>
-        <v>7.6130000000000004</v>
+        <v>10.475</v>
       </c>
       <c r="H67" s="22">
         <f t="shared" si="4"/>
-        <v>2.09</v>
+        <v>8.1920000000000002</v>
       </c>
       <c r="I67" s="23">
         <f t="shared" si="5"/>
-        <v>4.1375000000000002</v>
+        <v>5.768171806167401</v>
       </c>
       <c r="J67" s="24"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A68" s="18" t="s">
+      <c r="A68" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B68" s="19">
-        <v>93.41</v>
-      </c>
-      <c r="C68" s="20">
-        <v>4212</v>
-      </c>
-      <c r="D68" s="21">
-        <v>7190</v>
-      </c>
-      <c r="E68" s="21">
-        <v>720</v>
-      </c>
-      <c r="F68" s="21">
-        <v>539</v>
-      </c>
-      <c r="G68" s="22">
+      <c r="B68" s="12">
+        <v>46.34</v>
+      </c>
+      <c r="C68" s="13">
+        <v>2872</v>
+      </c>
+      <c r="D68" s="14">
+        <v>9323</v>
+      </c>
+      <c r="E68" s="14">
+        <v>7539</v>
+      </c>
+      <c r="F68" s="14">
+        <v>5202</v>
+      </c>
+      <c r="G68" s="15">
         <f t="shared" si="3"/>
-        <v>7.19</v>
-      </c>
-      <c r="H68" s="22">
+        <v>9.3230000000000004</v>
+      </c>
+      <c r="H68" s="15">
         <f t="shared" si="4"/>
-        <v>0.72</v>
-      </c>
-      <c r="I68" s="23">
+        <v>7.5389999999999997</v>
+      </c>
+      <c r="I68" s="16">
         <f t="shared" si="5"/>
-        <v>13.339517625231911</v>
-      </c>
-      <c r="J68" s="24"/>
+        <v>1.7921953094963476</v>
+      </c>
+      <c r="J68" s="17"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
         <v>76</v>
       </c>
       <c r="B69" s="19">
-        <v>159.81</v>
+        <v>93.41</v>
       </c>
       <c r="C69" s="20">
-        <v>5989</v>
+        <v>4212</v>
       </c>
       <c r="D69" s="21">
-        <v>6989</v>
+        <v>9273</v>
       </c>
       <c r="E69" s="21">
-        <v>788</v>
+        <v>4333</v>
       </c>
       <c r="F69" s="21">
-        <v>623</v>
+        <v>539</v>
       </c>
       <c r="G69" s="22">
         <f t="shared" ref="G69:G74" si="6">D69/1000</f>
-        <v>6.9889999999999999</v>
+        <v>9.2729999999999997</v>
       </c>
       <c r="H69" s="22">
         <f t="shared" ref="H69:H74" si="7">E69/1000</f>
-        <v>0.78800000000000003</v>
+        <v>4.3330000000000002</v>
       </c>
       <c r="I69" s="23">
         <f t="shared" ref="I69:I74" si="8">IFERROR(D69/F69,"")</f>
-        <v>11.218298555377206</v>
+        <v>17.204081632653061</v>
       </c>
       <c r="J69" s="24"/>
     </row>
@@ -3013,25 +3013,25 @@
         <v>7413</v>
       </c>
       <c r="D70" s="21">
-        <v>5546</v>
+        <v>9148</v>
       </c>
       <c r="E70" s="21">
-        <v>762</v>
+        <v>4725</v>
       </c>
       <c r="F70" s="21">
         <v>554</v>
       </c>
       <c r="G70" s="22">
         <f t="shared" si="6"/>
-        <v>5.5460000000000003</v>
+        <v>9.1479999999999997</v>
       </c>
       <c r="H70" s="22">
         <f t="shared" si="7"/>
-        <v>0.76200000000000001</v>
+        <v>4.7249999999999996</v>
       </c>
       <c r="I70" s="23">
         <f t="shared" si="8"/>
-        <v>10.010830324909747</v>
+        <v>16.512635379061372</v>
       </c>
       <c r="J70" s="24"/>
     </row>
@@ -3040,31 +3040,31 @@
         <v>78</v>
       </c>
       <c r="B71" s="19">
-        <v>110.29</v>
+        <v>30.12</v>
       </c>
       <c r="C71" s="20">
-        <v>5351</v>
+        <v>2592</v>
       </c>
       <c r="D71" s="21">
-        <v>4059</v>
+        <v>8857</v>
       </c>
       <c r="E71" s="21">
-        <v>172</v>
+        <v>7324</v>
       </c>
       <c r="F71" s="21">
-        <v>172</v>
+        <v>929</v>
       </c>
       <c r="G71" s="22">
         <f t="shared" si="6"/>
-        <v>4.0590000000000002</v>
+        <v>8.8569999999999993</v>
       </c>
       <c r="H71" s="22">
         <f t="shared" si="7"/>
-        <v>0.17199999999999999</v>
+        <v>7.3239999999999998</v>
       </c>
       <c r="I71" s="23">
         <f t="shared" si="8"/>
-        <v>23.598837209302324</v>
+        <v>9.5339074273412265</v>
       </c>
       <c r="J71" s="24"/>
     </row>
@@ -3079,7 +3079,7 @@
         <v>5228</v>
       </c>
       <c r="D72" s="21">
-        <v>4009</v>
+        <v>7078</v>
       </c>
       <c r="E72" s="21">
         <v>409</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="G72" s="22">
         <f t="shared" si="6"/>
-        <v>4.0090000000000003</v>
+        <v>7.0780000000000003</v>
       </c>
       <c r="H72" s="22">
         <f t="shared" si="7"/>
@@ -3097,42 +3097,42 @@
       </c>
       <c r="I72" s="23">
         <f t="shared" si="8"/>
-        <v>13.8719723183391</v>
+        <v>24.491349480968857</v>
       </c>
       <c r="J72" s="24"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="B73" s="5">
-        <v>30.12</v>
-      </c>
-      <c r="C73" s="6">
-        <v>2592</v>
-      </c>
-      <c r="D73" s="7">
-        <v>2394</v>
-      </c>
-      <c r="E73" s="7">
-        <v>1163</v>
-      </c>
-      <c r="F73" s="7">
-        <v>929</v>
-      </c>
-      <c r="G73" s="8">
+      <c r="B73" s="19">
+        <v>110.29</v>
+      </c>
+      <c r="C73" s="20">
+        <v>5351</v>
+      </c>
+      <c r="D73" s="21">
+        <v>5759</v>
+      </c>
+      <c r="E73" s="21">
+        <v>172</v>
+      </c>
+      <c r="F73" s="21">
+        <v>172</v>
+      </c>
+      <c r="G73" s="22">
         <f t="shared" si="6"/>
-        <v>2.3940000000000001</v>
-      </c>
-      <c r="H73" s="8">
+        <v>5.7590000000000003</v>
+      </c>
+      <c r="H73" s="22">
         <f t="shared" si="7"/>
-        <v>1.163</v>
-      </c>
-      <c r="I73" s="9">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="I73" s="23">
         <f t="shared" si="8"/>
-        <v>2.5769644779332617</v>
-      </c>
-      <c r="J73" s="10"/>
+        <v>33.482558139534881</v>
+      </c>
+      <c r="J73" s="24"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="18" t="s">
@@ -3177,15 +3177,15 @@
       </c>
       <c r="D76" s="27">
         <f>MAX(D5:D74)</f>
-        <v>30800</v>
+        <v>32882</v>
       </c>
       <c r="G76" s="28">
         <f>IFERROR(MAX(G5:G74),"")</f>
-        <v>30.8</v>
+        <v>32.881999999999998</v>
       </c>
       <c r="I76" s="29">
         <f>IFERROR(AVERAGE(I5:I74),"")</f>
-        <v>3.4136765085522693</v>
+        <v>4.0430925720190487</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9B4500-C253-4A0D-BFA5-3EFB3752F42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5C9745-90A8-4EE5-8217-B82EBE607B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="108">
   <si>
     <t>FAZENDA TUCANO — distância dos talhões até a sede</t>
   </si>
@@ -99,85 +99,175 @@
     <t>T-38C</t>
   </si>
   <si>
+    <t>T-39B</t>
+  </si>
+  <si>
+    <t>T-35</t>
+  </si>
+  <si>
     <t>T-36A</t>
   </si>
   <si>
-    <t>T-39B</t>
+    <t>T-37</t>
+  </si>
+  <si>
+    <t>T-38A</t>
+  </si>
+  <si>
+    <t>T-38B</t>
+  </si>
+  <si>
+    <t>T-36B</t>
+  </si>
+  <si>
+    <t>T-34</t>
+  </si>
+  <si>
+    <t>T-36C</t>
+  </si>
+  <si>
+    <t>T-36</t>
+  </si>
+  <si>
+    <t>T-33</t>
+  </si>
+  <si>
+    <t>T-33A</t>
+  </si>
+  <si>
+    <t>T-33C</t>
+  </si>
+  <si>
+    <t>T-33F</t>
+  </si>
+  <si>
+    <t>T-33E</t>
+  </si>
+  <si>
+    <t>T-33B</t>
+  </si>
+  <si>
+    <t>T-33D</t>
+  </si>
+  <si>
+    <t>T-32A</t>
+  </si>
+  <si>
+    <t>T-32B</t>
+  </si>
+  <si>
+    <t>T-32C</t>
+  </si>
+  <si>
+    <t>T-27B</t>
+  </si>
+  <si>
+    <t>T-29D</t>
+  </si>
+  <si>
+    <t>T-29B</t>
+  </si>
+  <si>
+    <t>T-30A</t>
+  </si>
+  <si>
+    <t>T-30C</t>
+  </si>
+  <si>
+    <t>T-30D</t>
+  </si>
+  <si>
+    <t>T-29A</t>
+  </si>
+  <si>
+    <t>T-32</t>
+  </si>
+  <si>
+    <t>T-29C</t>
+  </si>
+  <si>
+    <t>T-26B</t>
+  </si>
+  <si>
+    <t>T-26C</t>
+  </si>
+  <si>
+    <t>T-30B</t>
+  </si>
+  <si>
+    <t>T-17</t>
+  </si>
+  <si>
+    <t>T-16</t>
+  </si>
+  <si>
+    <t>T-26A</t>
+  </si>
+  <si>
+    <t>T-27C</t>
+  </si>
+  <si>
+    <t>T-27D</t>
+  </si>
+  <si>
+    <t>T-21</t>
+  </si>
+  <si>
+    <t>T-27A</t>
   </si>
   <si>
     <t>T-41A</t>
   </si>
   <si>
-    <t>T-38A</t>
-  </si>
-  <si>
-    <t>T-32A</t>
-  </si>
-  <si>
-    <t>T-32B</t>
-  </si>
-  <si>
-    <t>T-38B</t>
-  </si>
-  <si>
-    <t>T-36B</t>
-  </si>
-  <si>
-    <t>T-33D</t>
-  </si>
-  <si>
-    <t>T-33F</t>
-  </si>
-  <si>
-    <t>T-36C</t>
-  </si>
-  <si>
-    <t>T-33</t>
-  </si>
-  <si>
-    <t>T-33B</t>
-  </si>
-  <si>
-    <t>T-34</t>
-  </si>
-  <si>
-    <t>T-33A</t>
-  </si>
-  <si>
-    <t>T-36</t>
-  </si>
-  <si>
-    <t>T-35</t>
-  </si>
-  <si>
-    <t>T-37</t>
-  </si>
-  <si>
-    <t>T-32</t>
+    <t>T-41B</t>
+  </si>
+  <si>
+    <t>T-10B</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-05C</t>
+  </si>
+  <si>
+    <t>T-05B</t>
+  </si>
+  <si>
+    <t>T-05A</t>
   </si>
   <si>
     <t>T-22</t>
   </si>
   <si>
-    <t>T-21</t>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
+    <t>T-08</t>
   </si>
   <si>
     <t>T-03</t>
   </si>
   <si>
+    <t>T-06A</t>
+  </si>
+  <si>
+    <t>T-07B</t>
+  </si>
+  <si>
     <t>T-02</t>
   </si>
   <si>
     <t>T-01</t>
   </si>
   <si>
-    <t>T-10B</t>
-  </si>
-  <si>
     <t>T-10</t>
   </si>
   <si>
-    <t>T-04</t>
+    <t>T-05D</t>
   </si>
   <si>
     <t>sem acesso</t>
@@ -189,103 +279,13 @@
     <t>sem estrada até este talhão</t>
   </si>
   <si>
-    <t>T-05A</t>
-  </si>
-  <si>
-    <t>T-05B</t>
-  </si>
-  <si>
-    <t>T-05C</t>
-  </si>
-  <si>
-    <t>T-05D</t>
-  </si>
-  <si>
-    <t>T-06A</t>
-  </si>
-  <si>
     <t>T-06B</t>
   </si>
   <si>
     <t>T-06C</t>
   </si>
   <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-07B</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>T-16</t>
-  </si>
-  <si>
-    <t>T-17</t>
-  </si>
-  <si>
-    <t>T-26A</t>
-  </si>
-  <si>
-    <t>T-26B</t>
-  </si>
-  <si>
-    <t>T-26C</t>
-  </si>
-  <si>
-    <t>T-27A</t>
-  </si>
-  <si>
-    <t>T-27B</t>
-  </si>
-  <si>
-    <t>T-27C</t>
-  </si>
-  <si>
-    <t>T-27D</t>
-  </si>
-  <si>
-    <t>T-29A</t>
-  </si>
-  <si>
-    <t>T-29B</t>
-  </si>
-  <si>
-    <t>T-29C</t>
-  </si>
-  <si>
-    <t>T-29D</t>
-  </si>
-  <si>
-    <t>T-30A</t>
-  </si>
-  <si>
-    <t>T-30B</t>
-  </si>
-  <si>
-    <t>T-30C</t>
-  </si>
-  <si>
-    <t>T-30D</t>
-  </si>
-  <si>
-    <t>T-32C</t>
-  </si>
-  <si>
-    <t>T-33C</t>
-  </si>
-  <si>
-    <t>T-33E</t>
-  </si>
-  <si>
     <t>T-40C</t>
-  </si>
-  <si>
-    <t>T-41B</t>
   </si>
   <si>
     <t>T-CON</t>
@@ -896,25 +896,25 @@
         <v>4267</v>
       </c>
       <c r="D5" s="7">
-        <v>33695</v>
+        <v>26906</v>
       </c>
       <c r="E5" s="7">
-        <v>33326</v>
+        <v>26537</v>
       </c>
       <c r="F5" s="7">
         <v>14390</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:G39" si="0">D5/1000</f>
-        <v>33.695</v>
+        <f t="shared" ref="G5:G36" si="0">D5/1000</f>
+        <v>26.905999999999999</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" ref="H5:H39" si="1">E5/1000</f>
-        <v>33.326000000000001</v>
+        <f t="shared" ref="H5:H36" si="1">E5/1000</f>
+        <v>26.536999999999999</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I5:I39" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.3415566365531619</v>
+        <f t="shared" ref="I5:I36" si="2">IFERROR(D5/F5,"")</f>
+        <v>1.8697706740792217</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -929,25 +929,25 @@
         <v>2148</v>
       </c>
       <c r="D6" s="14">
-        <v>33695</v>
+        <v>26906</v>
       </c>
       <c r="E6" s="14">
-        <v>32924</v>
+        <v>26135</v>
       </c>
       <c r="F6" s="14">
         <v>14710</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>33.695</v>
+        <v>26.905999999999999</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>32.923999999999999</v>
+        <v>26.135000000000002</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>2.2906186267845001</v>
+        <v>1.8290958531611148</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -962,25 +962,25 @@
         <v>2376</v>
       </c>
       <c r="D7" s="7">
-        <v>33480</v>
+        <v>26691</v>
       </c>
       <c r="E7" s="7">
-        <v>32135</v>
+        <v>25346</v>
       </c>
       <c r="F7" s="7">
         <v>15101</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>33.479999999999997</v>
+        <v>26.690999999999999</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>32.134999999999998</v>
+        <v>25.346</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>2.2170717171048273</v>
+        <v>1.7674988411363486</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -995,25 +995,25 @@
         <v>3658</v>
       </c>
       <c r="D8" s="14">
-        <v>33304</v>
+        <v>26515</v>
       </c>
       <c r="E8" s="14">
-        <v>32311</v>
+        <v>25521</v>
       </c>
       <c r="F8" s="14">
         <v>13732</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>33.304000000000002</v>
+        <v>26.515000000000001</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>32.311</v>
+        <v>25.521000000000001</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.4252840081561318</v>
+        <v>1.9308913486746286</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -1028,25 +1028,25 @@
         <v>2363</v>
       </c>
       <c r="D9" s="7">
-        <v>33128</v>
+        <v>26339</v>
       </c>
       <c r="E9" s="7">
-        <v>32949</v>
+        <v>26160</v>
       </c>
       <c r="F9" s="7">
         <v>14034</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>33.128</v>
+        <v>26.338999999999999</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>32.948999999999998</v>
+        <v>26.16</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>2.3605529428530709</v>
+        <v>1.8767992019381503</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -1061,25 +1061,25 @@
         <v>1858</v>
       </c>
       <c r="D10" s="14">
-        <v>32975</v>
+        <v>26186</v>
       </c>
       <c r="E10" s="14">
-        <v>32463</v>
+        <v>25673</v>
       </c>
       <c r="F10" s="14">
         <v>14553</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>32.975000000000001</v>
+        <v>26.186</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>32.463000000000001</v>
+        <v>25.672999999999998</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>2.2658558372844086</v>
+        <v>1.7993540850683707</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -1094,25 +1094,25 @@
         <v>4182</v>
       </c>
       <c r="D11" s="7">
-        <v>32814</v>
+        <v>26025</v>
       </c>
       <c r="E11" s="7">
-        <v>32546</v>
+        <v>25756</v>
       </c>
       <c r="F11" s="7">
         <v>15781</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>32.814</v>
+        <v>26.024999999999999</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>32.545999999999999</v>
+        <v>25.756</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>2.0793359102718458</v>
+        <v>1.6491350358025474</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1127,25 +1127,25 @@
         <v>4183</v>
       </c>
       <c r="D12" s="14">
-        <v>32598</v>
+        <v>25809</v>
       </c>
       <c r="E12" s="14">
-        <v>31369</v>
+        <v>24529</v>
       </c>
       <c r="F12" s="14">
         <v>15031</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>32.597999999999999</v>
+        <v>25.809000000000001</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>31.369</v>
+        <v>24.529</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>2.1687179828354735</v>
+        <v>1.7170514270507617</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1160,25 +1160,25 @@
         <v>2368</v>
       </c>
       <c r="D13" s="7">
-        <v>32437</v>
+        <v>25648</v>
       </c>
       <c r="E13" s="7">
-        <v>31624</v>
+        <v>24834</v>
       </c>
       <c r="F13" s="7">
         <v>14263</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>32.436999999999998</v>
+        <v>25.648</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>31.623999999999999</v>
+        <v>24.834</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>2.274205987520157</v>
+        <v>1.7982191684778799</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1187,31 +1187,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>36.89</v>
+        <v>27.21</v>
       </c>
       <c r="C14" s="13">
-        <v>2563</v>
+        <v>2143</v>
       </c>
       <c r="D14" s="14">
-        <v>32248</v>
+        <v>25397</v>
       </c>
       <c r="E14" s="14">
-        <v>30862</v>
+        <v>24865</v>
       </c>
       <c r="F14" s="14">
-        <v>14740</v>
+        <v>14837</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>32.247999999999998</v>
+        <v>25.396999999999998</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>30.861999999999998</v>
+        <v>24.864999999999998</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>2.1877883310719133</v>
+        <v>1.7117341780683426</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1220,31 +1220,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>27.21</v>
+        <v>240.66</v>
       </c>
       <c r="C15" s="6">
-        <v>2143</v>
+        <v>6211</v>
       </c>
       <c r="D15" s="7">
-        <v>32186</v>
+        <v>25219</v>
       </c>
       <c r="E15" s="7">
-        <v>31654</v>
+        <v>22104</v>
       </c>
       <c r="F15" s="7">
-        <v>14837</v>
+        <v>16499</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>32.186</v>
+        <v>25.219000000000001</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>31.654</v>
+        <v>22.103999999999999</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>2.1693064635708028</v>
+        <v>1.5285168798108977</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1253,31 +1253,31 @@
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>150.53</v>
+        <v>36.89</v>
       </c>
       <c r="C16" s="13">
-        <v>4897</v>
+        <v>2563</v>
       </c>
       <c r="D16" s="14">
-        <v>31941</v>
+        <v>25018</v>
       </c>
       <c r="E16" s="14">
-        <v>30829</v>
+        <v>24073</v>
       </c>
       <c r="F16" s="14">
-        <v>12769</v>
+        <v>14740</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>31.940999999999999</v>
+        <v>25.018000000000001</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>30.829000000000001</v>
+        <v>24.073</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>2.5014488213642414</v>
+        <v>1.6972862957937584</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1286,31 +1286,31 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>52.93</v>
+        <v>182.45</v>
       </c>
       <c r="C17" s="6">
-        <v>3201</v>
+        <v>5565</v>
       </c>
       <c r="D17" s="7">
-        <v>31624</v>
+        <v>24974</v>
       </c>
       <c r="E17" s="7">
-        <v>29907</v>
+        <v>23468</v>
       </c>
       <c r="F17" s="7">
-        <v>13857</v>
+        <v>15705</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>31.623999999999999</v>
+        <v>24.974</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>29.907</v>
+        <v>23.468</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.2821678574005917</v>
+        <v>1.5901942056669851</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1319,31 +1319,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>49.81</v>
+        <v>52.93</v>
       </c>
       <c r="C18" s="13">
-        <v>3183</v>
+        <v>3201</v>
       </c>
       <c r="D18" s="14">
-        <v>31436</v>
+        <v>24834</v>
       </c>
       <c r="E18" s="14">
-        <v>30210</v>
+        <v>23118</v>
       </c>
       <c r="F18" s="14">
-        <v>12736</v>
+        <v>13857</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>31.436</v>
+        <v>24.834</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>30.21</v>
+        <v>23.117999999999999</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>2.4682788944723617</v>
+        <v>1.7921628058021217</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1352,31 +1352,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>56.22</v>
+        <v>25.33</v>
       </c>
       <c r="C19" s="6">
-        <v>3219</v>
+        <v>2313</v>
       </c>
       <c r="D19" s="7">
-        <v>31436</v>
+        <v>24634</v>
       </c>
       <c r="E19" s="7">
-        <v>30358</v>
+        <v>23896</v>
       </c>
       <c r="F19" s="7">
-        <v>12386</v>
+        <v>14244</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>31.436</v>
+        <v>24.634</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>30.358000000000001</v>
+        <v>23.896000000000001</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>2.5380268044566447</v>
+        <v>1.7294299354114013</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1385,31 +1385,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>25.33</v>
+        <v>39.71</v>
       </c>
       <c r="C20" s="13">
-        <v>2313</v>
+        <v>2648</v>
       </c>
       <c r="D20" s="14">
-        <v>31423</v>
+        <v>24123</v>
       </c>
       <c r="E20" s="14">
-        <v>30685</v>
+        <v>23515</v>
       </c>
       <c r="F20" s="14">
-        <v>14244</v>
+        <v>14442</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>31.422999999999998</v>
+        <v>24.123000000000001</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>30.684999999999999</v>
+        <v>23.515000000000001</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>2.2060516708789666</v>
+        <v>1.6703365184877441</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1418,31 +1418,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>39.71</v>
+        <v>228.96</v>
       </c>
       <c r="C21" s="6">
-        <v>2648</v>
+        <v>6152</v>
       </c>
       <c r="D21" s="7">
-        <v>30912</v>
+        <v>23574</v>
       </c>
       <c r="E21" s="7">
-        <v>30304</v>
+        <v>20237</v>
       </c>
       <c r="F21" s="7">
-        <v>14442</v>
+        <v>15117</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>30.911999999999999</v>
+        <v>23.574000000000002</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>30.303999999999998</v>
+        <v>20.236999999999998</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>2.1404237640216035</v>
+        <v>1.5594363961103395</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1451,31 +1451,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>20.329999999999998</v>
+        <v>42.33</v>
       </c>
       <c r="C22" s="13">
-        <v>1825</v>
+        <v>3171</v>
       </c>
       <c r="D22" s="14">
-        <v>30421</v>
+        <v>23566</v>
       </c>
       <c r="E22" s="14">
-        <v>30182</v>
+        <v>21991</v>
       </c>
       <c r="F22" s="14">
-        <v>13381</v>
+        <v>14233</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>30.420999999999999</v>
+        <v>23.565999999999999</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>30.181999999999999</v>
+        <v>21.991</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>2.2734474254540018</v>
+        <v>1.6557296423803836</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1484,31 +1484,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>83.54</v>
+        <v>93.86</v>
       </c>
       <c r="C23" s="6">
-        <v>3934</v>
+        <v>4450</v>
       </c>
       <c r="D23" s="7">
-        <v>30421</v>
+        <v>23514</v>
       </c>
       <c r="E23" s="7">
-        <v>30210</v>
+        <v>21794</v>
       </c>
       <c r="F23" s="7">
-        <v>12932</v>
+        <v>14968</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>30.420999999999999</v>
+        <v>23.513999999999999</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>30.21</v>
+        <v>21.794</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>2.3523816888339004</v>
+        <v>1.570951362907536</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1517,31 +1517,31 @@
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>42.33</v>
+        <v>187.06</v>
       </c>
       <c r="C24" s="13">
-        <v>3171</v>
+        <v>5526</v>
       </c>
       <c r="D24" s="14">
-        <v>30355</v>
+        <v>23040</v>
       </c>
       <c r="E24" s="14">
-        <v>28781</v>
+        <v>20153</v>
       </c>
       <c r="F24" s="14">
-        <v>14233</v>
+        <v>13729</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>30.355</v>
+        <v>23.04</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>28.780999999999999</v>
+        <v>20.152999999999999</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>2.1327197358251948</v>
+        <v>1.6781994318595674</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1550,31 +1550,31 @@
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>187.06</v>
+        <v>28.72</v>
       </c>
       <c r="C25" s="6">
-        <v>5526</v>
+        <v>2599</v>
       </c>
       <c r="D25" s="7">
-        <v>30266</v>
+        <v>22206</v>
       </c>
       <c r="E25" s="7">
-        <v>28583</v>
+        <v>20654</v>
       </c>
       <c r="F25" s="7">
-        <v>13729</v>
+        <v>14141</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>30.265999999999998</v>
+        <v>22.206</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>28.582999999999998</v>
+        <v>20.654</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>2.2045305557578847</v>
+        <v>1.57032741673149</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1583,31 +1583,31 @@
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>28.89</v>
+        <v>17.32</v>
       </c>
       <c r="C26" s="13">
-        <v>2630</v>
+        <v>1739</v>
       </c>
       <c r="D26" s="14">
-        <v>30266</v>
+        <v>21429</v>
       </c>
       <c r="E26" s="14">
-        <v>29684</v>
+        <v>21082</v>
       </c>
       <c r="F26" s="14">
-        <v>13724</v>
+        <v>13605</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>30.265999999999998</v>
+        <v>21.428999999999998</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>29.684000000000001</v>
+        <v>21.082000000000001</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>2.2053337219469542</v>
+        <v>1.5750826901874311</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1616,31 +1616,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>228.96</v>
+        <v>83.54</v>
       </c>
       <c r="C27" s="6">
-        <v>6152</v>
+        <v>3934</v>
       </c>
       <c r="D27" s="7">
-        <v>29829</v>
+        <v>21429</v>
       </c>
       <c r="E27" s="7">
-        <v>26906</v>
+        <v>20186</v>
       </c>
       <c r="F27" s="7">
-        <v>15117</v>
+        <v>12932</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>29.829000000000001</v>
+        <v>21.428999999999998</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>26.905999999999999</v>
+        <v>20.186</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>1.9732089700337367</v>
+        <v>1.6570522734302506</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1649,31 +1649,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>28.72</v>
+        <v>25.66</v>
       </c>
       <c r="C28" s="13">
-        <v>2599</v>
+        <v>2270</v>
       </c>
       <c r="D28" s="14">
-        <v>29766</v>
+        <v>21119</v>
       </c>
       <c r="E28" s="14">
-        <v>28604</v>
+        <v>20212</v>
       </c>
       <c r="F28" s="14">
-        <v>14141</v>
+        <v>13030</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>29.765999999999998</v>
+        <v>21.119</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>28.603999999999999</v>
+        <v>20.212</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>2.104943073332862</v>
+        <v>1.6207981580966999</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1682,31 +1682,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>93.86</v>
+        <v>28.89</v>
       </c>
       <c r="C29" s="6">
-        <v>4450</v>
+        <v>2630</v>
       </c>
       <c r="D29" s="7">
-        <v>28833</v>
+        <v>20736</v>
       </c>
       <c r="E29" s="7">
-        <v>26906</v>
+        <v>20153</v>
       </c>
       <c r="F29" s="7">
-        <v>14968</v>
+        <v>13724</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>28.832999999999998</v>
+        <v>20.736000000000001</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>26.905999999999999</v>
+        <v>20.152999999999999</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.926309460181721</v>
+        <v>1.510929758088021</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1715,31 +1715,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>240.66</v>
+        <v>20.329999999999998</v>
       </c>
       <c r="C30" s="13">
-        <v>6211</v>
+        <v>1825</v>
       </c>
       <c r="D30" s="14">
-        <v>26951</v>
+        <v>20237</v>
       </c>
       <c r="E30" s="14">
-        <v>22079</v>
+        <v>19999</v>
       </c>
       <c r="F30" s="14">
-        <v>16499</v>
+        <v>13381</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>26.951000000000001</v>
+        <v>20.236999999999998</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>22.079000000000001</v>
+        <v>19.998999999999999</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.633492938965998</v>
+        <v>1.5123682833868919</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1748,31 +1748,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>182.45</v>
+        <v>49.81</v>
       </c>
       <c r="C31" s="6">
-        <v>5565</v>
+        <v>3183</v>
       </c>
       <c r="D31" s="7">
-        <v>26951</v>
+        <v>20210</v>
       </c>
       <c r="E31" s="7">
-        <v>25446</v>
+        <v>18504</v>
       </c>
       <c r="F31" s="7">
-        <v>15705</v>
+        <v>12736</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>26.951000000000001</v>
+        <v>20.21</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>25.446000000000002</v>
+        <v>18.504000000000001</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.716077682266794</v>
+        <v>1.5868404522613064</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1781,31 +1781,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>82.03</v>
+        <v>56.22</v>
       </c>
       <c r="C32" s="13">
-        <v>3674</v>
+        <v>3219</v>
       </c>
       <c r="D32" s="14">
-        <v>18763</v>
+        <v>20061</v>
       </c>
       <c r="E32" s="14">
-        <v>17708</v>
+        <v>18953</v>
       </c>
       <c r="F32" s="14">
-        <v>13042</v>
+        <v>12386</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>18.763000000000002</v>
+        <v>20.061</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>17.707999999999998</v>
+        <v>18.952999999999999</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>1.4386597147676736</v>
+        <v>1.6196512191183594</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1814,31 +1814,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>303.58</v>
+        <v>73.53</v>
       </c>
       <c r="C33" s="6">
-        <v>7626</v>
+        <v>3551</v>
       </c>
       <c r="D33" s="7">
-        <v>10286</v>
+        <v>20050</v>
       </c>
       <c r="E33" s="7">
-        <v>6751</v>
+        <v>19497</v>
       </c>
       <c r="F33" s="7">
-        <v>6059</v>
+        <v>12059</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>10.286</v>
+        <v>20.05</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>6.7510000000000003</v>
+        <v>19.497</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.6976398745667602</v>
+        <v>1.6626585952400696</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1847,31 +1847,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>189.65</v>
+        <v>26.89</v>
       </c>
       <c r="C34" s="13">
-        <v>6663</v>
+        <v>2114</v>
       </c>
       <c r="D34" s="14">
-        <v>9595</v>
+        <v>19961</v>
       </c>
       <c r="E34" s="14">
-        <v>6565</v>
+        <v>19802</v>
       </c>
       <c r="F34" s="14">
-        <v>5929</v>
+        <v>7664</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>9.5950000000000006</v>
+        <v>19.960999999999999</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>6.5650000000000004</v>
+        <v>19.802</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.6183167481868781</v>
+        <v>2.6045146137787056</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1880,1156 +1880,1186 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>286.07</v>
+        <v>204.97</v>
       </c>
       <c r="C35" s="6">
-        <v>6866</v>
+        <v>6009</v>
       </c>
       <c r="D35" s="7">
-        <v>7297</v>
+        <v>19608</v>
       </c>
       <c r="E35" s="7">
-        <v>5218</v>
+        <v>16523</v>
       </c>
       <c r="F35" s="7">
-        <v>2661</v>
+        <v>9361</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>7.2969999999999997</v>
+        <v>19.608000000000001</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>5.218</v>
+        <v>16.523</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>2.7422021796317173</v>
+        <v>2.094648007691486</v>
       </c>
       <c r="J35" s="10"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="19">
-        <v>159.81</v>
-      </c>
-      <c r="C36" s="20">
-        <v>5989</v>
-      </c>
-      <c r="D36" s="21">
-        <v>5246</v>
-      </c>
-      <c r="E36" s="21">
-        <v>3236</v>
-      </c>
-      <c r="F36" s="21">
-        <v>623</v>
-      </c>
-      <c r="G36" s="22">
+      <c r="B36" s="12">
+        <v>51.46</v>
+      </c>
+      <c r="C36" s="13">
+        <v>3211</v>
+      </c>
+      <c r="D36" s="14">
+        <v>19538</v>
+      </c>
+      <c r="E36" s="14">
+        <v>18527</v>
+      </c>
+      <c r="F36" s="14">
+        <v>10413</v>
+      </c>
+      <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>5.2460000000000004</v>
-      </c>
-      <c r="H36" s="22">
+        <v>19.538</v>
+      </c>
+      <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>3.2360000000000002</v>
-      </c>
-      <c r="I36" s="23">
+        <v>18.527000000000001</v>
+      </c>
+      <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>8.4205457463884432</v>
-      </c>
-      <c r="J36" s="24"/>
+        <v>1.8763084605781235</v>
+      </c>
+      <c r="J36" s="17"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="19">
-        <v>110.29</v>
-      </c>
-      <c r="C37" s="20">
-        <v>5351</v>
-      </c>
-      <c r="D37" s="21">
-        <v>3236</v>
-      </c>
-      <c r="E37" s="21">
-        <v>590</v>
-      </c>
-      <c r="F37" s="21">
-        <v>172</v>
-      </c>
-      <c r="G37" s="22">
-        <f t="shared" si="0"/>
-        <v>3.2360000000000002</v>
-      </c>
-      <c r="H37" s="22">
-        <f t="shared" si="1"/>
-        <v>0.59</v>
-      </c>
-      <c r="I37" s="23">
-        <f t="shared" si="2"/>
-        <v>18.813953488372093</v>
-      </c>
-      <c r="J37" s="24"/>
+      <c r="B37" s="5">
+        <v>36.369999999999997</v>
+      </c>
+      <c r="C37" s="6">
+        <v>3031</v>
+      </c>
+      <c r="D37" s="7">
+        <v>19307</v>
+      </c>
+      <c r="E37" s="7">
+        <v>17451</v>
+      </c>
+      <c r="F37" s="7">
+        <v>10293</v>
+      </c>
+      <c r="G37" s="8">
+        <f t="shared" ref="G37:G69" si="3">D37/1000</f>
+        <v>19.306999999999999</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" ref="H37:H69" si="4">E37/1000</f>
+        <v>17.451000000000001</v>
+      </c>
+      <c r="I37" s="9">
+        <f t="shared" ref="I37:I69" si="5">IFERROR(D37/F37,"")</f>
+        <v>1.8757407947148548</v>
+      </c>
+      <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="19">
-        <v>127.8</v>
-      </c>
-      <c r="C38" s="20">
-        <v>5228</v>
-      </c>
-      <c r="D38" s="21">
-        <v>2270</v>
-      </c>
-      <c r="E38" s="21">
-        <v>1458</v>
-      </c>
-      <c r="F38" s="21">
-        <v>289</v>
-      </c>
-      <c r="G38" s="22">
-        <f t="shared" si="0"/>
-        <v>2.27</v>
-      </c>
-      <c r="H38" s="22">
-        <f t="shared" si="1"/>
-        <v>1.458</v>
-      </c>
-      <c r="I38" s="23">
-        <f t="shared" si="2"/>
-        <v>7.8546712802768166</v>
-      </c>
-      <c r="J38" s="24"/>
+      <c r="B38" s="12">
+        <v>135.69999999999999</v>
+      </c>
+      <c r="C38" s="13">
+        <v>5466</v>
+      </c>
+      <c r="D38" s="14">
+        <v>19307</v>
+      </c>
+      <c r="E38" s="14">
+        <v>16523</v>
+      </c>
+      <c r="F38" s="14">
+        <v>9364</v>
+      </c>
+      <c r="G38" s="15">
+        <f t="shared" si="3"/>
+        <v>19.306999999999999</v>
+      </c>
+      <c r="H38" s="15">
+        <f t="shared" si="4"/>
+        <v>16.523</v>
+      </c>
+      <c r="I38" s="16">
+        <f t="shared" si="5"/>
+        <v>2.0618325501922254</v>
+      </c>
+      <c r="J38" s="17"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="19">
-        <v>29.65</v>
-      </c>
-      <c r="C39" s="20">
-        <v>2527</v>
-      </c>
-      <c r="D39" s="21">
-        <v>1511</v>
-      </c>
-      <c r="E39" s="21">
-        <v>241</v>
-      </c>
-      <c r="F39" s="21">
-        <v>250</v>
-      </c>
-      <c r="G39" s="22">
-        <f t="shared" si="0"/>
-        <v>1.5109999999999999</v>
-      </c>
-      <c r="H39" s="22">
-        <f t="shared" si="1"/>
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="I39" s="23">
-        <f t="shared" si="2"/>
-        <v>6.0439999999999996</v>
-      </c>
-      <c r="J39" s="24"/>
+      <c r="B39" s="5">
+        <v>27.34</v>
+      </c>
+      <c r="C39" s="6">
+        <v>2417</v>
+      </c>
+      <c r="D39" s="7">
+        <v>19286</v>
+      </c>
+      <c r="E39" s="7">
+        <v>18213</v>
+      </c>
+      <c r="F39" s="7">
+        <v>10355</v>
+      </c>
+      <c r="G39" s="8">
+        <f t="shared" si="3"/>
+        <v>19.286000000000001</v>
+      </c>
+      <c r="H39" s="8">
+        <f t="shared" si="4"/>
+        <v>18.213000000000001</v>
+      </c>
+      <c r="I39" s="9">
+        <f t="shared" si="5"/>
+        <v>1.8624818928054081</v>
+      </c>
+      <c r="J39" s="10"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="19">
-        <v>172.75</v>
-      </c>
-      <c r="C40" s="20">
-        <v>5905</v>
-      </c>
-      <c r="D40" s="25" t="s">
+      <c r="B40" s="12">
+        <v>55.07</v>
+      </c>
+      <c r="C40" s="13">
+        <v>3294</v>
+      </c>
+      <c r="D40" s="14">
+        <v>19089</v>
+      </c>
+      <c r="E40" s="14">
+        <v>17502</v>
+      </c>
+      <c r="F40" s="14">
+        <v>10324</v>
+      </c>
+      <c r="G40" s="15">
+        <f t="shared" si="3"/>
+        <v>19.088999999999999</v>
+      </c>
+      <c r="H40" s="15">
+        <f t="shared" si="4"/>
+        <v>17.501999999999999</v>
+      </c>
+      <c r="I40" s="16">
+        <f t="shared" si="5"/>
+        <v>1.8489926385122046</v>
+      </c>
+      <c r="J40" s="17"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E40" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="21">
-        <v>2656</v>
-      </c>
-      <c r="G40" s="26" t="s">
+      <c r="B41" s="5">
+        <v>82.03</v>
+      </c>
+      <c r="C41" s="6">
+        <v>3674</v>
+      </c>
+      <c r="D41" s="7">
+        <v>18789</v>
+      </c>
+      <c r="E41" s="7">
+        <v>17734</v>
+      </c>
+      <c r="F41" s="7">
+        <v>13042</v>
+      </c>
+      <c r="G41" s="8">
+        <f t="shared" si="3"/>
+        <v>18.789000000000001</v>
+      </c>
+      <c r="H41" s="8">
+        <f t="shared" si="4"/>
+        <v>17.734000000000002</v>
+      </c>
+      <c r="I41" s="9">
+        <f t="shared" si="5"/>
+        <v>1.4406532740377243</v>
+      </c>
+      <c r="J41" s="10"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H40" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I40" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J40" s="28" t="s">
+      <c r="B42" s="12">
+        <v>43.21</v>
+      </c>
+      <c r="C42" s="13">
+        <v>2710</v>
+      </c>
+      <c r="D42" s="14">
+        <v>18577</v>
+      </c>
+      <c r="E42" s="14">
+        <v>17158</v>
+      </c>
+      <c r="F42" s="14">
+        <v>9510</v>
+      </c>
+      <c r="G42" s="15">
+        <f t="shared" si="3"/>
+        <v>18.577000000000002</v>
+      </c>
+      <c r="H42" s="15">
+        <f t="shared" si="4"/>
+        <v>17.158000000000001</v>
+      </c>
+      <c r="I42" s="16">
+        <f t="shared" si="5"/>
+        <v>1.9534174553101997</v>
+      </c>
+      <c r="J42" s="17"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="18" t="s">
+      <c r="B43" s="5">
+        <v>24.59</v>
+      </c>
+      <c r="C43" s="6">
+        <v>3289</v>
+      </c>
+      <c r="D43" s="7">
+        <v>18328</v>
+      </c>
+      <c r="E43" s="7">
+        <v>16878</v>
+      </c>
+      <c r="F43" s="7">
+        <v>8560</v>
+      </c>
+      <c r="G43" s="8">
+        <f t="shared" si="3"/>
+        <v>18.327999999999999</v>
+      </c>
+      <c r="H43" s="8">
+        <f t="shared" si="4"/>
+        <v>16.878</v>
+      </c>
+      <c r="I43" s="9">
+        <f t="shared" si="5"/>
+        <v>2.1411214953271029</v>
+      </c>
+      <c r="J43" s="10"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="19">
-        <v>49.08</v>
-      </c>
-      <c r="C41" s="20">
-        <v>3023</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E41" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" s="21">
-        <v>3629</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H41" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I41" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J41" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
+      <c r="B44" s="12">
+        <v>30.09</v>
+      </c>
+      <c r="C44" s="13">
+        <v>3233</v>
+      </c>
+      <c r="D44" s="14">
+        <v>18328</v>
+      </c>
+      <c r="E44" s="14">
+        <v>16878</v>
+      </c>
+      <c r="F44" s="14">
+        <v>8180</v>
+      </c>
+      <c r="G44" s="15">
+        <f t="shared" si="3"/>
+        <v>18.327999999999999</v>
+      </c>
+      <c r="H44" s="15">
+        <f t="shared" si="4"/>
+        <v>16.878</v>
+      </c>
+      <c r="I44" s="16">
+        <f t="shared" si="5"/>
+        <v>2.2405867970660145</v>
+      </c>
+      <c r="J44" s="17"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="19">
-        <v>31.8</v>
-      </c>
-      <c r="C42" s="20">
-        <v>2339</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E42" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F42" s="21">
-        <v>4262</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H42" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I42" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J42" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
+      <c r="B45" s="5">
+        <v>40.19</v>
+      </c>
+      <c r="C45" s="6">
+        <v>2657</v>
+      </c>
+      <c r="D45" s="7">
+        <v>17502</v>
+      </c>
+      <c r="E45" s="7">
+        <v>16523</v>
+      </c>
+      <c r="F45" s="7">
+        <v>9367</v>
+      </c>
+      <c r="G45" s="8">
+        <f t="shared" si="3"/>
+        <v>17.501999999999999</v>
+      </c>
+      <c r="H45" s="8">
+        <f t="shared" si="4"/>
+        <v>16.523</v>
+      </c>
+      <c r="I45" s="9">
+        <f t="shared" si="5"/>
+        <v>1.8684744315148927</v>
+      </c>
+      <c r="J45" s="10"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="19">
-        <v>41.44</v>
-      </c>
-      <c r="C43" s="20">
-        <v>2838</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E43" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F43" s="21">
-        <v>4215</v>
-      </c>
-      <c r="G43" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H43" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I43" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J43" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="19">
-        <v>33.869999999999997</v>
-      </c>
-      <c r="C44" s="20">
-        <v>2696</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="21">
-        <v>3966</v>
-      </c>
-      <c r="G44" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I44" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J44" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="19">
-        <v>39.74</v>
-      </c>
-      <c r="C45" s="20">
-        <v>3355</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E45" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F45" s="21">
-        <v>1816</v>
-      </c>
-      <c r="G45" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H45" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I45" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J45" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="19">
-        <v>40.44</v>
-      </c>
-      <c r="C46" s="20">
-        <v>2957</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="21">
-        <v>2698</v>
-      </c>
-      <c r="G46" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H46" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I46" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J46" s="28" t="s">
-        <v>50</v>
-      </c>
+      <c r="B46" s="12">
+        <v>190.66</v>
+      </c>
+      <c r="C46" s="13">
+        <v>7672</v>
+      </c>
+      <c r="D46" s="14">
+        <v>17200</v>
+      </c>
+      <c r="E46" s="14">
+        <v>14676</v>
+      </c>
+      <c r="F46" s="14">
+        <v>5896</v>
+      </c>
+      <c r="G46" s="15">
+        <f t="shared" si="3"/>
+        <v>17.2</v>
+      </c>
+      <c r="H46" s="15">
+        <f t="shared" si="4"/>
+        <v>14.676</v>
+      </c>
+      <c r="I46" s="16">
+        <f t="shared" si="5"/>
+        <v>2.9172320217096335</v>
+      </c>
+      <c r="J46" s="17"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="19">
+        <v>46.34</v>
+      </c>
+      <c r="C47" s="20">
+        <v>2872</v>
+      </c>
+      <c r="D47" s="21">
+        <v>16156</v>
+      </c>
+      <c r="E47" s="21">
+        <v>14600</v>
+      </c>
+      <c r="F47" s="21">
+        <v>5202</v>
+      </c>
+      <c r="G47" s="22">
+        <f t="shared" si="3"/>
+        <v>16.155999999999999</v>
+      </c>
+      <c r="H47" s="22">
+        <f t="shared" si="4"/>
+        <v>14.6</v>
+      </c>
+      <c r="I47" s="23">
+        <f t="shared" si="5"/>
+        <v>3.1057285659361784</v>
+      </c>
+      <c r="J47" s="24"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="12">
+        <v>161.05000000000001</v>
+      </c>
+      <c r="C48" s="13">
+        <v>6277</v>
+      </c>
+      <c r="D48" s="14">
+        <v>16043</v>
+      </c>
+      <c r="E48" s="14">
+        <v>14615</v>
+      </c>
+      <c r="F48" s="14">
+        <v>7560</v>
+      </c>
+      <c r="G48" s="15">
+        <f t="shared" si="3"/>
+        <v>16.042999999999999</v>
+      </c>
+      <c r="H48" s="15">
+        <f t="shared" si="4"/>
+        <v>14.615</v>
+      </c>
+      <c r="I48" s="16">
+        <f t="shared" si="5"/>
+        <v>2.1220899470899472</v>
+      </c>
+      <c r="J48" s="17"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="5">
+        <v>160.22</v>
+      </c>
+      <c r="C49" s="6">
+        <v>5695</v>
+      </c>
+      <c r="D49" s="7">
+        <v>16043</v>
+      </c>
+      <c r="E49" s="7">
+        <v>14615</v>
+      </c>
+      <c r="F49" s="7">
+        <v>7303</v>
+      </c>
+      <c r="G49" s="8">
+        <f t="shared" si="3"/>
+        <v>16.042999999999999</v>
+      </c>
+      <c r="H49" s="8">
+        <f t="shared" si="4"/>
+        <v>14.615</v>
+      </c>
+      <c r="I49" s="9">
+        <f t="shared" si="5"/>
+        <v>2.196768451321375</v>
+      </c>
+      <c r="J49" s="10"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B47" s="19">
-        <v>36.46</v>
-      </c>
-      <c r="C47" s="20">
-        <v>2605</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E47" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F47" s="21">
-        <v>3603</v>
-      </c>
-      <c r="G47" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H47" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I47" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J47" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
+      <c r="B50" s="12">
+        <v>33.869999999999997</v>
+      </c>
+      <c r="C50" s="13">
+        <v>2414</v>
+      </c>
+      <c r="D50" s="14">
+        <v>16043</v>
+      </c>
+      <c r="E50" s="14">
+        <v>15343</v>
+      </c>
+      <c r="F50" s="14">
+        <v>8238</v>
+      </c>
+      <c r="G50" s="15">
+        <f t="shared" si="3"/>
+        <v>16.042999999999999</v>
+      </c>
+      <c r="H50" s="15">
+        <f t="shared" si="4"/>
+        <v>15.343</v>
+      </c>
+      <c r="I50" s="16">
+        <f t="shared" si="5"/>
+        <v>1.9474386987132799</v>
+      </c>
+      <c r="J50" s="17"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B48" s="19">
-        <v>93.41</v>
-      </c>
-      <c r="C48" s="20">
-        <v>4212</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E48" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F48" s="21">
-        <v>539</v>
-      </c>
-      <c r="G48" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H48" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I48" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J48" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="18" t="s">
+      <c r="B51" s="5">
+        <v>189.65</v>
+      </c>
+      <c r="C51" s="6">
+        <v>6663</v>
+      </c>
+      <c r="D51" s="7">
+        <v>15433</v>
+      </c>
+      <c r="E51" s="7">
+        <v>11682</v>
+      </c>
+      <c r="F51" s="7">
+        <v>5929</v>
+      </c>
+      <c r="G51" s="8">
+        <f t="shared" si="3"/>
+        <v>15.433</v>
+      </c>
+      <c r="H51" s="8">
+        <f t="shared" si="4"/>
+        <v>11.682</v>
+      </c>
+      <c r="I51" s="9">
+        <f t="shared" si="5"/>
+        <v>2.6029684601113172</v>
+      </c>
+      <c r="J51" s="10"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="19">
-        <v>72.52</v>
-      </c>
-      <c r="C49" s="20">
-        <v>3558</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F49" s="21">
-        <v>1840</v>
-      </c>
-      <c r="G49" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H49" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I49" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J49" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="18" t="s">
+      <c r="B52" s="12">
+        <v>48.43</v>
+      </c>
+      <c r="C52" s="13">
+        <v>2895</v>
+      </c>
+      <c r="D52" s="14">
+        <v>15369</v>
+      </c>
+      <c r="E52" s="14">
+        <v>14615</v>
+      </c>
+      <c r="F52" s="14">
+        <v>7306</v>
+      </c>
+      <c r="G52" s="15">
+        <f t="shared" si="3"/>
+        <v>15.369</v>
+      </c>
+      <c r="H52" s="15">
+        <f t="shared" si="4"/>
+        <v>14.615</v>
+      </c>
+      <c r="I52" s="16">
+        <f t="shared" si="5"/>
+        <v>2.1036134683821515</v>
+      </c>
+      <c r="J52" s="17"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B50" s="19">
-        <v>30.12</v>
-      </c>
-      <c r="C50" s="20">
-        <v>2592</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F50" s="21">
-        <v>929</v>
-      </c>
-      <c r="G50" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H50" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I50" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J50" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="18" t="s">
+      <c r="B53" s="5">
+        <v>150.53</v>
+      </c>
+      <c r="C53" s="6">
+        <v>4897</v>
+      </c>
+      <c r="D53" s="7">
+        <v>14982</v>
+      </c>
+      <c r="E53" s="7">
+        <v>12772</v>
+      </c>
+      <c r="F53" s="7">
+        <v>12769</v>
+      </c>
+      <c r="G53" s="8">
+        <f t="shared" si="3"/>
+        <v>14.981999999999999</v>
+      </c>
+      <c r="H53" s="8">
+        <f t="shared" si="4"/>
+        <v>12.772</v>
+      </c>
+      <c r="I53" s="9">
+        <f t="shared" si="5"/>
+        <v>1.173310361030621</v>
+      </c>
+      <c r="J53" s="10"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B51" s="19">
-        <v>226.37</v>
-      </c>
-      <c r="C51" s="20">
-        <v>7413</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E51" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F51" s="21">
-        <v>554</v>
-      </c>
-      <c r="G51" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H51" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I51" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J51" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" s="19">
-        <v>46.34</v>
-      </c>
-      <c r="C52" s="20">
-        <v>2872</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E52" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F52" s="21">
-        <v>5202</v>
-      </c>
-      <c r="G52" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H52" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I52" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J52" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B53" s="19">
-        <v>190.66</v>
-      </c>
-      <c r="C53" s="20">
-        <v>7672</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E53" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F53" s="21">
-        <v>5896</v>
-      </c>
-      <c r="G53" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H53" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I53" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J53" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" s="19">
-        <v>161.05000000000001</v>
-      </c>
-      <c r="C54" s="20">
-        <v>6277</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E54" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F54" s="21">
-        <v>7560</v>
-      </c>
-      <c r="G54" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H54" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I54" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J54" s="28" t="s">
-        <v>50</v>
-      </c>
+      <c r="B54" s="12">
+        <v>38.03</v>
+      </c>
+      <c r="C54" s="13">
+        <v>2973</v>
+      </c>
+      <c r="D54" s="14">
+        <v>14154</v>
+      </c>
+      <c r="E54" s="14">
+        <v>13216</v>
+      </c>
+      <c r="F54" s="14">
+        <v>12971</v>
+      </c>
+      <c r="G54" s="15">
+        <f t="shared" si="3"/>
+        <v>14.154</v>
+      </c>
+      <c r="H54" s="15">
+        <f t="shared" si="4"/>
+        <v>13.215999999999999</v>
+      </c>
+      <c r="I54" s="16">
+        <f t="shared" si="5"/>
+        <v>1.0912034538586077</v>
+      </c>
+      <c r="J54" s="17"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B55" s="19">
-        <v>24.59</v>
+        <v>127.8</v>
       </c>
       <c r="C55" s="20">
-        <v>3289</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E55" s="25" t="s">
-        <v>48</v>
+        <v>5228</v>
+      </c>
+      <c r="D55" s="21">
+        <v>12637</v>
+      </c>
+      <c r="E55" s="21">
+        <v>9612</v>
       </c>
       <c r="F55" s="21">
-        <v>8560</v>
-      </c>
-      <c r="G55" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H55" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I55" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J55" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="G55" s="22">
+        <f t="shared" si="3"/>
+        <v>12.637</v>
+      </c>
+      <c r="H55" s="22">
+        <f t="shared" si="4"/>
+        <v>9.6120000000000001</v>
+      </c>
+      <c r="I55" s="23">
+        <f t="shared" si="5"/>
+        <v>43.726643598615915</v>
+      </c>
+      <c r="J55" s="24"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="19">
+        <v>226.37</v>
+      </c>
+      <c r="C56" s="20">
+        <v>7413</v>
+      </c>
+      <c r="D56" s="21">
+        <v>12059</v>
+      </c>
+      <c r="E56" s="21">
+        <v>9181</v>
+      </c>
+      <c r="F56" s="21">
+        <v>554</v>
+      </c>
+      <c r="G56" s="22">
+        <f t="shared" si="3"/>
+        <v>12.058999999999999</v>
+      </c>
+      <c r="H56" s="22">
+        <f t="shared" si="4"/>
+        <v>9.1809999999999992</v>
+      </c>
+      <c r="I56" s="23">
+        <f t="shared" si="5"/>
+        <v>21.767148014440433</v>
+      </c>
+      <c r="J56" s="24"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="5">
+        <v>41.44</v>
+      </c>
+      <c r="C57" s="6">
+        <v>2838</v>
+      </c>
+      <c r="D57" s="7">
+        <v>11834</v>
+      </c>
+      <c r="E57" s="7">
+        <v>11145</v>
+      </c>
+      <c r="F57" s="7">
+        <v>4215</v>
+      </c>
+      <c r="G57" s="8">
+        <f t="shared" si="3"/>
+        <v>11.834</v>
+      </c>
+      <c r="H57" s="8">
+        <f t="shared" si="4"/>
+        <v>11.145</v>
+      </c>
+      <c r="I57" s="9">
+        <f t="shared" si="5"/>
+        <v>2.8075919335705812</v>
+      </c>
+      <c r="J57" s="10"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="12">
+        <v>31.8</v>
+      </c>
+      <c r="C58" s="13">
+        <v>2339</v>
+      </c>
+      <c r="D58" s="14">
+        <v>11196</v>
+      </c>
+      <c r="E58" s="14">
+        <v>10394</v>
+      </c>
+      <c r="F58" s="14">
+        <v>4262</v>
+      </c>
+      <c r="G58" s="15">
+        <f t="shared" si="3"/>
+        <v>11.196</v>
+      </c>
+      <c r="H58" s="15">
+        <f t="shared" si="4"/>
+        <v>10.394</v>
+      </c>
+      <c r="I58" s="16">
+        <f t="shared" si="5"/>
+        <v>2.626935710933834</v>
+      </c>
+      <c r="J58" s="17"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="19">
-        <v>30.09</v>
-      </c>
-      <c r="C56" s="20">
-        <v>3233</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E56" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F56" s="21">
-        <v>8180</v>
-      </c>
-      <c r="G56" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H56" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I56" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J56" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="18" t="s">
+      <c r="B59" s="5">
+        <v>49.08</v>
+      </c>
+      <c r="C59" s="6">
+        <v>3023</v>
+      </c>
+      <c r="D59" s="7">
+        <v>10443</v>
+      </c>
+      <c r="E59" s="7">
+        <v>9891</v>
+      </c>
+      <c r="F59" s="7">
+        <v>3629</v>
+      </c>
+      <c r="G59" s="8">
+        <f t="shared" si="3"/>
+        <v>10.443</v>
+      </c>
+      <c r="H59" s="8">
+        <f t="shared" si="4"/>
+        <v>9.891</v>
+      </c>
+      <c r="I59" s="9">
+        <f t="shared" si="5"/>
+        <v>2.8776522457977403</v>
+      </c>
+      <c r="J59" s="10"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="19">
-        <v>48.43</v>
-      </c>
-      <c r="C57" s="20">
-        <v>2895</v>
-      </c>
-      <c r="D57" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E57" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F57" s="21">
-        <v>7306</v>
-      </c>
-      <c r="G57" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H57" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I57" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J57" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B58" s="19">
-        <v>26.89</v>
-      </c>
-      <c r="C58" s="20">
-        <v>2114</v>
-      </c>
-      <c r="D58" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E58" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F58" s="21">
-        <v>7664</v>
-      </c>
-      <c r="G58" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H58" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I58" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J58" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="19">
-        <v>160.22</v>
-      </c>
-      <c r="C59" s="20">
-        <v>5695</v>
-      </c>
-      <c r="D59" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E59" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F59" s="21">
-        <v>7303</v>
-      </c>
-      <c r="G59" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H59" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I59" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J59" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60" s="19">
-        <v>33.869999999999997</v>
-      </c>
-      <c r="C60" s="20">
-        <v>2414</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F60" s="21">
-        <v>8238</v>
-      </c>
-      <c r="G60" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H60" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I60" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J60" s="28" t="s">
-        <v>50</v>
-      </c>
+      <c r="B60" s="12">
+        <v>303.58</v>
+      </c>
+      <c r="C60" s="13">
+        <v>7626</v>
+      </c>
+      <c r="D60" s="14">
+        <v>10311</v>
+      </c>
+      <c r="E60" s="14">
+        <v>6777</v>
+      </c>
+      <c r="F60" s="14">
+        <v>6059</v>
+      </c>
+      <c r="G60" s="15">
+        <f t="shared" si="3"/>
+        <v>10.311</v>
+      </c>
+      <c r="H60" s="15">
+        <f t="shared" si="4"/>
+        <v>6.7770000000000001</v>
+      </c>
+      <c r="I60" s="16">
+        <f t="shared" si="5"/>
+        <v>1.7017659679815151</v>
+      </c>
+      <c r="J60" s="17"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B61" s="19">
-        <v>55.07</v>
+        <v>172.75</v>
       </c>
       <c r="C61" s="20">
-        <v>3294</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" s="25" t="s">
-        <v>48</v>
+        <v>5905</v>
+      </c>
+      <c r="D61" s="21">
+        <v>9916</v>
+      </c>
+      <c r="E61" s="21">
+        <v>6738</v>
       </c>
       <c r="F61" s="21">
-        <v>10324</v>
-      </c>
-      <c r="G61" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H61" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I61" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J61" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>2656</v>
+      </c>
+      <c r="G61" s="22">
+        <f t="shared" si="3"/>
+        <v>9.9160000000000004</v>
+      </c>
+      <c r="H61" s="22">
+        <f t="shared" si="4"/>
+        <v>6.7380000000000004</v>
+      </c>
+      <c r="I61" s="23">
+        <f t="shared" si="5"/>
+        <v>3.7334337349397591</v>
+      </c>
+      <c r="J61" s="24"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B62" s="19">
-        <v>51.46</v>
+        <v>93.41</v>
       </c>
       <c r="C62" s="20">
-        <v>3211</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62" s="25" t="s">
-        <v>48</v>
+        <v>4212</v>
+      </c>
+      <c r="D62" s="21">
+        <v>9612</v>
+      </c>
+      <c r="E62" s="21">
+        <v>8264</v>
       </c>
       <c r="F62" s="21">
-        <v>10413</v>
-      </c>
-      <c r="G62" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H62" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I62" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J62" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="G62" s="22">
+        <f t="shared" si="3"/>
+        <v>9.6120000000000001</v>
+      </c>
+      <c r="H62" s="22">
+        <f t="shared" si="4"/>
+        <v>8.2639999999999993</v>
+      </c>
+      <c r="I62" s="23">
+        <f t="shared" si="5"/>
+        <v>17.833024118738404</v>
+      </c>
+      <c r="J62" s="24"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B63" s="19">
-        <v>43.21</v>
+        <v>30.12</v>
       </c>
       <c r="C63" s="20">
-        <v>2710</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E63" s="25" t="s">
-        <v>48</v>
+        <v>2592</v>
+      </c>
+      <c r="D63" s="21">
+        <v>9477</v>
+      </c>
+      <c r="E63" s="21">
+        <v>8298</v>
       </c>
       <c r="F63" s="21">
-        <v>9510</v>
-      </c>
-      <c r="G63" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H63" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I63" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J63" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>929</v>
+      </c>
+      <c r="G63" s="22">
+        <f t="shared" si="3"/>
+        <v>9.4770000000000003</v>
+      </c>
+      <c r="H63" s="22">
+        <f t="shared" si="4"/>
+        <v>8.298</v>
+      </c>
+      <c r="I63" s="23">
+        <f t="shared" si="5"/>
+        <v>10.201291711517761</v>
+      </c>
+      <c r="J63" s="24"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B64" s="19">
-        <v>204.97</v>
+        <v>286.07</v>
       </c>
       <c r="C64" s="20">
-        <v>6009</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" s="25" t="s">
-        <v>48</v>
+        <v>6866</v>
+      </c>
+      <c r="D64" s="21">
+        <v>8739</v>
+      </c>
+      <c r="E64" s="21">
+        <v>5244</v>
       </c>
       <c r="F64" s="21">
-        <v>9361</v>
-      </c>
-      <c r="G64" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H64" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I64" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J64" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>2661</v>
+      </c>
+      <c r="G64" s="22">
+        <f t="shared" si="3"/>
+        <v>8.7390000000000008</v>
+      </c>
+      <c r="H64" s="22">
+        <f t="shared" si="4"/>
+        <v>5.2439999999999998</v>
+      </c>
+      <c r="I64" s="23">
+        <f t="shared" si="5"/>
+        <v>3.2841037204058625</v>
+      </c>
+      <c r="J64" s="24"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B65" s="19">
-        <v>36.369999999999997</v>
+        <v>39.74</v>
       </c>
       <c r="C65" s="20">
-        <v>3031</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E65" s="25" t="s">
-        <v>48</v>
+        <v>3355</v>
+      </c>
+      <c r="D65" s="21">
+        <v>8298</v>
+      </c>
+      <c r="E65" s="21">
+        <v>7284</v>
       </c>
       <c r="F65" s="21">
-        <v>10293</v>
-      </c>
-      <c r="G65" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H65" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I65" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J65" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>1816</v>
+      </c>
+      <c r="G65" s="22">
+        <f t="shared" si="3"/>
+        <v>8.298</v>
+      </c>
+      <c r="H65" s="22">
+        <f t="shared" si="4"/>
+        <v>7.2839999999999998</v>
+      </c>
+      <c r="I65" s="23">
+        <f t="shared" si="5"/>
+        <v>4.569383259911894</v>
+      </c>
+      <c r="J65" s="24"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B66" s="19">
-        <v>40.19</v>
+        <v>72.52</v>
       </c>
       <c r="C66" s="20">
-        <v>2657</v>
-      </c>
-      <c r="D66" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>48</v>
+        <v>3558</v>
+      </c>
+      <c r="D66" s="21">
+        <v>8298</v>
+      </c>
+      <c r="E66" s="21">
+        <v>6044</v>
       </c>
       <c r="F66" s="21">
-        <v>9367</v>
-      </c>
-      <c r="G66" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H66" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I66" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J66" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>1840</v>
+      </c>
+      <c r="G66" s="22">
+        <f t="shared" si="3"/>
+        <v>8.298</v>
+      </c>
+      <c r="H66" s="22">
+        <f t="shared" si="4"/>
+        <v>6.0439999999999996</v>
+      </c>
+      <c r="I66" s="23">
+        <f t="shared" si="5"/>
+        <v>4.5097826086956525</v>
+      </c>
+      <c r="J66" s="24"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B67" s="19">
-        <v>135.69999999999999</v>
+        <v>159.81</v>
       </c>
       <c r="C67" s="20">
-        <v>5466</v>
-      </c>
-      <c r="D67" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E67" s="25" t="s">
-        <v>48</v>
+        <v>5989</v>
+      </c>
+      <c r="D67" s="21">
+        <v>5271</v>
+      </c>
+      <c r="E67" s="21">
+        <v>3262</v>
       </c>
       <c r="F67" s="21">
-        <v>9364</v>
-      </c>
-      <c r="G67" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H67" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I67" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J67" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="G67" s="22">
+        <f t="shared" si="3"/>
+        <v>5.2709999999999999</v>
+      </c>
+      <c r="H67" s="22">
+        <f t="shared" si="4"/>
+        <v>3.262</v>
+      </c>
+      <c r="I67" s="23">
+        <f t="shared" si="5"/>
+        <v>8.4606741573033712</v>
+      </c>
+      <c r="J67" s="24"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B68" s="19">
-        <v>27.34</v>
+        <v>110.29</v>
       </c>
       <c r="C68" s="20">
-        <v>2417</v>
-      </c>
-      <c r="D68" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E68" s="25" t="s">
-        <v>48</v>
+        <v>5351</v>
+      </c>
+      <c r="D68" s="21">
+        <v>3262</v>
+      </c>
+      <c r="E68" s="21">
+        <v>616</v>
       </c>
       <c r="F68" s="21">
-        <v>10355</v>
-      </c>
-      <c r="G68" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H68" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I68" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J68" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G68" s="22">
+        <f t="shared" si="3"/>
+        <v>3.262</v>
+      </c>
+      <c r="H68" s="22">
+        <f t="shared" si="4"/>
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="I68" s="23">
+        <f t="shared" si="5"/>
+        <v>18.965116279069768</v>
+      </c>
+      <c r="J68" s="24"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B69" s="19">
-        <v>73.53</v>
+        <v>29.65</v>
       </c>
       <c r="C69" s="20">
-        <v>3551</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E69" s="25" t="s">
-        <v>48</v>
+        <v>2527</v>
+      </c>
+      <c r="D69" s="21">
+        <v>1536</v>
+      </c>
+      <c r="E69" s="21">
+        <v>266</v>
       </c>
       <c r="F69" s="21">
-        <v>12059</v>
-      </c>
-      <c r="G69" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H69" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I69" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J69" s="28" t="s">
-        <v>50</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G69" s="22">
+        <f t="shared" si="3"/>
+        <v>1.536</v>
+      </c>
+      <c r="H69" s="22">
+        <f t="shared" si="4"/>
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="I69" s="23">
+        <f t="shared" si="5"/>
+        <v>6.1440000000000001</v>
+      </c>
+      <c r="J69" s="24"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="19">
+        <v>33.869999999999997</v>
+      </c>
+      <c r="C70" s="20">
+        <v>2696</v>
+      </c>
+      <c r="D70" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="F70" s="21">
+        <v>3966</v>
+      </c>
+      <c r="G70" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H70" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="I70" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="J70" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="B70" s="19">
-        <v>17.32</v>
-      </c>
-      <c r="C70" s="20">
-        <v>1739</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E70" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F70" s="21">
-        <v>13605</v>
-      </c>
-      <c r="G70" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H70" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="I70" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="J70" s="28" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
@@ -3037,31 +3067,31 @@
         <v>81</v>
       </c>
       <c r="B71" s="19">
-        <v>25.66</v>
+        <v>40.44</v>
       </c>
       <c r="C71" s="20">
-        <v>2270</v>
+        <v>2957</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E71" s="25" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F71" s="21">
-        <v>13030</v>
+        <v>2698</v>
       </c>
       <c r="G71" s="26" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="I71" s="27" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="J71" s="28" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
@@ -3069,31 +3099,31 @@
         <v>82</v>
       </c>
       <c r="B72" s="19">
-        <v>39.65</v>
+        <v>36.46</v>
       </c>
       <c r="C72" s="20">
-        <v>2528</v>
+        <v>2605</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E72" s="25" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F72" s="21">
-        <v>13714</v>
+        <v>3603</v>
       </c>
       <c r="G72" s="26" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="I72" s="27" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="J72" s="28" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
@@ -3101,31 +3131,31 @@
         <v>83</v>
       </c>
       <c r="B73" s="19">
-        <v>38.03</v>
+        <v>39.65</v>
       </c>
       <c r="C73" s="20">
-        <v>2973</v>
+        <v>2528</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E73" s="25" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F73" s="21">
-        <v>12971</v>
+        <v>13714</v>
       </c>
       <c r="G73" s="26" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H73" s="26" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="I73" s="27" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="J73" s="28" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
@@ -3139,25 +3169,25 @@
         <v>1056</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E74" s="25" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F74" s="21">
         <v>3969</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="I74" s="27" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="J74" s="28" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
@@ -3166,19 +3196,19 @@
       </c>
       <c r="B76" s="30">
         <f>SUM(B5:B74)</f>
-        <v>5758.61</v>
+        <v>5758.6099999999988</v>
       </c>
       <c r="D76" s="31">
         <f>MAX(D5:D74)</f>
-        <v>33695</v>
+        <v>26906</v>
       </c>
       <c r="G76" s="32">
         <f>IFERROR(MAX(G5:G74),"")</f>
-        <v>33.695</v>
+        <v>26.905999999999999</v>
       </c>
       <c r="I76" s="33">
         <f>IFERROR(AVERAGE(I5:I74),"")</f>
-        <v>3.0876893297540038</v>
+        <v>3.770387308243587</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5C9745-90A8-4EE5-8217-B82EBE607B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ED30C4-DCCE-4B1A-AFD5-C9F75276A5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,6 +72,9 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-41A</t>
+  </si>
+  <si>
     <t>T-39</t>
   </si>
   <si>
@@ -96,19 +99,25 @@
     <t>T-37B</t>
   </si>
   <si>
+    <t>T-35</t>
+  </si>
+  <si>
     <t>T-38C</t>
   </si>
   <si>
+    <t>T-37</t>
+  </si>
+  <si>
     <t>T-39B</t>
   </si>
   <si>
-    <t>T-35</t>
-  </si>
-  <si>
     <t>T-36A</t>
   </si>
   <si>
-    <t>T-37</t>
+    <t>T-41B</t>
+  </si>
+  <si>
+    <t>T-36</t>
   </si>
   <si>
     <t>T-38A</t>
@@ -126,9 +135,6 @@
     <t>T-36C</t>
   </si>
   <si>
-    <t>T-36</t>
-  </si>
-  <si>
     <t>T-33</t>
   </si>
   <si>
@@ -141,12 +147,12 @@
     <t>T-33F</t>
   </si>
   <si>
+    <t>T-33B</t>
+  </si>
+  <si>
     <t>T-33E</t>
   </si>
   <si>
-    <t>T-33B</t>
-  </si>
-  <si>
     <t>T-33D</t>
   </si>
   <si>
@@ -159,94 +165,88 @@
     <t>T-32C</t>
   </si>
   <si>
+    <t>T-29B</t>
+  </si>
+  <si>
+    <t>T-29D</t>
+  </si>
+  <si>
+    <t>T-30A</t>
+  </si>
+  <si>
+    <t>T-30C</t>
+  </si>
+  <si>
+    <t>T-32</t>
+  </si>
+  <si>
+    <t>T-30D</t>
+  </si>
+  <si>
+    <t>T-29A</t>
+  </si>
+  <si>
+    <t>T-29C</t>
+  </si>
+  <si>
+    <t>T-30B</t>
+  </si>
+  <si>
+    <t>T-26B</t>
+  </si>
+  <si>
+    <t>T-26C</t>
+  </si>
+  <si>
     <t>T-27B</t>
   </si>
   <si>
-    <t>T-29D</t>
-  </si>
-  <si>
-    <t>T-29B</t>
-  </si>
-  <si>
-    <t>T-30A</t>
-  </si>
-  <si>
-    <t>T-30C</t>
-  </si>
-  <si>
-    <t>T-30D</t>
-  </si>
-  <si>
-    <t>T-29A</t>
-  </si>
-  <si>
-    <t>T-32</t>
-  </si>
-  <si>
-    <t>T-29C</t>
-  </si>
-  <si>
-    <t>T-26B</t>
-  </si>
-  <si>
-    <t>T-26C</t>
-  </si>
-  <si>
-    <t>T-30B</t>
+    <t>T-26A</t>
+  </si>
+  <si>
+    <t>T-27C</t>
+  </si>
+  <si>
+    <t>T-27D</t>
+  </si>
+  <si>
+    <t>T-27A</t>
   </si>
   <si>
     <t>T-17</t>
   </si>
   <si>
+    <t>T-05C</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-10B</t>
+  </si>
+  <si>
+    <t>T-05B</t>
+  </si>
+  <si>
+    <t>T-22</t>
+  </si>
+  <si>
+    <t>T-05A</t>
+  </si>
+  <si>
+    <t>T-21</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
     <t>T-16</t>
-  </si>
-  <si>
-    <t>T-26A</t>
-  </si>
-  <si>
-    <t>T-27C</t>
-  </si>
-  <si>
-    <t>T-27D</t>
-  </si>
-  <si>
-    <t>T-21</t>
-  </si>
-  <si>
-    <t>T-27A</t>
-  </si>
-  <si>
-    <t>T-41A</t>
-  </si>
-  <si>
-    <t>T-41B</t>
-  </si>
-  <si>
-    <t>T-10B</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>T-05C</t>
-  </si>
-  <si>
-    <t>T-05B</t>
-  </si>
-  <si>
-    <t>T-05A</t>
-  </si>
-  <si>
-    <t>T-22</t>
-  </si>
-  <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-08</t>
   </si>
   <si>
     <t>T-03</t>
@@ -890,31 +890,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>96.66</v>
+        <v>150.53</v>
       </c>
       <c r="C5" s="6">
-        <v>4267</v>
+        <v>4897</v>
       </c>
       <c r="D5" s="7">
-        <v>26906</v>
+        <v>27435</v>
       </c>
       <c r="E5" s="7">
-        <v>26537</v>
+        <v>23541</v>
       </c>
       <c r="F5" s="7">
-        <v>14390</v>
+        <v>12769</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G36" si="0">D5/1000</f>
-        <v>26.905999999999999</v>
+        <v>27.434999999999999</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H36" si="1">E5/1000</f>
-        <v>26.536999999999999</v>
+        <v>23.541</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I36" si="2">IFERROR(D5/F5,"")</f>
-        <v>1.8697706740792217</v>
+        <v>2.1485629258360093</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -923,31 +923,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>23.73</v>
+        <v>96.66</v>
       </c>
       <c r="C6" s="13">
-        <v>2148</v>
+        <v>4267</v>
       </c>
       <c r="D6" s="14">
-        <v>26906</v>
+        <v>26407</v>
       </c>
       <c r="E6" s="14">
-        <v>26135</v>
+        <v>26038</v>
       </c>
       <c r="F6" s="14">
-        <v>14710</v>
+        <v>14390</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>26.905999999999999</v>
+        <v>26.407</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>26.135000000000002</v>
+        <v>26.038</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>1.8290958531611148</v>
+        <v>1.8350938151494094</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -956,31 +956,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>34.07</v>
+        <v>23.73</v>
       </c>
       <c r="C7" s="6">
-        <v>2376</v>
+        <v>2148</v>
       </c>
       <c r="D7" s="7">
-        <v>26691</v>
+        <v>26407</v>
       </c>
       <c r="E7" s="7">
-        <v>25346</v>
+        <v>25636</v>
       </c>
       <c r="F7" s="7">
-        <v>15101</v>
+        <v>14710</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>26.690999999999999</v>
+        <v>26.407</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>25.346</v>
+        <v>25.635999999999999</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>1.7674988411363486</v>
+        <v>1.7951733514615908</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -989,31 +989,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="12">
-        <v>85.18</v>
+        <v>34.07</v>
       </c>
       <c r="C8" s="13">
-        <v>3658</v>
+        <v>2376</v>
       </c>
       <c r="D8" s="14">
-        <v>26515</v>
+        <v>26192</v>
       </c>
       <c r="E8" s="14">
-        <v>25521</v>
+        <v>24848</v>
       </c>
       <c r="F8" s="14">
-        <v>13732</v>
+        <v>15101</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>26.515000000000001</v>
+        <v>26.192</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>25.521000000000001</v>
+        <v>24.847999999999999</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>1.9308913486746286</v>
+        <v>1.7344546718760347</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -1022,31 +1022,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>31</v>
+        <v>85.18</v>
       </c>
       <c r="C9" s="6">
-        <v>2363</v>
+        <v>3658</v>
       </c>
       <c r="D9" s="7">
-        <v>26339</v>
+        <v>26016</v>
       </c>
       <c r="E9" s="7">
-        <v>26160</v>
+        <v>25022</v>
       </c>
       <c r="F9" s="7">
-        <v>14034</v>
+        <v>13732</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>26.338999999999999</v>
+        <v>26.015999999999998</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>26.16</v>
+        <v>25.021999999999998</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>1.8767992019381503</v>
+        <v>1.8945528692106031</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -1055,31 +1055,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="12">
-        <v>20.03</v>
+        <v>31</v>
       </c>
       <c r="C10" s="13">
-        <v>1858</v>
+        <v>2363</v>
       </c>
       <c r="D10" s="14">
-        <v>26186</v>
+        <v>25840</v>
       </c>
       <c r="E10" s="14">
-        <v>25673</v>
+        <v>25661</v>
       </c>
       <c r="F10" s="14">
-        <v>14553</v>
+        <v>14034</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>26.186</v>
+        <v>25.84</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>25.672999999999998</v>
+        <v>25.661000000000001</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.7993540850683707</v>
+        <v>1.8412426963089639</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -1088,31 +1088,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>85.99</v>
+        <v>20.03</v>
       </c>
       <c r="C11" s="6">
-        <v>4182</v>
+        <v>1858</v>
       </c>
       <c r="D11" s="7">
-        <v>26025</v>
+        <v>25687</v>
       </c>
       <c r="E11" s="7">
-        <v>25756</v>
+        <v>25174</v>
       </c>
       <c r="F11" s="7">
-        <v>15781</v>
+        <v>14553</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>26.024999999999999</v>
+        <v>25.687000000000001</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>25.756</v>
+        <v>25.173999999999999</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.6491350358025474</v>
+        <v>1.7650656222084793</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1121,31 +1121,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>108.01</v>
+        <v>85.99</v>
       </c>
       <c r="C12" s="13">
-        <v>4183</v>
+        <v>4182</v>
       </c>
       <c r="D12" s="14">
-        <v>25809</v>
+        <v>25525</v>
       </c>
       <c r="E12" s="14">
-        <v>24529</v>
+        <v>25269</v>
       </c>
       <c r="F12" s="14">
-        <v>15031</v>
+        <v>15781</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>25.809000000000001</v>
+        <v>25.524999999999999</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>24.529</v>
+        <v>25.268999999999998</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>1.7170514270507617</v>
+        <v>1.6174513655661873</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1154,31 +1154,31 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>27.75</v>
+        <v>108.01</v>
       </c>
       <c r="C13" s="6">
-        <v>2368</v>
+        <v>4183</v>
       </c>
       <c r="D13" s="7">
-        <v>25648</v>
+        <v>25298</v>
       </c>
       <c r="E13" s="7">
-        <v>24834</v>
+        <v>24081</v>
       </c>
       <c r="F13" s="7">
-        <v>14263</v>
+        <v>15031</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>25.648</v>
+        <v>25.297999999999998</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>24.834</v>
+        <v>24.081</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.7982191684778799</v>
+        <v>1.683055019626106</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1187,31 +1187,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>27.21</v>
+        <v>240.66</v>
       </c>
       <c r="C14" s="13">
-        <v>2143</v>
+        <v>6211</v>
       </c>
       <c r="D14" s="14">
-        <v>25397</v>
+        <v>25219</v>
       </c>
       <c r="E14" s="14">
-        <v>24865</v>
+        <v>22107</v>
       </c>
       <c r="F14" s="14">
-        <v>14837</v>
+        <v>16499</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>25.396999999999998</v>
+        <v>25.219000000000001</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>24.864999999999998</v>
+        <v>22.106999999999999</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>1.7117341780683426</v>
+        <v>1.5285168798108977</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1220,31 +1220,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>240.66</v>
+        <v>27.75</v>
       </c>
       <c r="C15" s="6">
-        <v>6211</v>
+        <v>2368</v>
       </c>
       <c r="D15" s="7">
-        <v>25219</v>
+        <v>25149</v>
       </c>
       <c r="E15" s="7">
-        <v>22104</v>
+        <v>24335</v>
       </c>
       <c r="F15" s="7">
-        <v>16499</v>
+        <v>14263</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>25.219000000000001</v>
+        <v>25.149000000000001</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>22.103999999999999</v>
+        <v>24.335000000000001</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>1.5285168798108977</v>
+        <v>1.7632335413307159</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1253,31 +1253,31 @@
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>36.89</v>
+        <v>182.45</v>
       </c>
       <c r="C16" s="13">
-        <v>2563</v>
+        <v>5565</v>
       </c>
       <c r="D16" s="14">
-        <v>25018</v>
+        <v>24974</v>
       </c>
       <c r="E16" s="14">
-        <v>24073</v>
+        <v>23468</v>
       </c>
       <c r="F16" s="14">
-        <v>14740</v>
+        <v>15705</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>25.018000000000001</v>
+        <v>24.974</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>24.073</v>
+        <v>23.468</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>1.6972862957937584</v>
+        <v>1.5901942056669851</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1286,31 +1286,31 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>182.45</v>
+        <v>27.21</v>
       </c>
       <c r="C17" s="6">
-        <v>5565</v>
+        <v>2143</v>
       </c>
       <c r="D17" s="7">
-        <v>24974</v>
+        <v>24901</v>
       </c>
       <c r="E17" s="7">
-        <v>23468</v>
+        <v>24366</v>
       </c>
       <c r="F17" s="7">
-        <v>15705</v>
+        <v>14837</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>24.974</v>
+        <v>24.901</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>23.468</v>
+        <v>24.366</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>1.5901942056669851</v>
+        <v>1.6783042394014962</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1319,31 +1319,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="12">
-        <v>52.93</v>
+        <v>36.89</v>
       </c>
       <c r="C18" s="13">
-        <v>3201</v>
+        <v>2563</v>
       </c>
       <c r="D18" s="14">
-        <v>24834</v>
+        <v>24731</v>
       </c>
       <c r="E18" s="14">
-        <v>23118</v>
+        <v>23574</v>
       </c>
       <c r="F18" s="14">
-        <v>13857</v>
+        <v>14740</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>24.834</v>
+        <v>24.731000000000002</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>23.117999999999999</v>
+        <v>23.574000000000002</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>1.7921628058021217</v>
+        <v>1.6778154681139756</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1352,31 +1352,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>25.33</v>
+        <v>38.03</v>
       </c>
       <c r="C19" s="6">
-        <v>2313</v>
+        <v>2973</v>
       </c>
       <c r="D19" s="7">
-        <v>24634</v>
+        <v>24672</v>
       </c>
       <c r="E19" s="7">
-        <v>23896</v>
+        <v>23734</v>
       </c>
       <c r="F19" s="7">
-        <v>14244</v>
+        <v>12971</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>24.634</v>
+        <v>24.672000000000001</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>23.896000000000001</v>
+        <v>23.734000000000002</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>1.7294299354114013</v>
+        <v>1.9020892760774035</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1385,31 +1385,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>39.71</v>
+        <v>93.86</v>
       </c>
       <c r="C20" s="13">
-        <v>2648</v>
+        <v>4450</v>
       </c>
       <c r="D20" s="14">
-        <v>24123</v>
+        <v>24543</v>
       </c>
       <c r="E20" s="14">
-        <v>23515</v>
+        <v>21794</v>
       </c>
       <c r="F20" s="14">
-        <v>14442</v>
+        <v>14968</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>24.123000000000001</v>
+        <v>24.542999999999999</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>23.515000000000001</v>
+        <v>21.794</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>1.6703365184877441</v>
+        <v>1.6396980224478888</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1418,31 +1418,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="5">
-        <v>228.96</v>
+        <v>52.93</v>
       </c>
       <c r="C21" s="6">
-        <v>6152</v>
+        <v>3201</v>
       </c>
       <c r="D21" s="7">
-        <v>23574</v>
+        <v>24335</v>
       </c>
       <c r="E21" s="7">
-        <v>20237</v>
+        <v>22619</v>
       </c>
       <c r="F21" s="7">
-        <v>15117</v>
+        <v>13857</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>23.574000000000002</v>
+        <v>24.335000000000001</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>20.236999999999998</v>
+        <v>22.619</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>1.5594363961103395</v>
+        <v>1.7561521252796422</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1451,31 +1451,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="12">
-        <v>42.33</v>
+        <v>25.33</v>
       </c>
       <c r="C22" s="13">
-        <v>3171</v>
+        <v>2313</v>
       </c>
       <c r="D22" s="14">
-        <v>23566</v>
+        <v>24135</v>
       </c>
       <c r="E22" s="14">
-        <v>21991</v>
+        <v>23397</v>
       </c>
       <c r="F22" s="14">
-        <v>14233</v>
+        <v>14244</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>23.565999999999999</v>
+        <v>24.135000000000002</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>21.991</v>
+        <v>23.396999999999998</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.6557296423803836</v>
+        <v>1.6943976411120472</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1484,31 +1484,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>93.86</v>
+        <v>39.71</v>
       </c>
       <c r="C23" s="6">
-        <v>4450</v>
+        <v>2648</v>
       </c>
       <c r="D23" s="7">
-        <v>23514</v>
+        <v>23624</v>
       </c>
       <c r="E23" s="7">
-        <v>21794</v>
+        <v>23016</v>
       </c>
       <c r="F23" s="7">
-        <v>14968</v>
+        <v>14442</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>23.513999999999999</v>
+        <v>23.623999999999999</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>21.794</v>
+        <v>23.015999999999998</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>1.570951362907536</v>
+        <v>1.6357845173798642</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1517,31 +1517,31 @@
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>187.06</v>
+        <v>228.96</v>
       </c>
       <c r="C24" s="13">
-        <v>5526</v>
+        <v>6152</v>
       </c>
       <c r="D24" s="14">
-        <v>23040</v>
+        <v>23514</v>
       </c>
       <c r="E24" s="14">
-        <v>20153</v>
+        <v>20237</v>
       </c>
       <c r="F24" s="14">
-        <v>13729</v>
+        <v>15117</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>23.04</v>
+        <v>23.513999999999999</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>20.152999999999999</v>
+        <v>20.236999999999998</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.6781994318595674</v>
+        <v>1.555467354633856</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1550,31 +1550,31 @@
         <v>32</v>
       </c>
       <c r="B25" s="5">
-        <v>28.72</v>
+        <v>42.33</v>
       </c>
       <c r="C25" s="6">
-        <v>2599</v>
+        <v>3171</v>
       </c>
       <c r="D25" s="7">
-        <v>22206</v>
+        <v>23067</v>
       </c>
       <c r="E25" s="7">
-        <v>20654</v>
+        <v>21668</v>
       </c>
       <c r="F25" s="7">
-        <v>14141</v>
+        <v>14233</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>22.206</v>
+        <v>23.067</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>20.654</v>
+        <v>21.667999999999999</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>1.57032741673149</v>
+        <v>1.6206702733085083</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1583,31 +1583,31 @@
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>17.32</v>
+        <v>187.06</v>
       </c>
       <c r="C26" s="13">
-        <v>1739</v>
+        <v>5526</v>
       </c>
       <c r="D26" s="14">
-        <v>21429</v>
+        <v>23040</v>
       </c>
       <c r="E26" s="14">
-        <v>21082</v>
+        <v>20154</v>
       </c>
       <c r="F26" s="14">
-        <v>13605</v>
+        <v>13729</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>21.428999999999998</v>
+        <v>23.04</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>21.082000000000001</v>
+        <v>20.154</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>1.5750826901874311</v>
+        <v>1.6781994318595674</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1616,31 +1616,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="5">
-        <v>83.54</v>
+        <v>28.72</v>
       </c>
       <c r="C27" s="6">
-        <v>3934</v>
+        <v>2599</v>
       </c>
       <c r="D27" s="7">
-        <v>21429</v>
+        <v>21924</v>
       </c>
       <c r="E27" s="7">
-        <v>20186</v>
+        <v>20654</v>
       </c>
       <c r="F27" s="7">
-        <v>12932</v>
+        <v>14141</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>21.428999999999998</v>
+        <v>21.923999999999999</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>20.186</v>
+        <v>20.654</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>1.6570522734302506</v>
+        <v>1.5503854041439784</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1649,31 +1649,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>25.66</v>
+        <v>17.32</v>
       </c>
       <c r="C28" s="13">
-        <v>2270</v>
+        <v>1739</v>
       </c>
       <c r="D28" s="14">
-        <v>21119</v>
+        <v>20930</v>
       </c>
       <c r="E28" s="14">
-        <v>20212</v>
+        <v>20583</v>
       </c>
       <c r="F28" s="14">
-        <v>13030</v>
+        <v>13605</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>21.119</v>
+        <v>20.93</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>20.212</v>
+        <v>20.582999999999998</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.6207981580966999</v>
+        <v>1.5384049981624404</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1682,31 +1682,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>28.89</v>
+        <v>83.54</v>
       </c>
       <c r="C29" s="6">
-        <v>2630</v>
+        <v>3934</v>
       </c>
       <c r="D29" s="7">
-        <v>20736</v>
+        <v>20930</v>
       </c>
       <c r="E29" s="7">
-        <v>20153</v>
+        <v>19687</v>
       </c>
       <c r="F29" s="7">
-        <v>13724</v>
+        <v>12932</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>20.736000000000001</v>
+        <v>20.93</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>20.152999999999999</v>
+        <v>19.687000000000001</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.510929758088021</v>
+        <v>1.6184658212186824</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1715,31 +1715,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>20.329999999999998</v>
+        <v>28.89</v>
       </c>
       <c r="C30" s="13">
-        <v>1825</v>
+        <v>2630</v>
       </c>
       <c r="D30" s="14">
-        <v>20237</v>
+        <v>20736</v>
       </c>
       <c r="E30" s="14">
-        <v>19999</v>
+        <v>20154</v>
       </c>
       <c r="F30" s="14">
-        <v>13381</v>
+        <v>13724</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>20.236999999999998</v>
+        <v>20.736000000000001</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>19.998999999999999</v>
+        <v>20.154</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.5123682833868919</v>
+        <v>1.510929758088021</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1748,31 +1748,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>49.81</v>
+        <v>25.66</v>
       </c>
       <c r="C31" s="6">
-        <v>3183</v>
+        <v>2270</v>
       </c>
       <c r="D31" s="7">
-        <v>20210</v>
+        <v>20620</v>
       </c>
       <c r="E31" s="7">
-        <v>18504</v>
+        <v>19713</v>
       </c>
       <c r="F31" s="7">
-        <v>12736</v>
+        <v>13030</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>20.21</v>
+        <v>20.62</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>18.504000000000001</v>
+        <v>19.713000000000001</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.5868404522613064</v>
+        <v>1.5825019186492708</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1781,31 +1781,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>56.22</v>
+        <v>20.329999999999998</v>
       </c>
       <c r="C32" s="13">
-        <v>3219</v>
+        <v>1825</v>
       </c>
       <c r="D32" s="14">
-        <v>20061</v>
+        <v>20237</v>
       </c>
       <c r="E32" s="14">
-        <v>18953</v>
+        <v>19999</v>
       </c>
       <c r="F32" s="14">
-        <v>12386</v>
+        <v>13381</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>20.061</v>
+        <v>20.236999999999998</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>18.952999999999999</v>
+        <v>19.998999999999999</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>1.6196512191183594</v>
+        <v>1.5123682833868919</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1814,31 +1814,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>73.53</v>
+        <v>49.81</v>
       </c>
       <c r="C33" s="6">
-        <v>3551</v>
+        <v>3183</v>
       </c>
       <c r="D33" s="7">
-        <v>20050</v>
+        <v>20210</v>
       </c>
       <c r="E33" s="7">
-        <v>19497</v>
+        <v>18504</v>
       </c>
       <c r="F33" s="7">
-        <v>12059</v>
+        <v>12736</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>20.05</v>
+        <v>20.21</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>19.497</v>
+        <v>18.504000000000001</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.6626585952400696</v>
+        <v>1.5868404522613064</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1847,31 +1847,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>26.89</v>
+        <v>56.22</v>
       </c>
       <c r="C34" s="13">
-        <v>2114</v>
+        <v>3219</v>
       </c>
       <c r="D34" s="14">
-        <v>19961</v>
+        <v>20061</v>
       </c>
       <c r="E34" s="14">
-        <v>19802</v>
+        <v>18953</v>
       </c>
       <c r="F34" s="14">
-        <v>7664</v>
+        <v>12386</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>19.960999999999999</v>
+        <v>20.061</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>19.802</v>
+        <v>18.952999999999999</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>2.6045146137787056</v>
+        <v>1.6196512191183594</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1880,31 +1880,31 @@
         <v>42</v>
       </c>
       <c r="B35" s="5">
-        <v>204.97</v>
+        <v>73.53</v>
       </c>
       <c r="C35" s="6">
-        <v>6009</v>
+        <v>3551</v>
       </c>
       <c r="D35" s="7">
-        <v>19608</v>
+        <v>19862</v>
       </c>
       <c r="E35" s="7">
-        <v>16523</v>
+        <v>19497</v>
       </c>
       <c r="F35" s="7">
-        <v>9361</v>
+        <v>12059</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>19.608000000000001</v>
+        <v>19.861999999999998</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
-        <v>16.523</v>
+        <v>19.497</v>
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>2.094648007691486</v>
+        <v>1.6470685794842026</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1919,25 +1919,25 @@
         <v>3211</v>
       </c>
       <c r="D36" s="14">
-        <v>19538</v>
+        <v>19048</v>
       </c>
       <c r="E36" s="14">
-        <v>18527</v>
+        <v>18028</v>
       </c>
       <c r="F36" s="14">
         <v>10413</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>19.538</v>
+        <v>19.047999999999998</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>18.527000000000001</v>
+        <v>18.027999999999999</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.8763084605781235</v>
+        <v>1.829251896667627</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1946,31 +1946,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>36.369999999999997</v>
+        <v>204.97</v>
       </c>
       <c r="C37" s="6">
-        <v>3031</v>
+        <v>6009</v>
       </c>
       <c r="D37" s="7">
-        <v>19307</v>
+        <v>19048</v>
       </c>
       <c r="E37" s="7">
-        <v>17451</v>
+        <v>16024</v>
       </c>
       <c r="F37" s="7">
-        <v>10293</v>
+        <v>9361</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" ref="G37:G69" si="3">D37/1000</f>
-        <v>19.306999999999999</v>
+        <v>19.047999999999998</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" ref="H37:H69" si="4">E37/1000</f>
-        <v>17.451000000000001</v>
+        <v>16.024000000000001</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" ref="I37:I69" si="5">IFERROR(D37/F37,"")</f>
-        <v>1.8757407947148548</v>
+        <v>2.0348253391731652</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1979,31 +1979,31 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>135.69999999999999</v>
+        <v>36.369999999999997</v>
       </c>
       <c r="C38" s="13">
-        <v>5466</v>
+        <v>3031</v>
       </c>
       <c r="D38" s="14">
-        <v>19307</v>
+        <v>18804</v>
       </c>
       <c r="E38" s="14">
-        <v>16523</v>
+        <v>16952</v>
       </c>
       <c r="F38" s="14">
-        <v>9364</v>
+        <v>10293</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="3"/>
-        <v>19.306999999999999</v>
+        <v>18.803999999999998</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="4"/>
-        <v>16.523</v>
+        <v>16.952000000000002</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="5"/>
-        <v>2.0618325501922254</v>
+        <v>1.8268726318857476</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -2012,31 +2012,31 @@
         <v>46</v>
       </c>
       <c r="B39" s="5">
-        <v>27.34</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C39" s="6">
-        <v>2417</v>
+        <v>5466</v>
       </c>
       <c r="D39" s="7">
-        <v>19286</v>
+        <v>18804</v>
       </c>
       <c r="E39" s="7">
-        <v>18213</v>
+        <v>16024</v>
       </c>
       <c r="F39" s="7">
-        <v>10355</v>
+        <v>9364</v>
       </c>
       <c r="G39" s="8">
         <f t="shared" si="3"/>
-        <v>19.286000000000001</v>
+        <v>18.803999999999998</v>
       </c>
       <c r="H39" s="8">
         <f t="shared" si="4"/>
-        <v>18.213000000000001</v>
+        <v>16.024000000000001</v>
       </c>
       <c r="I39" s="9">
         <f t="shared" si="5"/>
-        <v>1.8624818928054081</v>
+        <v>2.0081161896625375</v>
       </c>
       <c r="J39" s="10"/>
     </row>
@@ -2045,31 +2045,31 @@
         <v>47</v>
       </c>
       <c r="B40" s="12">
-        <v>55.07</v>
+        <v>82.03</v>
       </c>
       <c r="C40" s="13">
-        <v>3294</v>
+        <v>3674</v>
       </c>
       <c r="D40" s="14">
-        <v>19089</v>
+        <v>18789</v>
       </c>
       <c r="E40" s="14">
-        <v>17502</v>
+        <v>17734</v>
       </c>
       <c r="F40" s="14">
-        <v>10324</v>
+        <v>13042</v>
       </c>
       <c r="G40" s="15">
         <f t="shared" si="3"/>
-        <v>19.088999999999999</v>
+        <v>18.789000000000001</v>
       </c>
       <c r="H40" s="15">
         <f t="shared" si="4"/>
-        <v>17.501999999999999</v>
+        <v>17.734000000000002</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="5"/>
-        <v>1.8489926385122046</v>
+        <v>1.4406532740377243</v>
       </c>
       <c r="J40" s="17"/>
     </row>
@@ -2078,31 +2078,31 @@
         <v>48</v>
       </c>
       <c r="B41" s="5">
-        <v>82.03</v>
+        <v>27.34</v>
       </c>
       <c r="C41" s="6">
-        <v>3674</v>
+        <v>2417</v>
       </c>
       <c r="D41" s="7">
-        <v>18789</v>
+        <v>18787</v>
       </c>
       <c r="E41" s="7">
-        <v>17734</v>
+        <v>17714</v>
       </c>
       <c r="F41" s="7">
-        <v>13042</v>
+        <v>10355</v>
       </c>
       <c r="G41" s="8">
         <f t="shared" si="3"/>
-        <v>18.789000000000001</v>
+        <v>18.786999999999999</v>
       </c>
       <c r="H41" s="8">
         <f t="shared" si="4"/>
-        <v>17.734000000000002</v>
+        <v>17.713999999999999</v>
       </c>
       <c r="I41" s="9">
         <f t="shared" si="5"/>
-        <v>1.4406532740377243</v>
+        <v>1.8142926122646064</v>
       </c>
       <c r="J41" s="10"/>
     </row>
@@ -2111,31 +2111,31 @@
         <v>49</v>
       </c>
       <c r="B42" s="12">
-        <v>43.21</v>
+        <v>55.07</v>
       </c>
       <c r="C42" s="13">
-        <v>2710</v>
+        <v>3294</v>
       </c>
       <c r="D42" s="14">
-        <v>18577</v>
+        <v>18586</v>
       </c>
       <c r="E42" s="14">
-        <v>17158</v>
+        <v>17009</v>
       </c>
       <c r="F42" s="14">
-        <v>9510</v>
+        <v>10324</v>
       </c>
       <c r="G42" s="15">
         <f t="shared" si="3"/>
-        <v>18.577000000000002</v>
+        <v>18.585999999999999</v>
       </c>
       <c r="H42" s="15">
         <f t="shared" si="4"/>
-        <v>17.158000000000001</v>
+        <v>17.009</v>
       </c>
       <c r="I42" s="16">
         <f t="shared" si="5"/>
-        <v>1.9534174553101997</v>
+        <v>1.8002712127082525</v>
       </c>
       <c r="J42" s="17"/>
     </row>
@@ -2144,31 +2144,31 @@
         <v>50</v>
       </c>
       <c r="B43" s="5">
-        <v>24.59</v>
+        <v>43.21</v>
       </c>
       <c r="C43" s="6">
-        <v>3289</v>
+        <v>2710</v>
       </c>
       <c r="D43" s="7">
-        <v>18328</v>
+        <v>18078</v>
       </c>
       <c r="E43" s="7">
-        <v>16878</v>
+        <v>16659</v>
       </c>
       <c r="F43" s="7">
-        <v>8560</v>
+        <v>9510</v>
       </c>
       <c r="G43" s="8">
         <f t="shared" si="3"/>
-        <v>18.327999999999999</v>
+        <v>18.077999999999999</v>
       </c>
       <c r="H43" s="8">
         <f t="shared" si="4"/>
-        <v>16.878</v>
+        <v>16.658999999999999</v>
       </c>
       <c r="I43" s="9">
         <f t="shared" si="5"/>
-        <v>2.1411214953271029</v>
+        <v>1.9009463722397477</v>
       </c>
       <c r="J43" s="10"/>
     </row>
@@ -2177,31 +2177,31 @@
         <v>51</v>
       </c>
       <c r="B44" s="12">
-        <v>30.09</v>
+        <v>40.19</v>
       </c>
       <c r="C44" s="13">
-        <v>3233</v>
+        <v>2657</v>
       </c>
       <c r="D44" s="14">
-        <v>18328</v>
+        <v>17009</v>
       </c>
       <c r="E44" s="14">
-        <v>16878</v>
+        <v>16024</v>
       </c>
       <c r="F44" s="14">
-        <v>8180</v>
+        <v>9367</v>
       </c>
       <c r="G44" s="15">
         <f t="shared" si="3"/>
-        <v>18.327999999999999</v>
+        <v>17.009</v>
       </c>
       <c r="H44" s="15">
         <f t="shared" si="4"/>
-        <v>16.878</v>
+        <v>16.024000000000001</v>
       </c>
       <c r="I44" s="16">
         <f t="shared" si="5"/>
-        <v>2.2405867970660145</v>
+        <v>1.8158428525675243</v>
       </c>
       <c r="J44" s="17"/>
     </row>
@@ -2210,31 +2210,31 @@
         <v>52</v>
       </c>
       <c r="B45" s="5">
-        <v>40.19</v>
+        <v>24.59</v>
       </c>
       <c r="C45" s="6">
-        <v>2657</v>
+        <v>3289</v>
       </c>
       <c r="D45" s="7">
-        <v>17502</v>
+        <v>16873</v>
       </c>
       <c r="E45" s="7">
-        <v>16523</v>
+        <v>15752</v>
       </c>
       <c r="F45" s="7">
-        <v>9367</v>
+        <v>8560</v>
       </c>
       <c r="G45" s="8">
         <f t="shared" si="3"/>
-        <v>17.501999999999999</v>
+        <v>16.873000000000001</v>
       </c>
       <c r="H45" s="8">
         <f t="shared" si="4"/>
-        <v>16.523</v>
+        <v>15.752000000000001</v>
       </c>
       <c r="I45" s="9">
         <f t="shared" si="5"/>
-        <v>1.8684744315148927</v>
+        <v>1.9711448598130841</v>
       </c>
       <c r="J45" s="10"/>
     </row>
@@ -2243,66 +2243,66 @@
         <v>53</v>
       </c>
       <c r="B46" s="12">
-        <v>190.66</v>
+        <v>30.09</v>
       </c>
       <c r="C46" s="13">
-        <v>7672</v>
+        <v>3233</v>
       </c>
       <c r="D46" s="14">
-        <v>17200</v>
+        <v>16873</v>
       </c>
       <c r="E46" s="14">
-        <v>14676</v>
+        <v>15752</v>
       </c>
       <c r="F46" s="14">
-        <v>5896</v>
+        <v>8180</v>
       </c>
       <c r="G46" s="15">
         <f t="shared" si="3"/>
-        <v>17.2</v>
+        <v>16.873000000000001</v>
       </c>
       <c r="H46" s="15">
         <f t="shared" si="4"/>
-        <v>14.676</v>
+        <v>15.752000000000001</v>
       </c>
       <c r="I46" s="16">
         <f t="shared" si="5"/>
-        <v>2.9172320217096335</v>
+        <v>2.0627139364303178</v>
       </c>
       <c r="J46" s="17"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="19">
-        <v>46.34</v>
-      </c>
-      <c r="C47" s="20">
-        <v>2872</v>
-      </c>
-      <c r="D47" s="21">
-        <v>16156</v>
-      </c>
-      <c r="E47" s="21">
-        <v>14600</v>
-      </c>
-      <c r="F47" s="21">
-        <v>5202</v>
-      </c>
-      <c r="G47" s="22">
+      <c r="B47" s="5">
+        <v>26.89</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2114</v>
+      </c>
+      <c r="D47" s="7">
+        <v>15599</v>
+      </c>
+      <c r="E47" s="7">
+        <v>15439</v>
+      </c>
+      <c r="F47" s="7">
+        <v>7664</v>
+      </c>
+      <c r="G47" s="8">
         <f t="shared" si="3"/>
-        <v>16.155999999999999</v>
-      </c>
-      <c r="H47" s="22">
+        <v>15.599</v>
+      </c>
+      <c r="H47" s="8">
         <f t="shared" si="4"/>
-        <v>14.6</v>
-      </c>
-      <c r="I47" s="23">
+        <v>15.439</v>
+      </c>
+      <c r="I47" s="9">
         <f t="shared" si="5"/>
-        <v>3.1057285659361784</v>
-      </c>
-      <c r="J47" s="24"/>
+        <v>2.0353601252609606</v>
+      </c>
+      <c r="J47" s="10"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
@@ -2315,25 +2315,25 @@
         <v>6277</v>
       </c>
       <c r="D48" s="14">
-        <v>16043</v>
+        <v>15544</v>
       </c>
       <c r="E48" s="14">
-        <v>14615</v>
+        <v>14116</v>
       </c>
       <c r="F48" s="14">
         <v>7560</v>
       </c>
       <c r="G48" s="15">
         <f t="shared" si="3"/>
-        <v>16.042999999999999</v>
+        <v>15.544</v>
       </c>
       <c r="H48" s="15">
         <f t="shared" si="4"/>
-        <v>14.615</v>
+        <v>14.116</v>
       </c>
       <c r="I48" s="16">
         <f t="shared" si="5"/>
-        <v>2.1220899470899472</v>
+        <v>2.0560846560846562</v>
       </c>
       <c r="J48" s="17"/>
     </row>
@@ -2348,25 +2348,25 @@
         <v>5695</v>
       </c>
       <c r="D49" s="7">
-        <v>16043</v>
+        <v>15544</v>
       </c>
       <c r="E49" s="7">
-        <v>14615</v>
+        <v>14116</v>
       </c>
       <c r="F49" s="7">
         <v>7303</v>
       </c>
       <c r="G49" s="8">
         <f t="shared" si="3"/>
-        <v>16.042999999999999</v>
+        <v>15.544</v>
       </c>
       <c r="H49" s="8">
         <f t="shared" si="4"/>
-        <v>14.615</v>
+        <v>14.116</v>
       </c>
       <c r="I49" s="9">
         <f t="shared" si="5"/>
-        <v>2.196768451321375</v>
+        <v>2.1284403669724772</v>
       </c>
       <c r="J49" s="10"/>
     </row>
@@ -2381,25 +2381,25 @@
         <v>2414</v>
       </c>
       <c r="D50" s="14">
-        <v>16043</v>
+        <v>15544</v>
       </c>
       <c r="E50" s="14">
-        <v>15343</v>
+        <v>14831</v>
       </c>
       <c r="F50" s="14">
         <v>8238</v>
       </c>
       <c r="G50" s="15">
         <f t="shared" si="3"/>
-        <v>16.042999999999999</v>
+        <v>15.544</v>
       </c>
       <c r="H50" s="15">
         <f t="shared" si="4"/>
-        <v>15.343</v>
+        <v>14.831</v>
       </c>
       <c r="I50" s="16">
         <f t="shared" si="5"/>
-        <v>1.9474386987132799</v>
+        <v>1.8868657441126486</v>
       </c>
       <c r="J50" s="17"/>
     </row>
@@ -2408,31 +2408,31 @@
         <v>58</v>
       </c>
       <c r="B51" s="5">
-        <v>189.65</v>
+        <v>48.43</v>
       </c>
       <c r="C51" s="6">
-        <v>6663</v>
+        <v>2895</v>
       </c>
       <c r="D51" s="7">
-        <v>15433</v>
+        <v>15487</v>
       </c>
       <c r="E51" s="7">
-        <v>11682</v>
+        <v>14116</v>
       </c>
       <c r="F51" s="7">
-        <v>5929</v>
+        <v>7306</v>
       </c>
       <c r="G51" s="8">
         <f t="shared" si="3"/>
-        <v>15.433</v>
+        <v>15.487</v>
       </c>
       <c r="H51" s="8">
         <f t="shared" si="4"/>
-        <v>11.682</v>
+        <v>14.116</v>
       </c>
       <c r="I51" s="9">
         <f t="shared" si="5"/>
-        <v>2.6029684601113172</v>
+        <v>2.1197645770599509</v>
       </c>
       <c r="J51" s="10"/>
     </row>
@@ -2441,31 +2441,31 @@
         <v>59</v>
       </c>
       <c r="B52" s="12">
-        <v>48.43</v>
+        <v>190.66</v>
       </c>
       <c r="C52" s="13">
-        <v>2895</v>
+        <v>7672</v>
       </c>
       <c r="D52" s="14">
-        <v>15369</v>
+        <v>11835</v>
       </c>
       <c r="E52" s="14">
-        <v>14615</v>
+        <v>8224</v>
       </c>
       <c r="F52" s="14">
-        <v>7306</v>
+        <v>5896</v>
       </c>
       <c r="G52" s="15">
         <f t="shared" si="3"/>
-        <v>15.369</v>
+        <v>11.835000000000001</v>
       </c>
       <c r="H52" s="15">
         <f t="shared" si="4"/>
-        <v>14.615</v>
+        <v>8.2240000000000002</v>
       </c>
       <c r="I52" s="16">
         <f t="shared" si="5"/>
-        <v>2.1036134683821515</v>
+        <v>2.0072930800542741</v>
       </c>
       <c r="J52" s="17"/>
     </row>
@@ -2474,66 +2474,66 @@
         <v>60</v>
       </c>
       <c r="B53" s="5">
-        <v>150.53</v>
+        <v>41.44</v>
       </c>
       <c r="C53" s="6">
-        <v>4897</v>
+        <v>2838</v>
       </c>
       <c r="D53" s="7">
-        <v>14982</v>
+        <v>11834</v>
       </c>
       <c r="E53" s="7">
-        <v>12772</v>
+        <v>11145</v>
       </c>
       <c r="F53" s="7">
-        <v>12769</v>
+        <v>4215</v>
       </c>
       <c r="G53" s="8">
         <f t="shared" si="3"/>
-        <v>14.981999999999999</v>
+        <v>11.834</v>
       </c>
       <c r="H53" s="8">
         <f t="shared" si="4"/>
-        <v>12.772</v>
+        <v>11.145</v>
       </c>
       <c r="I53" s="9">
         <f t="shared" si="5"/>
-        <v>1.173310361030621</v>
+        <v>2.8075919335705812</v>
       </c>
       <c r="J53" s="10"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B54" s="12">
-        <v>38.03</v>
-      </c>
-      <c r="C54" s="13">
-        <v>2973</v>
-      </c>
-      <c r="D54" s="14">
-        <v>14154</v>
-      </c>
-      <c r="E54" s="14">
-        <v>13216</v>
-      </c>
-      <c r="F54" s="14">
-        <v>12971</v>
-      </c>
-      <c r="G54" s="15">
+      <c r="B54" s="19">
+        <v>226.37</v>
+      </c>
+      <c r="C54" s="20">
+        <v>7413</v>
+      </c>
+      <c r="D54" s="21">
+        <v>11392</v>
+      </c>
+      <c r="E54" s="21">
+        <v>9188</v>
+      </c>
+      <c r="F54" s="21">
+        <v>554</v>
+      </c>
+      <c r="G54" s="22">
         <f t="shared" si="3"/>
-        <v>14.154</v>
-      </c>
-      <c r="H54" s="15">
+        <v>11.391999999999999</v>
+      </c>
+      <c r="H54" s="22">
         <f t="shared" si="4"/>
-        <v>13.215999999999999</v>
-      </c>
-      <c r="I54" s="16">
+        <v>9.1880000000000006</v>
+      </c>
+      <c r="I54" s="23">
         <f t="shared" si="5"/>
-        <v>1.0912034538586077</v>
-      </c>
-      <c r="J54" s="17"/>
+        <v>20.56317689530686</v>
+      </c>
+      <c r="J54" s="24"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="18" t="s">
@@ -2546,91 +2546,91 @@
         <v>5228</v>
       </c>
       <c r="D55" s="21">
-        <v>12637</v>
+        <v>11392</v>
       </c>
       <c r="E55" s="21">
-        <v>9612</v>
+        <v>9600</v>
       </c>
       <c r="F55" s="21">
         <v>289</v>
       </c>
       <c r="G55" s="22">
         <f t="shared" si="3"/>
-        <v>12.637</v>
+        <v>11.391999999999999</v>
       </c>
       <c r="H55" s="22">
         <f t="shared" si="4"/>
-        <v>9.6120000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I55" s="23">
         <f t="shared" si="5"/>
-        <v>43.726643598615915</v>
+        <v>39.418685121107266</v>
       </c>
       <c r="J55" s="24"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B56" s="19">
-        <v>226.37</v>
-      </c>
-      <c r="C56" s="20">
-        <v>7413</v>
-      </c>
-      <c r="D56" s="21">
-        <v>12059</v>
-      </c>
-      <c r="E56" s="21">
-        <v>9181</v>
-      </c>
-      <c r="F56" s="21">
-        <v>554</v>
-      </c>
-      <c r="G56" s="22">
+      <c r="B56" s="12">
+        <v>31.8</v>
+      </c>
+      <c r="C56" s="13">
+        <v>2339</v>
+      </c>
+      <c r="D56" s="14">
+        <v>11196</v>
+      </c>
+      <c r="E56" s="14">
+        <v>10394</v>
+      </c>
+      <c r="F56" s="14">
+        <v>4262</v>
+      </c>
+      <c r="G56" s="15">
         <f t="shared" si="3"/>
-        <v>12.058999999999999</v>
-      </c>
-      <c r="H56" s="22">
+        <v>11.196</v>
+      </c>
+      <c r="H56" s="15">
         <f t="shared" si="4"/>
-        <v>9.1809999999999992</v>
-      </c>
-      <c r="I56" s="23">
+        <v>10.394</v>
+      </c>
+      <c r="I56" s="16">
         <f t="shared" si="5"/>
-        <v>21.767148014440433</v>
-      </c>
-      <c r="J56" s="24"/>
+        <v>2.626935710933834</v>
+      </c>
+      <c r="J56" s="17"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B57" s="5">
-        <v>41.44</v>
+        <v>303.58</v>
       </c>
       <c r="C57" s="6">
-        <v>2838</v>
+        <v>7626</v>
       </c>
       <c r="D57" s="7">
-        <v>11834</v>
+        <v>10643</v>
       </c>
       <c r="E57" s="7">
-        <v>11145</v>
+        <v>6775</v>
       </c>
       <c r="F57" s="7">
-        <v>4215</v>
+        <v>6059</v>
       </c>
       <c r="G57" s="8">
         <f t="shared" si="3"/>
-        <v>11.834</v>
+        <v>10.643000000000001</v>
       </c>
       <c r="H57" s="8">
         <f t="shared" si="4"/>
-        <v>11.145</v>
+        <v>6.7750000000000004</v>
       </c>
       <c r="I57" s="9">
         <f t="shared" si="5"/>
-        <v>2.8075919335705812</v>
+        <v>1.7565604885294603</v>
       </c>
       <c r="J57" s="10"/>
     </row>
@@ -2639,31 +2639,31 @@
         <v>65</v>
       </c>
       <c r="B58" s="12">
-        <v>31.8</v>
+        <v>49.08</v>
       </c>
       <c r="C58" s="13">
-        <v>2339</v>
+        <v>3023</v>
       </c>
       <c r="D58" s="14">
-        <v>11196</v>
+        <v>10443</v>
       </c>
       <c r="E58" s="14">
-        <v>10394</v>
+        <v>9891</v>
       </c>
       <c r="F58" s="14">
-        <v>4262</v>
+        <v>3629</v>
       </c>
       <c r="G58" s="15">
         <f t="shared" si="3"/>
-        <v>11.196</v>
+        <v>10.443</v>
       </c>
       <c r="H58" s="15">
         <f t="shared" si="4"/>
-        <v>10.394</v>
+        <v>9.891</v>
       </c>
       <c r="I58" s="16">
         <f t="shared" si="5"/>
-        <v>2.626935710933834</v>
+        <v>2.8776522457977403</v>
       </c>
       <c r="J58" s="17"/>
     </row>
@@ -2672,97 +2672,97 @@
         <v>66</v>
       </c>
       <c r="B59" s="5">
-        <v>49.08</v>
+        <v>189.65</v>
       </c>
       <c r="C59" s="6">
-        <v>3023</v>
+        <v>6663</v>
       </c>
       <c r="D59" s="7">
-        <v>10443</v>
+        <v>9935</v>
       </c>
       <c r="E59" s="7">
-        <v>9891</v>
+        <v>6591</v>
       </c>
       <c r="F59" s="7">
-        <v>3629</v>
+        <v>5929</v>
       </c>
       <c r="G59" s="8">
         <f t="shared" si="3"/>
-        <v>10.443</v>
+        <v>9.9350000000000005</v>
       </c>
       <c r="H59" s="8">
         <f t="shared" si="4"/>
-        <v>9.891</v>
+        <v>6.5910000000000002</v>
       </c>
       <c r="I59" s="9">
         <f t="shared" si="5"/>
-        <v>2.8776522457977403</v>
+        <v>1.675662000337325</v>
       </c>
       <c r="J59" s="10"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B60" s="12">
-        <v>303.58</v>
-      </c>
-      <c r="C60" s="13">
-        <v>7626</v>
-      </c>
-      <c r="D60" s="14">
-        <v>10311</v>
-      </c>
-      <c r="E60" s="14">
-        <v>6777</v>
-      </c>
-      <c r="F60" s="14">
-        <v>6059</v>
-      </c>
-      <c r="G60" s="15">
+      <c r="B60" s="19">
+        <v>172.75</v>
+      </c>
+      <c r="C60" s="20">
+        <v>5905</v>
+      </c>
+      <c r="D60" s="21">
+        <v>9916</v>
+      </c>
+      <c r="E60" s="21">
+        <v>6738</v>
+      </c>
+      <c r="F60" s="21">
+        <v>2656</v>
+      </c>
+      <c r="G60" s="22">
         <f t="shared" si="3"/>
-        <v>10.311</v>
-      </c>
-      <c r="H60" s="15">
+        <v>9.9160000000000004</v>
+      </c>
+      <c r="H60" s="22">
         <f t="shared" si="4"/>
-        <v>6.7770000000000001</v>
-      </c>
-      <c r="I60" s="16">
+        <v>6.7380000000000004</v>
+      </c>
+      <c r="I60" s="23">
         <f t="shared" si="5"/>
-        <v>1.7017659679815151</v>
-      </c>
-      <c r="J60" s="17"/>
+        <v>3.7334337349397591</v>
+      </c>
+      <c r="J60" s="24"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="18" t="s">
         <v>68</v>
       </c>
       <c r="B61" s="19">
-        <v>172.75</v>
+        <v>93.41</v>
       </c>
       <c r="C61" s="20">
-        <v>5905</v>
+        <v>4212</v>
       </c>
       <c r="D61" s="21">
-        <v>9916</v>
+        <v>9600</v>
       </c>
       <c r="E61" s="21">
-        <v>6738</v>
+        <v>8252</v>
       </c>
       <c r="F61" s="21">
-        <v>2656</v>
+        <v>539</v>
       </c>
       <c r="G61" s="22">
         <f t="shared" si="3"/>
-        <v>9.9160000000000004</v>
+        <v>9.6</v>
       </c>
       <c r="H61" s="22">
         <f t="shared" si="4"/>
-        <v>6.7380000000000004</v>
+        <v>8.2520000000000007</v>
       </c>
       <c r="I61" s="23">
         <f t="shared" si="5"/>
-        <v>3.7334337349397591</v>
+        <v>17.810760667903526</v>
       </c>
       <c r="J61" s="24"/>
     </row>
@@ -2771,66 +2771,66 @@
         <v>69</v>
       </c>
       <c r="B62" s="19">
-        <v>93.41</v>
+        <v>30.12</v>
       </c>
       <c r="C62" s="20">
-        <v>4212</v>
+        <v>2592</v>
       </c>
       <c r="D62" s="21">
-        <v>9612</v>
+        <v>9450</v>
       </c>
       <c r="E62" s="21">
-        <v>8264</v>
+        <v>8286</v>
       </c>
       <c r="F62" s="21">
-        <v>539</v>
+        <v>929</v>
       </c>
       <c r="G62" s="22">
         <f t="shared" si="3"/>
-        <v>9.6120000000000001</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="H62" s="22">
         <f t="shared" si="4"/>
-        <v>8.2639999999999993</v>
+        <v>8.2859999999999996</v>
       </c>
       <c r="I62" s="23">
         <f t="shared" si="5"/>
-        <v>17.833024118738404</v>
+        <v>10.172228202368137</v>
       </c>
       <c r="J62" s="24"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="18" t="s">
+      <c r="A63" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B63" s="19">
-        <v>30.12</v>
-      </c>
-      <c r="C63" s="20">
-        <v>2592</v>
-      </c>
-      <c r="D63" s="21">
-        <v>9477</v>
-      </c>
-      <c r="E63" s="21">
-        <v>8298</v>
-      </c>
-      <c r="F63" s="21">
-        <v>929</v>
-      </c>
-      <c r="G63" s="22">
+      <c r="B63" s="5">
+        <v>46.34</v>
+      </c>
+      <c r="C63" s="6">
+        <v>2872</v>
+      </c>
+      <c r="D63" s="7">
+        <v>8982</v>
+      </c>
+      <c r="E63" s="7">
+        <v>7133</v>
+      </c>
+      <c r="F63" s="7">
+        <v>5202</v>
+      </c>
+      <c r="G63" s="8">
         <f t="shared" si="3"/>
-        <v>9.4770000000000003</v>
-      </c>
-      <c r="H63" s="22">
+        <v>8.9819999999999993</v>
+      </c>
+      <c r="H63" s="8">
         <f t="shared" si="4"/>
-        <v>8.298</v>
-      </c>
-      <c r="I63" s="23">
+        <v>7.133</v>
+      </c>
+      <c r="I63" s="9">
         <f t="shared" si="5"/>
-        <v>10.201291711517761</v>
-      </c>
-      <c r="J63" s="24"/>
+        <v>1.726643598615917</v>
+      </c>
+      <c r="J63" s="10"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="18" t="s">
@@ -2876,25 +2876,25 @@
         <v>3355</v>
       </c>
       <c r="D65" s="21">
-        <v>8298</v>
+        <v>8286</v>
       </c>
       <c r="E65" s="21">
-        <v>7284</v>
+        <v>7283</v>
       </c>
       <c r="F65" s="21">
         <v>1816</v>
       </c>
       <c r="G65" s="22">
         <f t="shared" si="3"/>
-        <v>8.298</v>
+        <v>8.2859999999999996</v>
       </c>
       <c r="H65" s="22">
         <f t="shared" si="4"/>
-        <v>7.2839999999999998</v>
+        <v>7.2830000000000004</v>
       </c>
       <c r="I65" s="23">
         <f t="shared" si="5"/>
-        <v>4.569383259911894</v>
+        <v>4.5627753303964758</v>
       </c>
       <c r="J65" s="24"/>
     </row>
@@ -2909,7 +2909,7 @@
         <v>3558</v>
       </c>
       <c r="D66" s="21">
-        <v>8298</v>
+        <v>8286</v>
       </c>
       <c r="E66" s="21">
         <v>6044</v>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="G66" s="22">
         <f t="shared" si="3"/>
-        <v>8.298</v>
+        <v>8.2859999999999996</v>
       </c>
       <c r="H66" s="22">
         <f t="shared" si="4"/>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="I66" s="23">
         <f t="shared" si="5"/>
-        <v>4.5097826086956525</v>
+        <v>4.5032608695652172</v>
       </c>
       <c r="J66" s="24"/>
     </row>
@@ -2945,7 +2945,7 @@
         <v>5271</v>
       </c>
       <c r="E67" s="21">
-        <v>3262</v>
+        <v>3243</v>
       </c>
       <c r="F67" s="21">
         <v>623</v>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="H67" s="22">
         <f t="shared" si="4"/>
-        <v>3.262</v>
+        <v>3.2429999999999999</v>
       </c>
       <c r="I67" s="23">
         <f t="shared" si="5"/>
@@ -2975,7 +2975,7 @@
         <v>5351</v>
       </c>
       <c r="D68" s="21">
-        <v>3262</v>
+        <v>4395</v>
       </c>
       <c r="E68" s="21">
         <v>616</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G68" s="22">
         <f t="shared" si="3"/>
-        <v>3.262</v>
+        <v>4.3949999999999996</v>
       </c>
       <c r="H68" s="22">
         <f t="shared" si="4"/>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="I68" s="23">
         <f t="shared" si="5"/>
-        <v>18.965116279069768</v>
+        <v>25.552325581395348</v>
       </c>
       <c r="J68" s="24"/>
     </row>
@@ -3200,15 +3200,15 @@
       </c>
       <c r="D76" s="31">
         <f>MAX(D5:D74)</f>
-        <v>26906</v>
+        <v>27435</v>
       </c>
       <c r="G76" s="32">
         <f>IFERROR(MAX(G5:G74),"")</f>
-        <v>26.905999999999999</v>
+        <v>27.434999999999999</v>
       </c>
       <c r="I76" s="33">
         <f>IFERROR(AVERAGE(I5:I74),"")</f>
-        <v>3.770387308243587</v>
+        <v>3.7325692574407903</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ED30C4-DCCE-4B1A-AFD5-C9F75276A5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6127F424-DF2F-4FDD-A9A9-DD8F78712100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="108">
   <si>
     <t>FAZENDA TUCANO — distância dos talhões até a sede</t>
   </si>
@@ -240,6 +240,9 @@
     <t>T-04</t>
   </si>
   <si>
+    <t>T-06B</t>
+  </si>
+  <si>
     <t>T-07</t>
   </si>
   <si>
@@ -261,6 +264,9 @@
     <t>T-02</t>
   </si>
   <si>
+    <t>T-06C</t>
+  </si>
+  <si>
     <t>T-01</t>
   </si>
   <si>
@@ -277,12 +283,6 @@
   </si>
   <si>
     <t>sem estrada até este talhão</t>
-  </si>
-  <si>
-    <t>T-06B</t>
-  </si>
-  <si>
-    <t>T-06C</t>
   </si>
   <si>
     <t>T-40C</t>
@@ -1961,15 +1961,15 @@
         <v>9361</v>
       </c>
       <c r="G37" s="8">
-        <f t="shared" ref="G37:G69" si="3">D37/1000</f>
+        <f t="shared" ref="G37:G71" si="3">D37/1000</f>
         <v>19.047999999999998</v>
       </c>
       <c r="H37" s="8">
-        <f t="shared" ref="H37:H69" si="4">E37/1000</f>
+        <f t="shared" ref="H37:H71" si="4">E37/1000</f>
         <v>16.024000000000001</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" ref="I37:I69" si="5">IFERROR(D37/F37,"")</f>
+        <f t="shared" ref="I37:I71" si="5">IFERROR(D37/F37,"")</f>
         <v>2.0348253391731652</v>
       </c>
       <c r="J37" s="10"/>
@@ -2447,7 +2447,7 @@
         <v>7672</v>
       </c>
       <c r="D52" s="14">
-        <v>11835</v>
+        <v>12406</v>
       </c>
       <c r="E52" s="14">
         <v>8224</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G52" s="15">
         <f t="shared" si="3"/>
-        <v>11.835000000000001</v>
+        <v>12.406000000000001</v>
       </c>
       <c r="H52" s="15">
         <f t="shared" si="4"/>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I52" s="16">
         <f t="shared" si="5"/>
-        <v>2.0072930800542741</v>
+        <v>2.1041383989145181</v>
       </c>
       <c r="J52" s="17"/>
     </row>
@@ -2738,31 +2738,31 @@
         <v>68</v>
       </c>
       <c r="B61" s="19">
-        <v>93.41</v>
+        <v>40.44</v>
       </c>
       <c r="C61" s="20">
-        <v>4212</v>
+        <v>2957</v>
       </c>
       <c r="D61" s="21">
-        <v>9600</v>
+        <v>9658</v>
       </c>
       <c r="E61" s="21">
-        <v>8252</v>
+        <v>8939</v>
       </c>
       <c r="F61" s="21">
-        <v>539</v>
+        <v>2698</v>
       </c>
       <c r="G61" s="22">
         <f t="shared" si="3"/>
-        <v>9.6</v>
+        <v>9.6579999999999995</v>
       </c>
       <c r="H61" s="22">
         <f t="shared" si="4"/>
-        <v>8.2520000000000007</v>
+        <v>8.9390000000000001</v>
       </c>
       <c r="I61" s="23">
         <f t="shared" si="5"/>
-        <v>17.810760667903526</v>
+        <v>3.5796886582653817</v>
       </c>
       <c r="J61" s="24"/>
     </row>
@@ -2771,130 +2771,130 @@
         <v>69</v>
       </c>
       <c r="B62" s="19">
-        <v>30.12</v>
+        <v>93.41</v>
       </c>
       <c r="C62" s="20">
-        <v>2592</v>
+        <v>4212</v>
       </c>
       <c r="D62" s="21">
-        <v>9450</v>
+        <v>9600</v>
       </c>
       <c r="E62" s="21">
-        <v>8286</v>
+        <v>8252</v>
       </c>
       <c r="F62" s="21">
-        <v>929</v>
+        <v>539</v>
       </c>
       <c r="G62" s="22">
         <f t="shared" si="3"/>
-        <v>9.4499999999999993</v>
+        <v>9.6</v>
       </c>
       <c r="H62" s="22">
         <f t="shared" si="4"/>
-        <v>8.2859999999999996</v>
+        <v>8.2520000000000007</v>
       </c>
       <c r="I62" s="23">
         <f t="shared" si="5"/>
+        <v>17.810760667903526</v>
+      </c>
+      <c r="J62" s="24"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="19">
+        <v>30.12</v>
+      </c>
+      <c r="C63" s="20">
+        <v>2592</v>
+      </c>
+      <c r="D63" s="21">
+        <v>9450</v>
+      </c>
+      <c r="E63" s="21">
+        <v>8286</v>
+      </c>
+      <c r="F63" s="21">
+        <v>929</v>
+      </c>
+      <c r="G63" s="22">
+        <f t="shared" si="3"/>
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="H63" s="22">
+        <f t="shared" si="4"/>
+        <v>8.2859999999999996</v>
+      </c>
+      <c r="I63" s="23">
+        <f t="shared" si="5"/>
         <v>10.172228202368137</v>
       </c>
-      <c r="J62" s="24"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="5">
+      <c r="J63" s="24"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="12">
         <v>46.34</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C64" s="13">
         <v>2872</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D64" s="14">
         <v>8982</v>
       </c>
-      <c r="E63" s="7">
+      <c r="E64" s="14">
         <v>7133</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F64" s="14">
         <v>5202</v>
       </c>
-      <c r="G63" s="8">
+      <c r="G64" s="15">
         <f t="shared" si="3"/>
         <v>8.9819999999999993</v>
       </c>
-      <c r="H63" s="8">
+      <c r="H64" s="15">
         <f t="shared" si="4"/>
         <v>7.133</v>
       </c>
-      <c r="I63" s="9">
+      <c r="I64" s="16">
         <f t="shared" si="5"/>
         <v>1.726643598615917</v>
       </c>
-      <c r="J63" s="10"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="19">
-        <v>286.07</v>
-      </c>
-      <c r="C64" s="20">
-        <v>6866</v>
-      </c>
-      <c r="D64" s="21">
-        <v>8739</v>
-      </c>
-      <c r="E64" s="21">
-        <v>5244</v>
-      </c>
-      <c r="F64" s="21">
-        <v>2661</v>
-      </c>
-      <c r="G64" s="22">
-        <f t="shared" si="3"/>
-        <v>8.7390000000000008</v>
-      </c>
-      <c r="H64" s="22">
-        <f t="shared" si="4"/>
-        <v>5.2439999999999998</v>
-      </c>
-      <c r="I64" s="23">
-        <f t="shared" si="5"/>
-        <v>3.2841037204058625</v>
-      </c>
-      <c r="J64" s="24"/>
+      <c r="J64" s="17"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
         <v>72</v>
       </c>
       <c r="B65" s="19">
-        <v>39.74</v>
+        <v>286.07</v>
       </c>
       <c r="C65" s="20">
-        <v>3355</v>
+        <v>6866</v>
       </c>
       <c r="D65" s="21">
-        <v>8286</v>
+        <v>8739</v>
       </c>
       <c r="E65" s="21">
-        <v>7283</v>
+        <v>5244</v>
       </c>
       <c r="F65" s="21">
-        <v>1816</v>
+        <v>2661</v>
       </c>
       <c r="G65" s="22">
         <f t="shared" si="3"/>
-        <v>8.2859999999999996</v>
+        <v>8.7390000000000008</v>
       </c>
       <c r="H65" s="22">
         <f t="shared" si="4"/>
-        <v>7.2830000000000004</v>
+        <v>5.2439999999999998</v>
       </c>
       <c r="I65" s="23">
         <f t="shared" si="5"/>
-        <v>4.5627753303964758</v>
+        <v>3.2841037204058625</v>
       </c>
       <c r="J65" s="24"/>
     </row>
@@ -2903,19 +2903,19 @@
         <v>73</v>
       </c>
       <c r="B66" s="19">
-        <v>72.52</v>
+        <v>39.74</v>
       </c>
       <c r="C66" s="20">
-        <v>3558</v>
+        <v>3355</v>
       </c>
       <c r="D66" s="21">
         <v>8286</v>
       </c>
       <c r="E66" s="21">
-        <v>6044</v>
+        <v>7283</v>
       </c>
       <c r="F66" s="21">
-        <v>1840</v>
+        <v>1816</v>
       </c>
       <c r="G66" s="22">
         <f t="shared" si="3"/>
@@ -2923,11 +2923,11 @@
       </c>
       <c r="H66" s="22">
         <f t="shared" si="4"/>
-        <v>6.0439999999999996</v>
+        <v>7.2830000000000004</v>
       </c>
       <c r="I66" s="23">
         <f t="shared" si="5"/>
-        <v>4.5032608695652172</v>
+        <v>4.5627753303964758</v>
       </c>
       <c r="J66" s="24"/>
     </row>
@@ -2936,31 +2936,31 @@
         <v>74</v>
       </c>
       <c r="B67" s="19">
-        <v>159.81</v>
+        <v>72.52</v>
       </c>
       <c r="C67" s="20">
-        <v>5989</v>
+        <v>3558</v>
       </c>
       <c r="D67" s="21">
-        <v>5271</v>
+        <v>8286</v>
       </c>
       <c r="E67" s="21">
-        <v>3243</v>
+        <v>6044</v>
       </c>
       <c r="F67" s="21">
-        <v>623</v>
+        <v>1840</v>
       </c>
       <c r="G67" s="22">
         <f t="shared" si="3"/>
-        <v>5.2709999999999999</v>
+        <v>8.2859999999999996</v>
       </c>
       <c r="H67" s="22">
         <f t="shared" si="4"/>
-        <v>3.2429999999999999</v>
+        <v>6.0439999999999996</v>
       </c>
       <c r="I67" s="23">
         <f t="shared" si="5"/>
-        <v>8.4606741573033712</v>
+        <v>4.5032608695652172</v>
       </c>
       <c r="J67" s="24"/>
     </row>
@@ -2969,161 +2969,163 @@
         <v>75</v>
       </c>
       <c r="B68" s="19">
-        <v>110.29</v>
+        <v>159.81</v>
       </c>
       <c r="C68" s="20">
-        <v>5351</v>
+        <v>5989</v>
       </c>
       <c r="D68" s="21">
-        <v>4395</v>
+        <v>5271</v>
       </c>
       <c r="E68" s="21">
-        <v>616</v>
+        <v>3243</v>
       </c>
       <c r="F68" s="21">
-        <v>172</v>
+        <v>623</v>
       </c>
       <c r="G68" s="22">
         <f t="shared" si="3"/>
-        <v>4.3949999999999996</v>
+        <v>5.2709999999999999</v>
       </c>
       <c r="H68" s="22">
         <f t="shared" si="4"/>
-        <v>0.61599999999999999</v>
+        <v>3.2429999999999999</v>
       </c>
       <c r="I68" s="23">
         <f t="shared" si="5"/>
-        <v>25.552325581395348</v>
+        <v>8.4606741573033712</v>
       </c>
       <c r="J68" s="24"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="18" t="s">
+      <c r="A69" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="19">
-        <v>29.65</v>
-      </c>
-      <c r="C69" s="20">
-        <v>2527</v>
-      </c>
-      <c r="D69" s="21">
-        <v>1536</v>
-      </c>
-      <c r="E69" s="21">
-        <v>266</v>
-      </c>
-      <c r="F69" s="21">
-        <v>250</v>
-      </c>
-      <c r="G69" s="22">
+      <c r="B69" s="5">
+        <v>36.46</v>
+      </c>
+      <c r="C69" s="6">
+        <v>2605</v>
+      </c>
+      <c r="D69" s="7">
+        <v>4420</v>
+      </c>
+      <c r="E69" s="7">
+        <v>4380</v>
+      </c>
+      <c r="F69" s="7">
+        <v>3603</v>
+      </c>
+      <c r="G69" s="8">
         <f t="shared" si="3"/>
-        <v>1.536</v>
-      </c>
-      <c r="H69" s="22">
+        <v>4.42</v>
+      </c>
+      <c r="H69" s="8">
         <f t="shared" si="4"/>
-        <v>0.26600000000000001</v>
-      </c>
-      <c r="I69" s="23">
+        <v>4.38</v>
+      </c>
+      <c r="I69" s="9">
         <f t="shared" si="5"/>
-        <v>6.1440000000000001</v>
-      </c>
-      <c r="J69" s="24"/>
+        <v>1.2267554815431585</v>
+      </c>
+      <c r="J69" s="10"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
         <v>77</v>
       </c>
       <c r="B70" s="19">
-        <v>33.869999999999997</v>
+        <v>110.29</v>
       </c>
       <c r="C70" s="20">
-        <v>2696</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" s="25" t="s">
-        <v>78</v>
+        <v>5351</v>
+      </c>
+      <c r="D70" s="21">
+        <v>4395</v>
+      </c>
+      <c r="E70" s="21">
+        <v>616</v>
       </c>
       <c r="F70" s="21">
-        <v>3966</v>
-      </c>
-      <c r="G70" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="H70" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="I70" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="J70" s="28" t="s">
-        <v>80</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G70" s="22">
+        <f t="shared" si="3"/>
+        <v>4.3949999999999996</v>
+      </c>
+      <c r="H70" s="22">
+        <f t="shared" si="4"/>
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="I70" s="23">
+        <f t="shared" si="5"/>
+        <v>25.552325581395348</v>
+      </c>
+      <c r="J70" s="24"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B71" s="19">
-        <v>40.44</v>
+        <v>29.65</v>
       </c>
       <c r="C71" s="20">
-        <v>2957</v>
-      </c>
-      <c r="D71" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="E71" s="25" t="s">
-        <v>78</v>
+        <v>2527</v>
+      </c>
+      <c r="D71" s="21">
+        <v>1536</v>
+      </c>
+      <c r="E71" s="21">
+        <v>266</v>
       </c>
       <c r="F71" s="21">
-        <v>2698</v>
-      </c>
-      <c r="G71" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="H71" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="I71" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="J71" s="28" t="s">
-        <v>80</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G71" s="22">
+        <f t="shared" si="3"/>
+        <v>1.536</v>
+      </c>
+      <c r="H71" s="22">
+        <f t="shared" si="4"/>
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="I71" s="23">
+        <f t="shared" si="5"/>
+        <v>6.1440000000000001</v>
+      </c>
+      <c r="J71" s="24"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="19">
+        <v>33.869999999999997</v>
+      </c>
+      <c r="C72" s="20">
+        <v>2696</v>
+      </c>
+      <c r="D72" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E72" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="F72" s="21">
+        <v>3966</v>
+      </c>
+      <c r="G72" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="H72" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="I72" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="J72" s="28" t="s">
         <v>82</v>
-      </c>
-      <c r="B72" s="19">
-        <v>36.46</v>
-      </c>
-      <c r="C72" s="20">
-        <v>2605</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="E72" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="F72" s="21">
-        <v>3603</v>
-      </c>
-      <c r="G72" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="H72" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="I72" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="J72" s="28" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
@@ -3137,25 +3139,25 @@
         <v>2528</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E73" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F73" s="21">
         <v>13714</v>
       </c>
       <c r="G73" s="26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H73" s="26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I73" s="27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J73" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
@@ -3169,25 +3171,25 @@
         <v>1056</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E74" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F74" s="21">
         <v>3969</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I74" s="27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J74" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
@@ -3208,7 +3210,7 @@
       </c>
       <c r="I76" s="33">
         <f>IFERROR(AVERAGE(I5:I74),"")</f>
-        <v>3.7325692574407903</v>
+        <v>3.6943327043629872</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6127F424-DF2F-4FDD-A9A9-DD8F78712100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AA9C28-4097-4C83-B23F-B0C60904FFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,24 +72,27 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-39A</t>
+  </si>
+  <si>
+    <t>T-39</t>
+  </si>
+  <si>
+    <t>T-39D</t>
+  </si>
+  <si>
+    <t>T-40A</t>
+  </si>
+  <si>
     <t>T-41A</t>
   </si>
   <si>
-    <t>T-39</t>
-  </si>
-  <si>
-    <t>T-39D</t>
-  </si>
-  <si>
-    <t>T-39A</t>
-  </si>
-  <si>
-    <t>T-40A</t>
-  </si>
-  <si>
     <t>T-40B</t>
   </si>
   <si>
+    <t>T-35</t>
+  </si>
+  <si>
     <t>T-39C</t>
   </si>
   <si>
@@ -99,39 +102,36 @@
     <t>T-37B</t>
   </si>
   <si>
-    <t>T-35</t>
+    <t>T-37</t>
   </si>
   <si>
     <t>T-38C</t>
   </si>
   <si>
-    <t>T-37</t>
-  </si>
-  <si>
     <t>T-39B</t>
   </si>
   <si>
     <t>T-36A</t>
   </si>
   <si>
+    <t>T-36</t>
+  </si>
+  <si>
     <t>T-41B</t>
   </si>
   <si>
-    <t>T-36</t>
-  </si>
-  <si>
     <t>T-38A</t>
   </si>
   <si>
     <t>T-38B</t>
   </si>
   <si>
+    <t>T-34</t>
+  </si>
+  <si>
     <t>T-36B</t>
   </si>
   <si>
-    <t>T-34</t>
-  </si>
-  <si>
     <t>T-36C</t>
   </si>
   <si>
@@ -141,30 +141,33 @@
     <t>T-33A</t>
   </si>
   <si>
+    <t>T-33B</t>
+  </si>
+  <si>
+    <t>T-33D</t>
+  </si>
+  <si>
+    <t>T-32A</t>
+  </si>
+  <si>
     <t>T-33C</t>
   </si>
   <si>
     <t>T-33F</t>
   </si>
   <si>
-    <t>T-33B</t>
+    <t>T-32B</t>
   </si>
   <si>
     <t>T-33E</t>
   </si>
   <si>
-    <t>T-33D</t>
-  </si>
-  <si>
-    <t>T-32A</t>
-  </si>
-  <si>
-    <t>T-32B</t>
-  </si>
-  <si>
     <t>T-32C</t>
   </si>
   <si>
+    <t>T-32</t>
+  </si>
+  <si>
     <t>T-29B</t>
   </si>
   <si>
@@ -177,9 +180,6 @@
     <t>T-30C</t>
   </si>
   <si>
-    <t>T-32</t>
-  </si>
-  <si>
     <t>T-30D</t>
   </si>
   <si>
@@ -189,15 +189,15 @@
     <t>T-29C</t>
   </si>
   <si>
+    <t>T-26B</t>
+  </si>
+  <si>
+    <t>T-26C</t>
+  </si>
+  <si>
     <t>T-30B</t>
   </si>
   <si>
-    <t>T-26B</t>
-  </si>
-  <si>
-    <t>T-26C</t>
-  </si>
-  <si>
     <t>T-27B</t>
   </si>
   <si>
@@ -219,49 +219,49 @@
     <t>T-05C</t>
   </si>
   <si>
+    <t>T-22</t>
+  </si>
+  <si>
+    <t>T-05B</t>
+  </si>
+  <si>
+    <t>T-21</t>
+  </si>
+  <si>
+    <t>T-05A</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-06B</t>
+  </si>
+  <si>
+    <t>T-16</t>
+  </si>
+  <si>
+    <t>T-06A</t>
+  </si>
+  <si>
+    <t>T-07B</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-02</t>
+  </si>
+  <si>
     <t>T-09</t>
   </si>
   <si>
     <t>T-10B</t>
-  </si>
-  <si>
-    <t>T-05B</t>
-  </si>
-  <si>
-    <t>T-22</t>
-  </si>
-  <si>
-    <t>T-05A</t>
-  </si>
-  <si>
-    <t>T-21</t>
-  </si>
-  <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>T-06B</t>
-  </si>
-  <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-16</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-06A</t>
-  </si>
-  <si>
-    <t>T-07B</t>
-  </si>
-  <si>
-    <t>T-02</t>
   </si>
   <si>
     <t>T-06C</t>
@@ -890,31 +890,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>150.53</v>
+        <v>34.07</v>
       </c>
       <c r="C5" s="6">
-        <v>4897</v>
+        <v>2376</v>
       </c>
       <c r="D5" s="7">
-        <v>27435</v>
+        <v>25675</v>
       </c>
       <c r="E5" s="7">
-        <v>23541</v>
+        <v>24111</v>
       </c>
       <c r="F5" s="7">
-        <v>12769</v>
+        <v>15101</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" ref="G5:G36" si="0">D5/1000</f>
-        <v>27.434999999999999</v>
+        <v>25.675000000000001</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" ref="H5:H36" si="1">E5/1000</f>
-        <v>23.541</v>
+        <v>24.111000000000001</v>
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:I36" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.1485629258360093</v>
+        <v>1.7002185285742666</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -929,25 +929,25 @@
         <v>4267</v>
       </c>
       <c r="D6" s="14">
-        <v>26407</v>
+        <v>25605</v>
       </c>
       <c r="E6" s="14">
-        <v>26038</v>
+        <v>25190</v>
       </c>
       <c r="F6" s="14">
         <v>14390</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>26.407</v>
+        <v>25.605</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>26.038</v>
+        <v>25.19</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>1.8350938151494094</v>
+        <v>1.7793606671299513</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -962,25 +962,25 @@
         <v>2148</v>
       </c>
       <c r="D7" s="7">
-        <v>26407</v>
+        <v>25605</v>
       </c>
       <c r="E7" s="7">
-        <v>25636</v>
+        <v>24897</v>
       </c>
       <c r="F7" s="7">
         <v>14710</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>26.407</v>
+        <v>25.605</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>25.635999999999999</v>
+        <v>24.896999999999998</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>1.7951733514615908</v>
+        <v>1.7406526172671652</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -989,31 +989,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="12">
-        <v>34.07</v>
+        <v>85.18</v>
       </c>
       <c r="C8" s="13">
-        <v>2376</v>
+        <v>3658</v>
       </c>
       <c r="D8" s="14">
-        <v>26192</v>
+        <v>25277</v>
       </c>
       <c r="E8" s="14">
-        <v>24848</v>
+        <v>24284</v>
       </c>
       <c r="F8" s="14">
-        <v>15101</v>
+        <v>13732</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>26.192</v>
+        <v>25.277000000000001</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>24.847999999999999</v>
+        <v>24.283999999999999</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>1.7344546718760347</v>
+        <v>1.8407369647538596</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -1022,31 +1022,31 @@
         <v>16</v>
       </c>
       <c r="B9" s="5">
-        <v>85.18</v>
+        <v>150.53</v>
       </c>
       <c r="C9" s="6">
-        <v>3658</v>
+        <v>4897</v>
       </c>
       <c r="D9" s="7">
-        <v>26016</v>
+        <v>25277</v>
       </c>
       <c r="E9" s="7">
-        <v>25022</v>
+        <v>22802</v>
       </c>
       <c r="F9" s="7">
-        <v>13732</v>
+        <v>12769</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>26.015999999999998</v>
+        <v>25.277000000000001</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>25.021999999999998</v>
+        <v>22.802</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>1.8945528692106031</v>
+        <v>1.979559871563944</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -1061,25 +1061,25 @@
         <v>2363</v>
       </c>
       <c r="D10" s="14">
-        <v>25840</v>
+        <v>25101</v>
       </c>
       <c r="E10" s="14">
-        <v>25661</v>
+        <v>24922</v>
       </c>
       <c r="F10" s="14">
         <v>14034</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>25.84</v>
+        <v>25.100999999999999</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>25.661000000000001</v>
+        <v>24.922000000000001</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>1.8412426963089639</v>
+        <v>1.7885848653270628</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -1088,31 +1088,31 @@
         <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>20.03</v>
+        <v>240.66</v>
       </c>
       <c r="C11" s="6">
-        <v>1858</v>
+        <v>6211</v>
       </c>
       <c r="D11" s="7">
-        <v>25687</v>
+        <v>24958</v>
       </c>
       <c r="E11" s="7">
-        <v>25174</v>
+        <v>22107</v>
       </c>
       <c r="F11" s="7">
-        <v>14553</v>
+        <v>16499</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
-        <v>25.687000000000001</v>
+        <v>24.957999999999998</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="1"/>
-        <v>25.173999999999999</v>
+        <v>22.106999999999999</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="2"/>
-        <v>1.7650656222084793</v>
+        <v>1.5126977392569247</v>
       </c>
       <c r="J11" s="10"/>
     </row>
@@ -1121,31 +1121,31 @@
         <v>19</v>
       </c>
       <c r="B12" s="12">
-        <v>85.99</v>
+        <v>20.03</v>
       </c>
       <c r="C12" s="13">
-        <v>4182</v>
+        <v>1858</v>
       </c>
       <c r="D12" s="14">
-        <v>25525</v>
+        <v>24948</v>
       </c>
       <c r="E12" s="14">
-        <v>25269</v>
+        <v>24436</v>
       </c>
       <c r="F12" s="14">
-        <v>15781</v>
+        <v>14553</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>25.524999999999999</v>
+        <v>24.948</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
-        <v>25.268999999999998</v>
+        <v>24.436</v>
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>1.6174513655661873</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1154,31 +1154,31 @@
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>108.01</v>
+        <v>85.99</v>
       </c>
       <c r="C13" s="6">
-        <v>4183</v>
+        <v>4182</v>
       </c>
       <c r="D13" s="7">
-        <v>25298</v>
+        <v>24787</v>
       </c>
       <c r="E13" s="7">
-        <v>24081</v>
+        <v>24530</v>
       </c>
       <c r="F13" s="7">
-        <v>15031</v>
+        <v>15781</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>25.297999999999998</v>
+        <v>24.786999999999999</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>24.081</v>
+        <v>24.53</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>1.683055019626106</v>
+        <v>1.5706862682973195</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1187,31 +1187,31 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>240.66</v>
+        <v>108.01</v>
       </c>
       <c r="C14" s="13">
-        <v>6211</v>
+        <v>4183</v>
       </c>
       <c r="D14" s="14">
-        <v>25219</v>
+        <v>24560</v>
       </c>
       <c r="E14" s="14">
-        <v>22107</v>
+        <v>23343</v>
       </c>
       <c r="F14" s="14">
-        <v>16499</v>
+        <v>15031</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>25.219000000000001</v>
+        <v>24.56</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>22.106999999999999</v>
+        <v>23.343</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>1.5285168798108977</v>
+        <v>1.6339564899208303</v>
       </c>
       <c r="J14" s="17"/>
     </row>
@@ -1220,31 +1220,31 @@
         <v>22</v>
       </c>
       <c r="B15" s="5">
-        <v>27.75</v>
+        <v>182.45</v>
       </c>
       <c r="C15" s="6">
-        <v>2368</v>
+        <v>5565</v>
       </c>
       <c r="D15" s="7">
-        <v>25149</v>
+        <v>24469</v>
       </c>
       <c r="E15" s="7">
-        <v>24335</v>
+        <v>22963</v>
       </c>
       <c r="F15" s="7">
-        <v>14263</v>
+        <v>15705</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
-        <v>25.149000000000001</v>
+        <v>24.469000000000001</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>24.335000000000001</v>
+        <v>22.963000000000001</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
-        <v>1.7632335413307159</v>
+        <v>1.558038841133397</v>
       </c>
       <c r="J15" s="10"/>
     </row>
@@ -1253,31 +1253,31 @@
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>182.45</v>
+        <v>27.75</v>
       </c>
       <c r="C16" s="13">
-        <v>5565</v>
+        <v>2368</v>
       </c>
       <c r="D16" s="14">
-        <v>24974</v>
+        <v>24411</v>
       </c>
       <c r="E16" s="14">
-        <v>23468</v>
+        <v>23597</v>
       </c>
       <c r="F16" s="14">
-        <v>15705</v>
+        <v>14263</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>24.974</v>
+        <v>24.411000000000001</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>23.468</v>
+        <v>23.597000000000001</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>1.5901942056669851</v>
+        <v>1.7114912711210826</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1292,25 +1292,25 @@
         <v>2143</v>
       </c>
       <c r="D17" s="7">
-        <v>24901</v>
+        <v>24165</v>
       </c>
       <c r="E17" s="7">
-        <v>24366</v>
+        <v>23627</v>
       </c>
       <c r="F17" s="7">
         <v>14837</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>24.901</v>
+        <v>24.164999999999999</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>24.366</v>
+        <v>23.626999999999999</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>1.6783042394014962</v>
+        <v>1.6286985239603693</v>
       </c>
       <c r="J17" s="10"/>
     </row>
@@ -1325,25 +1325,25 @@
         <v>2563</v>
       </c>
       <c r="D18" s="14">
-        <v>24731</v>
+        <v>24117</v>
       </c>
       <c r="E18" s="14">
-        <v>23574</v>
+        <v>22836</v>
       </c>
       <c r="F18" s="14">
         <v>14740</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>24.731000000000002</v>
+        <v>24.117000000000001</v>
       </c>
       <c r="H18" s="15">
         <f t="shared" si="1"/>
-        <v>23.574000000000002</v>
+        <v>22.835999999999999</v>
       </c>
       <c r="I18" s="16">
         <f t="shared" si="2"/>
-        <v>1.6778154681139756</v>
+        <v>1.6361601085481683</v>
       </c>
       <c r="J18" s="17"/>
     </row>
@@ -1352,31 +1352,31 @@
         <v>26</v>
       </c>
       <c r="B19" s="5">
-        <v>38.03</v>
+        <v>93.86</v>
       </c>
       <c r="C19" s="6">
-        <v>2973</v>
+        <v>4450</v>
       </c>
       <c r="D19" s="7">
-        <v>24672</v>
+        <v>24038</v>
       </c>
       <c r="E19" s="7">
-        <v>23734</v>
+        <v>21081</v>
       </c>
       <c r="F19" s="7">
-        <v>12971</v>
+        <v>14968</v>
       </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
-        <v>24.672000000000001</v>
+        <v>24.038</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>23.734000000000002</v>
+        <v>21.081</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
-        <v>1.9020892760774035</v>
+        <v>1.6059593800106895</v>
       </c>
       <c r="J19" s="10"/>
     </row>
@@ -1385,31 +1385,31 @@
         <v>27</v>
       </c>
       <c r="B20" s="12">
-        <v>93.86</v>
+        <v>38.03</v>
       </c>
       <c r="C20" s="13">
-        <v>4450</v>
+        <v>2973</v>
       </c>
       <c r="D20" s="14">
-        <v>24543</v>
+        <v>23934</v>
       </c>
       <c r="E20" s="14">
-        <v>21794</v>
+        <v>22996</v>
       </c>
       <c r="F20" s="14">
-        <v>14968</v>
+        <v>12971</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>24.542999999999999</v>
+        <v>23.934000000000001</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>21.794</v>
+        <v>22.995999999999999</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>1.6396980224478888</v>
+        <v>1.8451931231208079</v>
       </c>
       <c r="J20" s="17"/>
     </row>
@@ -1424,25 +1424,25 @@
         <v>3201</v>
       </c>
       <c r="D21" s="7">
-        <v>24335</v>
+        <v>23597</v>
       </c>
       <c r="E21" s="7">
-        <v>22619</v>
+        <v>21881</v>
       </c>
       <c r="F21" s="7">
         <v>13857</v>
       </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
-        <v>24.335000000000001</v>
+        <v>23.597000000000001</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="1"/>
-        <v>22.619</v>
+        <v>21.881</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="2"/>
-        <v>1.7561521252796422</v>
+        <v>1.7028938442664356</v>
       </c>
       <c r="J21" s="10"/>
     </row>
@@ -1457,25 +1457,25 @@
         <v>2313</v>
       </c>
       <c r="D22" s="14">
-        <v>24135</v>
+        <v>23396</v>
       </c>
       <c r="E22" s="14">
-        <v>23397</v>
+        <v>22658</v>
       </c>
       <c r="F22" s="14">
         <v>14244</v>
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>24.135000000000002</v>
+        <v>23.396000000000001</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
-        <v>23.396999999999998</v>
+        <v>22.658000000000001</v>
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.6943976411120472</v>
+        <v>1.642516147149677</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1484,31 +1484,31 @@
         <v>30</v>
       </c>
       <c r="B23" s="5">
-        <v>39.71</v>
+        <v>228.96</v>
       </c>
       <c r="C23" s="6">
-        <v>2648</v>
+        <v>6152</v>
       </c>
       <c r="D23" s="7">
-        <v>23624</v>
+        <v>23253</v>
       </c>
       <c r="E23" s="7">
-        <v>23016</v>
+        <v>20237</v>
       </c>
       <c r="F23" s="7">
-        <v>14442</v>
+        <v>15117</v>
       </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
-        <v>23.623999999999999</v>
+        <v>23.253</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="1"/>
-        <v>23.015999999999998</v>
+        <v>20.236999999999998</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="2"/>
-        <v>1.6357845173798642</v>
+        <v>1.5382020242111529</v>
       </c>
       <c r="J23" s="10"/>
     </row>
@@ -1517,31 +1517,31 @@
         <v>31</v>
       </c>
       <c r="B24" s="12">
-        <v>228.96</v>
+        <v>39.71</v>
       </c>
       <c r="C24" s="13">
-        <v>6152</v>
+        <v>2648</v>
       </c>
       <c r="D24" s="14">
-        <v>23514</v>
+        <v>22885</v>
       </c>
       <c r="E24" s="14">
-        <v>20237</v>
+        <v>22278</v>
       </c>
       <c r="F24" s="14">
-        <v>15117</v>
+        <v>14442</v>
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>23.513999999999999</v>
+        <v>22.885000000000002</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
-        <v>20.236999999999998</v>
+        <v>22.277999999999999</v>
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.555467354633856</v>
+        <v>1.5846143193463509</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1556,25 +1556,25 @@
         <v>3171</v>
       </c>
       <c r="D25" s="7">
-        <v>23067</v>
+        <v>22329</v>
       </c>
       <c r="E25" s="7">
-        <v>21668</v>
+        <v>20929</v>
       </c>
       <c r="F25" s="7">
         <v>14233</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>23.067</v>
+        <v>22.329000000000001</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>21.667999999999999</v>
+        <v>20.928999999999998</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>1.6206702733085083</v>
+        <v>1.5688189418955947</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1589,25 +1589,25 @@
         <v>5526</v>
       </c>
       <c r="D26" s="14">
-        <v>23040</v>
+        <v>21563</v>
       </c>
       <c r="E26" s="14">
-        <v>20154</v>
+        <v>18739</v>
       </c>
       <c r="F26" s="14">
         <v>13729</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>23.04</v>
+        <v>21.562999999999999</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>20.154</v>
+        <v>18.739000000000001</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>1.6781994318595674</v>
+        <v>1.5706169422390559</v>
       </c>
       <c r="J26" s="17"/>
     </row>
@@ -1622,25 +1622,25 @@
         <v>2599</v>
       </c>
       <c r="D27" s="7">
-        <v>21924</v>
+        <v>21563</v>
       </c>
       <c r="E27" s="7">
-        <v>20654</v>
+        <v>20518</v>
       </c>
       <c r="F27" s="7">
         <v>14141</v>
       </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
-        <v>21.923999999999999</v>
+        <v>21.562999999999999</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>20.654</v>
+        <v>20.518000000000001</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
-        <v>1.5503854041439784</v>
+        <v>1.524856799377696</v>
       </c>
       <c r="J27" s="10"/>
     </row>
@@ -1649,31 +1649,31 @@
         <v>35</v>
       </c>
       <c r="B28" s="12">
-        <v>17.32</v>
+        <v>28.89</v>
       </c>
       <c r="C28" s="13">
-        <v>1739</v>
+        <v>2630</v>
       </c>
       <c r="D28" s="14">
-        <v>20930</v>
+        <v>20736</v>
       </c>
       <c r="E28" s="14">
-        <v>20583</v>
+        <v>20154</v>
       </c>
       <c r="F28" s="14">
-        <v>13605</v>
+        <v>13724</v>
       </c>
       <c r="G28" s="15">
         <f t="shared" si="0"/>
-        <v>20.93</v>
+        <v>20.736000000000001</v>
       </c>
       <c r="H28" s="15">
         <f t="shared" si="1"/>
-        <v>20.582999999999998</v>
+        <v>20.154</v>
       </c>
       <c r="I28" s="16">
         <f t="shared" si="2"/>
-        <v>1.5384049981624404</v>
+        <v>1.510929758088021</v>
       </c>
       <c r="J28" s="17"/>
     </row>
@@ -1682,31 +1682,31 @@
         <v>36</v>
       </c>
       <c r="B29" s="5">
-        <v>83.54</v>
+        <v>20.329999999999998</v>
       </c>
       <c r="C29" s="6">
-        <v>3934</v>
+        <v>1825</v>
       </c>
       <c r="D29" s="7">
-        <v>20930</v>
+        <v>20237</v>
       </c>
       <c r="E29" s="7">
-        <v>19687</v>
+        <v>19999</v>
       </c>
       <c r="F29" s="7">
-        <v>12932</v>
+        <v>13381</v>
       </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
-        <v>20.93</v>
+        <v>20.236999999999998</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="1"/>
-        <v>19.687000000000001</v>
+        <v>19.998999999999999</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="2"/>
-        <v>1.6184658212186824</v>
+        <v>1.5123682833868919</v>
       </c>
       <c r="J29" s="10"/>
     </row>
@@ -1715,31 +1715,31 @@
         <v>37</v>
       </c>
       <c r="B30" s="12">
-        <v>28.89</v>
+        <v>49.81</v>
       </c>
       <c r="C30" s="13">
-        <v>2630</v>
+        <v>3183</v>
       </c>
       <c r="D30" s="14">
-        <v>20736</v>
+        <v>20210</v>
       </c>
       <c r="E30" s="14">
-        <v>20154</v>
+        <v>18504</v>
       </c>
       <c r="F30" s="14">
-        <v>13724</v>
+        <v>12736</v>
       </c>
       <c r="G30" s="15">
         <f t="shared" si="0"/>
-        <v>20.736000000000001</v>
+        <v>20.21</v>
       </c>
       <c r="H30" s="15">
         <f t="shared" si="1"/>
-        <v>20.154</v>
+        <v>18.504000000000001</v>
       </c>
       <c r="I30" s="16">
         <f t="shared" si="2"/>
-        <v>1.510929758088021</v>
+        <v>1.5868404522613064</v>
       </c>
       <c r="J30" s="17"/>
     </row>
@@ -1748,31 +1748,31 @@
         <v>38</v>
       </c>
       <c r="B31" s="5">
-        <v>25.66</v>
+        <v>17.32</v>
       </c>
       <c r="C31" s="6">
-        <v>2270</v>
+        <v>1739</v>
       </c>
       <c r="D31" s="7">
-        <v>20620</v>
+        <v>20192</v>
       </c>
       <c r="E31" s="7">
-        <v>19713</v>
+        <v>19845</v>
       </c>
       <c r="F31" s="7">
-        <v>13030</v>
+        <v>13605</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>20.62</v>
+        <v>20.192</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="1"/>
-        <v>19.713000000000001</v>
+        <v>19.844999999999999</v>
       </c>
       <c r="I31" s="9">
         <f t="shared" si="2"/>
-        <v>1.5825019186492708</v>
+        <v>1.4841602352076442</v>
       </c>
       <c r="J31" s="10"/>
     </row>
@@ -1781,31 +1781,31 @@
         <v>39</v>
       </c>
       <c r="B32" s="12">
-        <v>20.329999999999998</v>
+        <v>83.54</v>
       </c>
       <c r="C32" s="13">
-        <v>1825</v>
+        <v>3934</v>
       </c>
       <c r="D32" s="14">
-        <v>20237</v>
+        <v>20192</v>
       </c>
       <c r="E32" s="14">
-        <v>19999</v>
+        <v>18948</v>
       </c>
       <c r="F32" s="14">
-        <v>13381</v>
+        <v>12932</v>
       </c>
       <c r="G32" s="15">
         <f t="shared" si="0"/>
-        <v>20.236999999999998</v>
+        <v>20.192</v>
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>19.998999999999999</v>
+        <v>18.948</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
-        <v>1.5123682833868919</v>
+        <v>1.5613980822765234</v>
       </c>
       <c r="J32" s="17"/>
     </row>
@@ -1814,31 +1814,31 @@
         <v>40</v>
       </c>
       <c r="B33" s="5">
-        <v>49.81</v>
+        <v>56.22</v>
       </c>
       <c r="C33" s="6">
-        <v>3183</v>
+        <v>3219</v>
       </c>
       <c r="D33" s="7">
-        <v>20210</v>
+        <v>20061</v>
       </c>
       <c r="E33" s="7">
-        <v>18504</v>
+        <v>18953</v>
       </c>
       <c r="F33" s="7">
-        <v>12736</v>
+        <v>12386</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>20.21</v>
+        <v>20.061</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="1"/>
-        <v>18.504000000000001</v>
+        <v>18.952999999999999</v>
       </c>
       <c r="I33" s="9">
         <f t="shared" si="2"/>
-        <v>1.5868404522613064</v>
+        <v>1.6196512191183594</v>
       </c>
       <c r="J33" s="10"/>
     </row>
@@ -1847,31 +1847,31 @@
         <v>41</v>
       </c>
       <c r="B34" s="12">
-        <v>56.22</v>
+        <v>25.66</v>
       </c>
       <c r="C34" s="13">
-        <v>3219</v>
+        <v>2270</v>
       </c>
       <c r="D34" s="14">
-        <v>20061</v>
+        <v>19882</v>
       </c>
       <c r="E34" s="14">
-        <v>18953</v>
+        <v>18975</v>
       </c>
       <c r="F34" s="14">
-        <v>12386</v>
+        <v>13030</v>
       </c>
       <c r="G34" s="15">
         <f t="shared" si="0"/>
-        <v>20.061</v>
+        <v>19.882000000000001</v>
       </c>
       <c r="H34" s="15">
         <f t="shared" si="1"/>
-        <v>18.952999999999999</v>
+        <v>18.975000000000001</v>
       </c>
       <c r="I34" s="16">
         <f t="shared" si="2"/>
-        <v>1.6196512191183594</v>
+        <v>1.5258633921719109</v>
       </c>
       <c r="J34" s="17"/>
     </row>
@@ -1886,7 +1886,7 @@
         <v>3551</v>
       </c>
       <c r="D35" s="7">
-        <v>19862</v>
+        <v>19860</v>
       </c>
       <c r="E35" s="7">
         <v>19497</v>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>19.861999999999998</v>
+        <v>19.86</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="1"/>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I35" s="9">
         <f t="shared" si="2"/>
-        <v>1.6470685794842026</v>
+        <v>1.6469027282527573</v>
       </c>
       <c r="J35" s="10"/>
     </row>
@@ -1913,31 +1913,31 @@
         <v>43</v>
       </c>
       <c r="B36" s="12">
-        <v>51.46</v>
+        <v>82.03</v>
       </c>
       <c r="C36" s="13">
-        <v>3211</v>
+        <v>3674</v>
       </c>
       <c r="D36" s="14">
-        <v>19048</v>
+        <v>18789</v>
       </c>
       <c r="E36" s="14">
-        <v>18028</v>
+        <v>17738</v>
       </c>
       <c r="F36" s="14">
-        <v>10413</v>
+        <v>13042</v>
       </c>
       <c r="G36" s="15">
         <f t="shared" si="0"/>
-        <v>19.047999999999998</v>
+        <v>18.789000000000001</v>
       </c>
       <c r="H36" s="15">
         <f t="shared" si="1"/>
-        <v>18.027999999999999</v>
+        <v>17.738</v>
       </c>
       <c r="I36" s="16">
         <f t="shared" si="2"/>
-        <v>1.829251896667627</v>
+        <v>1.4406532740377243</v>
       </c>
       <c r="J36" s="17"/>
     </row>
@@ -1946,31 +1946,31 @@
         <v>44</v>
       </c>
       <c r="B37" s="5">
-        <v>204.97</v>
+        <v>51.46</v>
       </c>
       <c r="C37" s="6">
-        <v>6009</v>
+        <v>3211</v>
       </c>
       <c r="D37" s="7">
-        <v>19048</v>
+        <v>18310</v>
       </c>
       <c r="E37" s="7">
-        <v>16024</v>
+        <v>17289</v>
       </c>
       <c r="F37" s="7">
-        <v>9361</v>
+        <v>10413</v>
       </c>
       <c r="G37" s="8">
         <f t="shared" ref="G37:G71" si="3">D37/1000</f>
-        <v>19.047999999999998</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" ref="H37:H71" si="4">E37/1000</f>
-        <v>16.024000000000001</v>
+        <v>17.289000000000001</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" ref="I37:I71" si="5">IFERROR(D37/F37,"")</f>
-        <v>2.0348253391731652</v>
+        <v>1.7583789493901854</v>
       </c>
       <c r="J37" s="10"/>
     </row>
@@ -1979,31 +1979,31 @@
         <v>45</v>
       </c>
       <c r="B38" s="12">
-        <v>36.369999999999997</v>
+        <v>204.97</v>
       </c>
       <c r="C38" s="13">
-        <v>3031</v>
+        <v>6009</v>
       </c>
       <c r="D38" s="14">
-        <v>18804</v>
+        <v>18310</v>
       </c>
       <c r="E38" s="14">
-        <v>16952</v>
+        <v>15285</v>
       </c>
       <c r="F38" s="14">
-        <v>10293</v>
+        <v>9361</v>
       </c>
       <c r="G38" s="15">
         <f t="shared" si="3"/>
-        <v>18.803999999999998</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="H38" s="15">
         <f t="shared" si="4"/>
-        <v>16.952000000000002</v>
+        <v>15.285</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="5"/>
-        <v>1.8268726318857476</v>
+        <v>1.9559876081615213</v>
       </c>
       <c r="J38" s="17"/>
     </row>
@@ -2012,31 +2012,31 @@
         <v>46</v>
       </c>
       <c r="B39" s="5">
-        <v>135.69999999999999</v>
+        <v>36.369999999999997</v>
       </c>
       <c r="C39" s="6">
-        <v>5466</v>
+        <v>3031</v>
       </c>
       <c r="D39" s="7">
-        <v>18804</v>
+        <v>18065</v>
       </c>
       <c r="E39" s="7">
-        <v>16024</v>
+        <v>16213</v>
       </c>
       <c r="F39" s="7">
-        <v>9364</v>
+        <v>10293</v>
       </c>
       <c r="G39" s="8">
         <f t="shared" si="3"/>
-        <v>18.803999999999998</v>
+        <v>18.065000000000001</v>
       </c>
       <c r="H39" s="8">
         <f t="shared" si="4"/>
-        <v>16.024000000000001</v>
+        <v>16.213000000000001</v>
       </c>
       <c r="I39" s="9">
         <f t="shared" si="5"/>
-        <v>2.0081161896625375</v>
+        <v>1.7550762654231031</v>
       </c>
       <c r="J39" s="10"/>
     </row>
@@ -2045,31 +2045,31 @@
         <v>47</v>
       </c>
       <c r="B40" s="12">
-        <v>82.03</v>
+        <v>135.69999999999999</v>
       </c>
       <c r="C40" s="13">
-        <v>3674</v>
+        <v>5466</v>
       </c>
       <c r="D40" s="14">
-        <v>18789</v>
+        <v>18065</v>
       </c>
       <c r="E40" s="14">
-        <v>17734</v>
+        <v>15285</v>
       </c>
       <c r="F40" s="14">
-        <v>13042</v>
+        <v>9364</v>
       </c>
       <c r="G40" s="15">
         <f t="shared" si="3"/>
-        <v>18.789000000000001</v>
+        <v>18.065000000000001</v>
       </c>
       <c r="H40" s="15">
         <f t="shared" si="4"/>
-        <v>17.734000000000002</v>
+        <v>15.285</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="5"/>
-        <v>1.4406532740377243</v>
+        <v>1.9291969243912859</v>
       </c>
       <c r="J40" s="17"/>
     </row>
@@ -2084,25 +2084,25 @@
         <v>2417</v>
       </c>
       <c r="D41" s="7">
-        <v>18787</v>
+        <v>18048</v>
       </c>
       <c r="E41" s="7">
-        <v>17714</v>
+        <v>16975</v>
       </c>
       <c r="F41" s="7">
         <v>10355</v>
       </c>
       <c r="G41" s="8">
         <f t="shared" si="3"/>
-        <v>18.786999999999999</v>
+        <v>18.047999999999998</v>
       </c>
       <c r="H41" s="8">
         <f t="shared" si="4"/>
-        <v>17.713999999999999</v>
+        <v>16.975000000000001</v>
       </c>
       <c r="I41" s="9">
         <f t="shared" si="5"/>
-        <v>1.8142926122646064</v>
+        <v>1.7429261226460646</v>
       </c>
       <c r="J41" s="10"/>
     </row>
@@ -2117,25 +2117,25 @@
         <v>3294</v>
       </c>
       <c r="D42" s="14">
-        <v>18586</v>
+        <v>17847</v>
       </c>
       <c r="E42" s="14">
-        <v>17009</v>
+        <v>16271</v>
       </c>
       <c r="F42" s="14">
         <v>10324</v>
       </c>
       <c r="G42" s="15">
         <f t="shared" si="3"/>
-        <v>18.585999999999999</v>
+        <v>17.847000000000001</v>
       </c>
       <c r="H42" s="15">
         <f t="shared" si="4"/>
-        <v>17.009</v>
+        <v>16.271000000000001</v>
       </c>
       <c r="I42" s="16">
         <f t="shared" si="5"/>
-        <v>1.8002712127082525</v>
+        <v>1.7286904300658659</v>
       </c>
       <c r="J42" s="17"/>
     </row>
@@ -2150,25 +2150,25 @@
         <v>2710</v>
       </c>
       <c r="D43" s="7">
-        <v>18078</v>
+        <v>17339</v>
       </c>
       <c r="E43" s="7">
-        <v>16659</v>
+        <v>15920</v>
       </c>
       <c r="F43" s="7">
         <v>9510</v>
       </c>
       <c r="G43" s="8">
         <f t="shared" si="3"/>
-        <v>18.077999999999999</v>
+        <v>17.338999999999999</v>
       </c>
       <c r="H43" s="8">
         <f t="shared" si="4"/>
-        <v>16.658999999999999</v>
+        <v>15.92</v>
       </c>
       <c r="I43" s="9">
         <f t="shared" si="5"/>
-        <v>1.9009463722397477</v>
+        <v>1.8232386961093585</v>
       </c>
       <c r="J43" s="10"/>
     </row>
@@ -2177,31 +2177,31 @@
         <v>51</v>
       </c>
       <c r="B44" s="12">
-        <v>40.19</v>
+        <v>24.59</v>
       </c>
       <c r="C44" s="13">
-        <v>2657</v>
+        <v>3289</v>
       </c>
       <c r="D44" s="14">
-        <v>17009</v>
+        <v>16463</v>
       </c>
       <c r="E44" s="14">
-        <v>16024</v>
+        <v>15013</v>
       </c>
       <c r="F44" s="14">
-        <v>9367</v>
+        <v>8560</v>
       </c>
       <c r="G44" s="15">
         <f t="shared" si="3"/>
-        <v>17.009</v>
+        <v>16.463000000000001</v>
       </c>
       <c r="H44" s="15">
         <f t="shared" si="4"/>
-        <v>16.024000000000001</v>
+        <v>15.013</v>
       </c>
       <c r="I44" s="16">
         <f t="shared" si="5"/>
-        <v>1.8158428525675243</v>
+        <v>1.923247663551402</v>
       </c>
       <c r="J44" s="17"/>
     </row>
@@ -2210,31 +2210,31 @@
         <v>52</v>
       </c>
       <c r="B45" s="5">
-        <v>24.59</v>
+        <v>30.09</v>
       </c>
       <c r="C45" s="6">
-        <v>3289</v>
+        <v>3233</v>
       </c>
       <c r="D45" s="7">
-        <v>16873</v>
+        <v>16463</v>
       </c>
       <c r="E45" s="7">
-        <v>15752</v>
+        <v>15013</v>
       </c>
       <c r="F45" s="7">
-        <v>8560</v>
+        <v>8180</v>
       </c>
       <c r="G45" s="8">
         <f t="shared" si="3"/>
-        <v>16.873000000000001</v>
+        <v>16.463000000000001</v>
       </c>
       <c r="H45" s="8">
         <f t="shared" si="4"/>
-        <v>15.752000000000001</v>
+        <v>15.013</v>
       </c>
       <c r="I45" s="9">
         <f t="shared" si="5"/>
-        <v>1.9711448598130841</v>
+        <v>2.012591687041565</v>
       </c>
       <c r="J45" s="10"/>
     </row>
@@ -2243,31 +2243,31 @@
         <v>53</v>
       </c>
       <c r="B46" s="12">
-        <v>30.09</v>
+        <v>40.19</v>
       </c>
       <c r="C46" s="13">
-        <v>3233</v>
+        <v>2657</v>
       </c>
       <c r="D46" s="14">
-        <v>16873</v>
+        <v>16271</v>
       </c>
       <c r="E46" s="14">
-        <v>15752</v>
+        <v>15285</v>
       </c>
       <c r="F46" s="14">
-        <v>8180</v>
+        <v>9367</v>
       </c>
       <c r="G46" s="15">
         <f t="shared" si="3"/>
-        <v>16.873000000000001</v>
+        <v>16.271000000000001</v>
       </c>
       <c r="H46" s="15">
         <f t="shared" si="4"/>
-        <v>15.752000000000001</v>
+        <v>15.285</v>
       </c>
       <c r="I46" s="16">
         <f t="shared" si="5"/>
-        <v>2.0627139364303178</v>
+        <v>1.737055620796413</v>
       </c>
       <c r="J46" s="17"/>
     </row>
@@ -2282,25 +2282,25 @@
         <v>2114</v>
       </c>
       <c r="D47" s="7">
-        <v>15599</v>
+        <v>14860</v>
       </c>
       <c r="E47" s="7">
-        <v>15439</v>
+        <v>14700</v>
       </c>
       <c r="F47" s="7">
         <v>7664</v>
       </c>
       <c r="G47" s="8">
         <f t="shared" si="3"/>
-        <v>15.599</v>
+        <v>14.86</v>
       </c>
       <c r="H47" s="8">
         <f t="shared" si="4"/>
-        <v>15.439</v>
+        <v>14.7</v>
       </c>
       <c r="I47" s="9">
         <f t="shared" si="5"/>
-        <v>2.0353601252609606</v>
+        <v>1.9389352818371608</v>
       </c>
       <c r="J47" s="10"/>
     </row>
@@ -2315,25 +2315,25 @@
         <v>6277</v>
       </c>
       <c r="D48" s="14">
-        <v>15544</v>
+        <v>14805</v>
       </c>
       <c r="E48" s="14">
-        <v>14116</v>
+        <v>13377</v>
       </c>
       <c r="F48" s="14">
         <v>7560</v>
       </c>
       <c r="G48" s="15">
         <f t="shared" si="3"/>
-        <v>15.544</v>
+        <v>14.805</v>
       </c>
       <c r="H48" s="15">
         <f t="shared" si="4"/>
-        <v>14.116</v>
+        <v>13.377000000000001</v>
       </c>
       <c r="I48" s="16">
         <f t="shared" si="5"/>
-        <v>2.0560846560846562</v>
+        <v>1.9583333333333333</v>
       </c>
       <c r="J48" s="17"/>
     </row>
@@ -2348,25 +2348,25 @@
         <v>5695</v>
       </c>
       <c r="D49" s="7">
-        <v>15544</v>
+        <v>14805</v>
       </c>
       <c r="E49" s="7">
-        <v>14116</v>
+        <v>13377</v>
       </c>
       <c r="F49" s="7">
         <v>7303</v>
       </c>
       <c r="G49" s="8">
         <f t="shared" si="3"/>
-        <v>15.544</v>
+        <v>14.805</v>
       </c>
       <c r="H49" s="8">
         <f t="shared" si="4"/>
-        <v>14.116</v>
+        <v>13.377000000000001</v>
       </c>
       <c r="I49" s="9">
         <f t="shared" si="5"/>
-        <v>2.1284403669724772</v>
+        <v>2.0272490757223061</v>
       </c>
       <c r="J49" s="10"/>
     </row>
@@ -2381,25 +2381,25 @@
         <v>2414</v>
       </c>
       <c r="D50" s="14">
-        <v>15544</v>
+        <v>14805</v>
       </c>
       <c r="E50" s="14">
-        <v>14831</v>
+        <v>14092</v>
       </c>
       <c r="F50" s="14">
         <v>8238</v>
       </c>
       <c r="G50" s="15">
         <f t="shared" si="3"/>
-        <v>15.544</v>
+        <v>14.805</v>
       </c>
       <c r="H50" s="15">
         <f t="shared" si="4"/>
-        <v>14.831</v>
+        <v>14.092000000000001</v>
       </c>
       <c r="I50" s="16">
         <f t="shared" si="5"/>
-        <v>1.8868657441126486</v>
+        <v>1.7971595047341589</v>
       </c>
       <c r="J50" s="17"/>
     </row>
@@ -2414,25 +2414,25 @@
         <v>2895</v>
       </c>
       <c r="D51" s="7">
-        <v>15487</v>
+        <v>14749</v>
       </c>
       <c r="E51" s="7">
-        <v>14116</v>
+        <v>13377</v>
       </c>
       <c r="F51" s="7">
         <v>7306</v>
       </c>
       <c r="G51" s="8">
         <f t="shared" si="3"/>
-        <v>15.487</v>
+        <v>14.749000000000001</v>
       </c>
       <c r="H51" s="8">
         <f t="shared" si="4"/>
-        <v>14.116</v>
+        <v>13.377000000000001</v>
       </c>
       <c r="I51" s="9">
         <f t="shared" si="5"/>
-        <v>2.1197645770599509</v>
+        <v>2.0187517109225293</v>
       </c>
       <c r="J51" s="10"/>
     </row>
@@ -2447,25 +2447,25 @@
         <v>7672</v>
       </c>
       <c r="D52" s="14">
-        <v>12406</v>
+        <v>11569</v>
       </c>
       <c r="E52" s="14">
-        <v>8224</v>
+        <v>7485</v>
       </c>
       <c r="F52" s="14">
         <v>5896</v>
       </c>
       <c r="G52" s="15">
         <f t="shared" si="3"/>
-        <v>12.406000000000001</v>
+        <v>11.569000000000001</v>
       </c>
       <c r="H52" s="15">
         <f t="shared" si="4"/>
-        <v>8.2240000000000002</v>
+        <v>7.4850000000000003</v>
       </c>
       <c r="I52" s="16">
         <f t="shared" si="5"/>
-        <v>2.1041383989145181</v>
+        <v>1.9621777476255089</v>
       </c>
       <c r="J52" s="17"/>
     </row>
@@ -2480,124 +2480,124 @@
         <v>2838</v>
       </c>
       <c r="D53" s="7">
-        <v>11834</v>
+        <v>11253</v>
       </c>
       <c r="E53" s="7">
-        <v>11145</v>
+        <v>10565</v>
       </c>
       <c r="F53" s="7">
         <v>4215</v>
       </c>
       <c r="G53" s="8">
         <f t="shared" si="3"/>
-        <v>11.834</v>
+        <v>11.253</v>
       </c>
       <c r="H53" s="8">
         <f t="shared" si="4"/>
-        <v>11.145</v>
+        <v>10.565</v>
       </c>
       <c r="I53" s="9">
         <f t="shared" si="5"/>
-        <v>2.8075919335705812</v>
+        <v>2.6697508896797153</v>
       </c>
       <c r="J53" s="10"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B54" s="19">
-        <v>226.37</v>
-      </c>
-      <c r="C54" s="20">
-        <v>7413</v>
-      </c>
-      <c r="D54" s="21">
-        <v>11392</v>
-      </c>
-      <c r="E54" s="21">
-        <v>9188</v>
-      </c>
-      <c r="F54" s="21">
-        <v>554</v>
-      </c>
-      <c r="G54" s="22">
+      <c r="B54" s="12">
+        <v>303.58</v>
+      </c>
+      <c r="C54" s="13">
+        <v>7626</v>
+      </c>
+      <c r="D54" s="14">
+        <v>10643</v>
+      </c>
+      <c r="E54" s="14">
+        <v>6775</v>
+      </c>
+      <c r="F54" s="14">
+        <v>6059</v>
+      </c>
+      <c r="G54" s="15">
         <f t="shared" si="3"/>
-        <v>11.391999999999999</v>
-      </c>
-      <c r="H54" s="22">
+        <v>10.643000000000001</v>
+      </c>
+      <c r="H54" s="15">
         <f t="shared" si="4"/>
-        <v>9.1880000000000006</v>
-      </c>
-      <c r="I54" s="23">
+        <v>6.7750000000000004</v>
+      </c>
+      <c r="I54" s="16">
         <f t="shared" si="5"/>
-        <v>20.56317689530686</v>
-      </c>
-      <c r="J54" s="24"/>
+        <v>1.7565604885294603</v>
+      </c>
+      <c r="J54" s="17"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="18" t="s">
+      <c r="A55" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B55" s="19">
-        <v>127.8</v>
-      </c>
-      <c r="C55" s="20">
-        <v>5228</v>
-      </c>
-      <c r="D55" s="21">
-        <v>11392</v>
-      </c>
-      <c r="E55" s="21">
-        <v>9600</v>
-      </c>
-      <c r="F55" s="21">
-        <v>289</v>
-      </c>
-      <c r="G55" s="22">
+      <c r="B55" s="5">
+        <v>31.8</v>
+      </c>
+      <c r="C55" s="6">
+        <v>2339</v>
+      </c>
+      <c r="D55" s="7">
+        <v>10615</v>
+      </c>
+      <c r="E55" s="7">
+        <v>9813</v>
+      </c>
+      <c r="F55" s="7">
+        <v>4262</v>
+      </c>
+      <c r="G55" s="8">
         <f t="shared" si="3"/>
-        <v>11.391999999999999</v>
-      </c>
-      <c r="H55" s="22">
+        <v>10.615</v>
+      </c>
+      <c r="H55" s="8">
         <f t="shared" si="4"/>
-        <v>9.6</v>
-      </c>
-      <c r="I55" s="23">
+        <v>9.8130000000000006</v>
+      </c>
+      <c r="I55" s="9">
         <f t="shared" si="5"/>
-        <v>39.418685121107266</v>
-      </c>
-      <c r="J55" s="24"/>
+        <v>2.4906147348662602</v>
+      </c>
+      <c r="J55" s="10"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>63</v>
       </c>
       <c r="B56" s="12">
-        <v>31.8</v>
+        <v>189.65</v>
       </c>
       <c r="C56" s="13">
-        <v>2339</v>
+        <v>6663</v>
       </c>
       <c r="D56" s="14">
-        <v>11196</v>
+        <v>9935</v>
       </c>
       <c r="E56" s="14">
-        <v>10394</v>
+        <v>6591</v>
       </c>
       <c r="F56" s="14">
-        <v>4262</v>
+        <v>5929</v>
       </c>
       <c r="G56" s="15">
         <f t="shared" si="3"/>
-        <v>11.196</v>
+        <v>9.9350000000000005</v>
       </c>
       <c r="H56" s="15">
         <f t="shared" si="4"/>
-        <v>10.394</v>
+        <v>6.5910000000000002</v>
       </c>
       <c r="I56" s="16">
         <f t="shared" si="5"/>
-        <v>2.626935710933834</v>
+        <v>1.675662000337325</v>
       </c>
       <c r="J56" s="17"/>
     </row>
@@ -2606,196 +2606,196 @@
         <v>64</v>
       </c>
       <c r="B57" s="5">
-        <v>303.58</v>
+        <v>49.08</v>
       </c>
       <c r="C57" s="6">
-        <v>7626</v>
+        <v>3023</v>
       </c>
       <c r="D57" s="7">
-        <v>10643</v>
+        <v>9862</v>
       </c>
       <c r="E57" s="7">
-        <v>6775</v>
+        <v>9301</v>
       </c>
       <c r="F57" s="7">
-        <v>6059</v>
+        <v>3629</v>
       </c>
       <c r="G57" s="8">
         <f t="shared" si="3"/>
-        <v>10.643000000000001</v>
+        <v>9.8620000000000001</v>
       </c>
       <c r="H57" s="8">
         <f t="shared" si="4"/>
-        <v>6.7750000000000004</v>
+        <v>9.3010000000000002</v>
       </c>
       <c r="I57" s="9">
         <f t="shared" si="5"/>
-        <v>1.7565604885294603</v>
+        <v>2.7175530449159546</v>
       </c>
       <c r="J57" s="10"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B58" s="12">
-        <v>49.08</v>
-      </c>
-      <c r="C58" s="13">
-        <v>3023</v>
-      </c>
-      <c r="D58" s="14">
-        <v>10443</v>
-      </c>
-      <c r="E58" s="14">
-        <v>9891</v>
-      </c>
-      <c r="F58" s="14">
-        <v>3629</v>
-      </c>
-      <c r="G58" s="15">
+      <c r="B58" s="19">
+        <v>172.75</v>
+      </c>
+      <c r="C58" s="20">
+        <v>5905</v>
+      </c>
+      <c r="D58" s="21">
+        <v>9611</v>
+      </c>
+      <c r="E58" s="21">
+        <v>6727</v>
+      </c>
+      <c r="F58" s="21">
+        <v>2656</v>
+      </c>
+      <c r="G58" s="22">
         <f t="shared" si="3"/>
-        <v>10.443</v>
-      </c>
-      <c r="H58" s="15">
+        <v>9.6110000000000007</v>
+      </c>
+      <c r="H58" s="22">
         <f t="shared" si="4"/>
-        <v>9.891</v>
-      </c>
-      <c r="I58" s="16">
+        <v>6.7270000000000003</v>
+      </c>
+      <c r="I58" s="23">
         <f t="shared" si="5"/>
-        <v>2.8776522457977403</v>
-      </c>
-      <c r="J58" s="17"/>
+        <v>3.6185993975903616</v>
+      </c>
+      <c r="J58" s="24"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B59" s="5">
-        <v>189.65</v>
-      </c>
-      <c r="C59" s="6">
-        <v>6663</v>
-      </c>
-      <c r="D59" s="7">
-        <v>9935</v>
-      </c>
-      <c r="E59" s="7">
-        <v>6591</v>
-      </c>
-      <c r="F59" s="7">
-        <v>5929</v>
-      </c>
-      <c r="G59" s="8">
+      <c r="B59" s="19">
+        <v>286.07</v>
+      </c>
+      <c r="C59" s="20">
+        <v>6866</v>
+      </c>
+      <c r="D59" s="21">
+        <v>8728</v>
+      </c>
+      <c r="E59" s="21">
+        <v>5244</v>
+      </c>
+      <c r="F59" s="21">
+        <v>2661</v>
+      </c>
+      <c r="G59" s="22">
         <f t="shared" si="3"/>
-        <v>9.9350000000000005</v>
-      </c>
-      <c r="H59" s="8">
+        <v>8.7279999999999998</v>
+      </c>
+      <c r="H59" s="22">
         <f t="shared" si="4"/>
-        <v>6.5910000000000002</v>
-      </c>
-      <c r="I59" s="9">
+        <v>5.2439999999999998</v>
+      </c>
+      <c r="I59" s="23">
         <f t="shared" si="5"/>
-        <v>1.675662000337325</v>
-      </c>
-      <c r="J59" s="10"/>
+        <v>3.2799699361142429</v>
+      </c>
+      <c r="J59" s="24"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
         <v>67</v>
       </c>
       <c r="B60" s="19">
-        <v>172.75</v>
+        <v>40.44</v>
       </c>
       <c r="C60" s="20">
-        <v>5905</v>
+        <v>2957</v>
       </c>
       <c r="D60" s="21">
-        <v>9916</v>
+        <v>8638</v>
       </c>
       <c r="E60" s="21">
-        <v>6738</v>
+        <v>7920</v>
       </c>
       <c r="F60" s="21">
-        <v>2656</v>
+        <v>2698</v>
       </c>
       <c r="G60" s="22">
         <f t="shared" si="3"/>
-        <v>9.9160000000000004</v>
+        <v>8.6379999999999999</v>
       </c>
       <c r="H60" s="22">
         <f t="shared" si="4"/>
-        <v>6.7380000000000004</v>
+        <v>7.92</v>
       </c>
       <c r="I60" s="23">
         <f t="shared" si="5"/>
-        <v>3.7334337349397591</v>
+        <v>3.201630837657524</v>
       </c>
       <c r="J60" s="24"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="18" t="s">
+      <c r="A61" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="19">
-        <v>40.44</v>
-      </c>
-      <c r="C61" s="20">
-        <v>2957</v>
-      </c>
-      <c r="D61" s="21">
-        <v>9658</v>
-      </c>
-      <c r="E61" s="21">
-        <v>8939</v>
-      </c>
-      <c r="F61" s="21">
-        <v>2698</v>
-      </c>
-      <c r="G61" s="22">
+      <c r="B61" s="5">
+        <v>46.34</v>
+      </c>
+      <c r="C61" s="6">
+        <v>2872</v>
+      </c>
+      <c r="D61" s="7">
+        <v>8048</v>
+      </c>
+      <c r="E61" s="7">
+        <v>6402</v>
+      </c>
+      <c r="F61" s="7">
+        <v>5202</v>
+      </c>
+      <c r="G61" s="8">
         <f t="shared" si="3"/>
-        <v>9.6579999999999995</v>
-      </c>
-      <c r="H61" s="22">
+        <v>8.048</v>
+      </c>
+      <c r="H61" s="8">
         <f t="shared" si="4"/>
-        <v>8.9390000000000001</v>
-      </c>
-      <c r="I61" s="23">
+        <v>6.4020000000000001</v>
+      </c>
+      <c r="I61" s="9">
         <f t="shared" si="5"/>
-        <v>3.5796886582653817</v>
-      </c>
-      <c r="J61" s="24"/>
+        <v>1.5470972702806614</v>
+      </c>
+      <c r="J61" s="10"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
         <v>69</v>
       </c>
       <c r="B62" s="19">
-        <v>93.41</v>
+        <v>39.74</v>
       </c>
       <c r="C62" s="20">
-        <v>4212</v>
+        <v>3355</v>
       </c>
       <c r="D62" s="21">
-        <v>9600</v>
+        <v>7579</v>
       </c>
       <c r="E62" s="21">
-        <v>8252</v>
+        <v>6617</v>
       </c>
       <c r="F62" s="21">
-        <v>539</v>
+        <v>1816</v>
       </c>
       <c r="G62" s="22">
         <f t="shared" si="3"/>
-        <v>9.6</v>
+        <v>7.5789999999999997</v>
       </c>
       <c r="H62" s="22">
         <f t="shared" si="4"/>
-        <v>8.2520000000000007</v>
+        <v>6.617</v>
       </c>
       <c r="I62" s="23">
         <f t="shared" si="5"/>
-        <v>17.810760667903526</v>
+        <v>4.1734581497797354</v>
       </c>
       <c r="J62" s="24"/>
     </row>
@@ -2804,97 +2804,97 @@
         <v>70</v>
       </c>
       <c r="B63" s="19">
-        <v>30.12</v>
+        <v>72.52</v>
       </c>
       <c r="C63" s="20">
-        <v>2592</v>
+        <v>3558</v>
       </c>
       <c r="D63" s="21">
-        <v>9450</v>
+        <v>7432</v>
       </c>
       <c r="E63" s="21">
-        <v>8286</v>
+        <v>6033</v>
       </c>
       <c r="F63" s="21">
-        <v>929</v>
+        <v>1840</v>
       </c>
       <c r="G63" s="22">
         <f t="shared" si="3"/>
-        <v>9.4499999999999993</v>
+        <v>7.4320000000000004</v>
       </c>
       <c r="H63" s="22">
         <f t="shared" si="4"/>
-        <v>8.2859999999999996</v>
+        <v>6.0330000000000004</v>
       </c>
       <c r="I63" s="23">
         <f t="shared" si="5"/>
-        <v>10.172228202368137</v>
+        <v>4.0391304347826091</v>
       </c>
       <c r="J63" s="24"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B64" s="12">
-        <v>46.34</v>
-      </c>
-      <c r="C64" s="13">
-        <v>2872</v>
-      </c>
-      <c r="D64" s="14">
-        <v>8982</v>
-      </c>
-      <c r="E64" s="14">
-        <v>7133</v>
-      </c>
-      <c r="F64" s="14">
-        <v>5202</v>
-      </c>
-      <c r="G64" s="15">
+      <c r="B64" s="19">
+        <v>93.41</v>
+      </c>
+      <c r="C64" s="20">
+        <v>4212</v>
+      </c>
+      <c r="D64" s="21">
+        <v>6651</v>
+      </c>
+      <c r="E64" s="21">
+        <v>5303</v>
+      </c>
+      <c r="F64" s="21">
+        <v>539</v>
+      </c>
+      <c r="G64" s="22">
         <f t="shared" si="3"/>
-        <v>8.9819999999999993</v>
-      </c>
-      <c r="H64" s="15">
+        <v>6.6509999999999998</v>
+      </c>
+      <c r="H64" s="22">
         <f t="shared" si="4"/>
-        <v>7.133</v>
-      </c>
-      <c r="I64" s="16">
+        <v>5.3029999999999999</v>
+      </c>
+      <c r="I64" s="23">
         <f t="shared" si="5"/>
-        <v>1.726643598615917</v>
-      </c>
-      <c r="J64" s="17"/>
+        <v>12.339517625231911</v>
+      </c>
+      <c r="J64" s="24"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
         <v>72</v>
       </c>
       <c r="B65" s="19">
-        <v>286.07</v>
+        <v>30.12</v>
       </c>
       <c r="C65" s="20">
-        <v>6866</v>
+        <v>2592</v>
       </c>
       <c r="D65" s="21">
-        <v>8739</v>
+        <v>6617</v>
       </c>
       <c r="E65" s="21">
-        <v>5244</v>
+        <v>5688</v>
       </c>
       <c r="F65" s="21">
-        <v>2661</v>
+        <v>929</v>
       </c>
       <c r="G65" s="22">
         <f t="shared" si="3"/>
-        <v>8.7390000000000008</v>
+        <v>6.617</v>
       </c>
       <c r="H65" s="22">
         <f t="shared" si="4"/>
-        <v>5.2439999999999998</v>
+        <v>5.6879999999999997</v>
       </c>
       <c r="I65" s="23">
         <f t="shared" si="5"/>
-        <v>3.2841037204058625</v>
+        <v>7.1227125941872984</v>
       </c>
       <c r="J65" s="24"/>
     </row>
@@ -2903,31 +2903,31 @@
         <v>73</v>
       </c>
       <c r="B66" s="19">
-        <v>39.74</v>
+        <v>159.81</v>
       </c>
       <c r="C66" s="20">
-        <v>3355</v>
+        <v>5989</v>
       </c>
       <c r="D66" s="21">
-        <v>8286</v>
+        <v>6061</v>
       </c>
       <c r="E66" s="21">
-        <v>7283</v>
+        <v>3243</v>
       </c>
       <c r="F66" s="21">
-        <v>1816</v>
+        <v>623</v>
       </c>
       <c r="G66" s="22">
         <f t="shared" si="3"/>
-        <v>8.2859999999999996</v>
+        <v>6.0609999999999999</v>
       </c>
       <c r="H66" s="22">
         <f t="shared" si="4"/>
-        <v>7.2830000000000004</v>
+        <v>3.2429999999999999</v>
       </c>
       <c r="I66" s="23">
         <f t="shared" si="5"/>
-        <v>4.5627753303964758</v>
+        <v>9.728731942215088</v>
       </c>
       <c r="J66" s="24"/>
     </row>
@@ -2936,31 +2936,31 @@
         <v>74</v>
       </c>
       <c r="B67" s="19">
-        <v>72.52</v>
+        <v>226.37</v>
       </c>
       <c r="C67" s="20">
-        <v>3558</v>
+        <v>7413</v>
       </c>
       <c r="D67" s="21">
-        <v>8286</v>
+        <v>6005</v>
       </c>
       <c r="E67" s="21">
-        <v>6044</v>
+        <v>3122</v>
       </c>
       <c r="F67" s="21">
-        <v>1840</v>
+        <v>554</v>
       </c>
       <c r="G67" s="22">
         <f t="shared" si="3"/>
-        <v>8.2859999999999996</v>
+        <v>6.0049999999999999</v>
       </c>
       <c r="H67" s="22">
         <f t="shared" si="4"/>
-        <v>6.0439999999999996</v>
+        <v>3.1219999999999999</v>
       </c>
       <c r="I67" s="23">
         <f t="shared" si="5"/>
-        <v>4.5032608695652172</v>
+        <v>10.839350180505415</v>
       </c>
       <c r="J67" s="24"/>
     </row>
@@ -2969,31 +2969,31 @@
         <v>75</v>
       </c>
       <c r="B68" s="19">
-        <v>159.81</v>
+        <v>127.8</v>
       </c>
       <c r="C68" s="20">
-        <v>5989</v>
+        <v>5228</v>
       </c>
       <c r="D68" s="21">
-        <v>5271</v>
+        <v>5303</v>
       </c>
       <c r="E68" s="21">
-        <v>3243</v>
+        <v>1483</v>
       </c>
       <c r="F68" s="21">
-        <v>623</v>
+        <v>289</v>
       </c>
       <c r="G68" s="22">
         <f t="shared" si="3"/>
-        <v>5.2709999999999999</v>
+        <v>5.3029999999999999</v>
       </c>
       <c r="H68" s="22">
         <f t="shared" si="4"/>
-        <v>3.2429999999999999</v>
+        <v>1.4830000000000001</v>
       </c>
       <c r="I68" s="23">
         <f t="shared" si="5"/>
-        <v>8.4606741573033712</v>
+        <v>18.349480968858131</v>
       </c>
       <c r="J68" s="24"/>
     </row>
@@ -3202,15 +3202,15 @@
       </c>
       <c r="D76" s="31">
         <f>MAX(D5:D74)</f>
-        <v>27435</v>
+        <v>25675</v>
       </c>
       <c r="G76" s="32">
         <f>IFERROR(MAX(G5:G74),"")</f>
-        <v>27.434999999999999</v>
+        <v>25.675000000000001</v>
       </c>
       <c r="I76" s="33">
         <f>IFERROR(AVERAGE(I5:I74),"")</f>
-        <v>3.6943327043629872</v>
+        <v>3.0568576954892626</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16AA9C28-4097-4C83-B23F-B0C60904FFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED1BAE8-6B5C-4E0C-8E3F-D25C1F5907AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -995,7 +995,7 @@
         <v>3658</v>
       </c>
       <c r="D8" s="14">
-        <v>25277</v>
+        <v>25278</v>
       </c>
       <c r="E8" s="14">
         <v>24284</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>25.277000000000001</v>
+        <v>25.277999999999999</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>1.8407369647538596</v>
+        <v>1.8408097873579958</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -1064,7 +1064,7 @@
         <v>25101</v>
       </c>
       <c r="E10" s="14">
-        <v>24922</v>
+        <v>24923</v>
       </c>
       <c r="F10" s="14">
         <v>14034</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>24.922000000000001</v>
+        <v>24.922999999999998</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
@@ -1127,7 +1127,7 @@
         <v>1858</v>
       </c>
       <c r="D12" s="14">
-        <v>24948</v>
+        <v>24949</v>
       </c>
       <c r="E12" s="14">
         <v>24436</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>24.948</v>
+        <v>24.949000000000002</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>1.7142857142857142</v>
+        <v>1.7143544286401429</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1229,7 +1229,7 @@
         <v>24469</v>
       </c>
       <c r="E15" s="7">
-        <v>22963</v>
+        <v>22964</v>
       </c>
       <c r="F15" s="7">
         <v>15705</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
-        <v>22.963000000000001</v>
+        <v>22.963999999999999</v>
       </c>
       <c r="I15" s="9">
         <f t="shared" si="2"/>
@@ -1361,7 +1361,7 @@
         <v>24038</v>
       </c>
       <c r="E19" s="7">
-        <v>21081</v>
+        <v>21082</v>
       </c>
       <c r="F19" s="7">
         <v>14968</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
-        <v>21.081</v>
+        <v>21.082000000000001</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="2"/>
@@ -1457,7 +1457,7 @@
         <v>2313</v>
       </c>
       <c r="D22" s="14">
-        <v>23396</v>
+        <v>23397</v>
       </c>
       <c r="E22" s="14">
         <v>22658</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="G22" s="15">
         <f t="shared" si="0"/>
-        <v>23.396000000000001</v>
+        <v>23.396999999999998</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="1"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="I22" s="16">
         <f t="shared" si="2"/>
-        <v>1.642516147149677</v>
+        <v>1.6425863521482729</v>
       </c>
       <c r="J22" s="17"/>
     </row>
@@ -1523,7 +1523,7 @@
         <v>2648</v>
       </c>
       <c r="D24" s="14">
-        <v>22885</v>
+        <v>22886</v>
       </c>
       <c r="E24" s="14">
         <v>22278</v>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G24" s="15">
         <f t="shared" si="0"/>
-        <v>22.885000000000002</v>
+        <v>22.885999999999999</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="1"/>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I24" s="16">
         <f t="shared" si="2"/>
-        <v>1.5846143193463509</v>
+        <v>1.5846835618335411</v>
       </c>
       <c r="J24" s="17"/>
     </row>
@@ -1559,7 +1559,7 @@
         <v>22329</v>
       </c>
       <c r="E25" s="7">
-        <v>20929</v>
+        <v>20930</v>
       </c>
       <c r="F25" s="7">
         <v>14233</v>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>20.928999999999998</v>
+        <v>20.93</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
@@ -1625,7 +1625,7 @@
         <v>21563</v>
       </c>
       <c r="E27" s="7">
-        <v>20518</v>
+        <v>20519</v>
       </c>
       <c r="F27" s="7">
         <v>14141</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="H27" s="8">
         <f t="shared" si="1"/>
-        <v>20.518000000000001</v>
+        <v>20.518999999999998</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="2"/>
@@ -1790,7 +1790,7 @@
         <v>20192</v>
       </c>
       <c r="E32" s="14">
-        <v>18948</v>
+        <v>18949</v>
       </c>
       <c r="F32" s="14">
         <v>12932</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H32" s="15">
         <f t="shared" si="1"/>
-        <v>18.948</v>
+        <v>18.949000000000002</v>
       </c>
       <c r="I32" s="16">
         <f t="shared" si="2"/>
@@ -1955,7 +1955,7 @@
         <v>18310</v>
       </c>
       <c r="E37" s="7">
-        <v>17289</v>
+        <v>17290</v>
       </c>
       <c r="F37" s="7">
         <v>10413</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H37" s="8">
         <f t="shared" ref="H37:H71" si="4">E37/1000</f>
-        <v>17.289000000000001</v>
+        <v>17.29</v>
       </c>
       <c r="I37" s="9">
         <f t="shared" ref="I37:I71" si="5">IFERROR(D37/F37,"")</f>
@@ -1988,7 +1988,7 @@
         <v>18310</v>
       </c>
       <c r="E38" s="14">
-        <v>15285</v>
+        <v>15286</v>
       </c>
       <c r="F38" s="14">
         <v>9361</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H38" s="15">
         <f t="shared" si="4"/>
-        <v>15.285</v>
+        <v>15.286</v>
       </c>
       <c r="I38" s="16">
         <f t="shared" si="5"/>
@@ -2018,25 +2018,25 @@
         <v>3031</v>
       </c>
       <c r="D39" s="7">
-        <v>18065</v>
+        <v>18066</v>
       </c>
       <c r="E39" s="7">
-        <v>16213</v>
+        <v>16214</v>
       </c>
       <c r="F39" s="7">
         <v>10293</v>
       </c>
       <c r="G39" s="8">
         <f t="shared" si="3"/>
-        <v>18.065000000000001</v>
+        <v>18.065999999999999</v>
       </c>
       <c r="H39" s="8">
         <f t="shared" si="4"/>
-        <v>16.213000000000001</v>
+        <v>16.213999999999999</v>
       </c>
       <c r="I39" s="9">
         <f t="shared" si="5"/>
-        <v>1.7550762654231031</v>
+        <v>1.7551734188283299</v>
       </c>
       <c r="J39" s="10"/>
     </row>
@@ -2051,25 +2051,25 @@
         <v>5466</v>
       </c>
       <c r="D40" s="14">
-        <v>18065</v>
+        <v>18066</v>
       </c>
       <c r="E40" s="14">
-        <v>15285</v>
+        <v>15286</v>
       </c>
       <c r="F40" s="14">
         <v>9364</v>
       </c>
       <c r="G40" s="15">
         <f t="shared" si="3"/>
-        <v>18.065000000000001</v>
+        <v>18.065999999999999</v>
       </c>
       <c r="H40" s="15">
         <f t="shared" si="4"/>
-        <v>15.285</v>
+        <v>15.286</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="5"/>
-        <v>1.9291969243912859</v>
+        <v>1.9293037163605298</v>
       </c>
       <c r="J40" s="17"/>
     </row>
@@ -2084,25 +2084,25 @@
         <v>2417</v>
       </c>
       <c r="D41" s="7">
-        <v>18048</v>
+        <v>18049</v>
       </c>
       <c r="E41" s="7">
-        <v>16975</v>
+        <v>16976</v>
       </c>
       <c r="F41" s="7">
         <v>10355</v>
       </c>
       <c r="G41" s="8">
         <f t="shared" si="3"/>
-        <v>18.047999999999998</v>
+        <v>18.048999999999999</v>
       </c>
       <c r="H41" s="8">
         <f t="shared" si="4"/>
-        <v>16.975000000000001</v>
+        <v>16.975999999999999</v>
       </c>
       <c r="I41" s="9">
         <f t="shared" si="5"/>
-        <v>1.7429261226460646</v>
+        <v>1.7430226943505553</v>
       </c>
       <c r="J41" s="10"/>
     </row>
@@ -2117,7 +2117,7 @@
         <v>3294</v>
       </c>
       <c r="D42" s="14">
-        <v>17847</v>
+        <v>17848</v>
       </c>
       <c r="E42" s="14">
         <v>16271</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="G42" s="15">
         <f t="shared" si="3"/>
-        <v>17.847000000000001</v>
+        <v>17.847999999999999</v>
       </c>
       <c r="H42" s="15">
         <f t="shared" si="4"/>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="I42" s="16">
         <f t="shared" si="5"/>
-        <v>1.7286904300658659</v>
+        <v>1.7287872917473848</v>
       </c>
       <c r="J42" s="17"/>
     </row>
@@ -2150,25 +2150,25 @@
         <v>2710</v>
       </c>
       <c r="D43" s="7">
-        <v>17339</v>
+        <v>17340</v>
       </c>
       <c r="E43" s="7">
-        <v>15920</v>
+        <v>15921</v>
       </c>
       <c r="F43" s="7">
         <v>9510</v>
       </c>
       <c r="G43" s="8">
         <f t="shared" si="3"/>
-        <v>17.338999999999999</v>
+        <v>17.34</v>
       </c>
       <c r="H43" s="8">
         <f t="shared" si="4"/>
-        <v>15.92</v>
+        <v>15.920999999999999</v>
       </c>
       <c r="I43" s="9">
         <f t="shared" si="5"/>
-        <v>1.8232386961093585</v>
+        <v>1.8233438485804416</v>
       </c>
       <c r="J43" s="10"/>
     </row>
@@ -2252,7 +2252,7 @@
         <v>16271</v>
       </c>
       <c r="E46" s="14">
-        <v>15285</v>
+        <v>15286</v>
       </c>
       <c r="F46" s="14">
         <v>9367</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H46" s="15">
         <f t="shared" si="4"/>
-        <v>15.285</v>
+        <v>15.286</v>
       </c>
       <c r="I46" s="16">
         <f t="shared" si="5"/>
@@ -2285,7 +2285,7 @@
         <v>14860</v>
       </c>
       <c r="E47" s="7">
-        <v>14700</v>
+        <v>14701</v>
       </c>
       <c r="F47" s="7">
         <v>7664</v>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="H47" s="8">
         <f t="shared" si="4"/>
-        <v>14.7</v>
+        <v>14.701000000000001</v>
       </c>
       <c r="I47" s="9">
         <f t="shared" si="5"/>
@@ -2318,7 +2318,7 @@
         <v>14805</v>
       </c>
       <c r="E48" s="14">
-        <v>13377</v>
+        <v>13378</v>
       </c>
       <c r="F48" s="14">
         <v>7560</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="H48" s="15">
         <f t="shared" si="4"/>
-        <v>13.377000000000001</v>
+        <v>13.378</v>
       </c>
       <c r="I48" s="16">
         <f t="shared" si="5"/>
@@ -2351,7 +2351,7 @@
         <v>14805</v>
       </c>
       <c r="E49" s="7">
-        <v>13377</v>
+        <v>13378</v>
       </c>
       <c r="F49" s="7">
         <v>7303</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H49" s="8">
         <f t="shared" si="4"/>
-        <v>13.377000000000001</v>
+        <v>13.378</v>
       </c>
       <c r="I49" s="9">
         <f t="shared" si="5"/>
@@ -2417,7 +2417,7 @@
         <v>14749</v>
       </c>
       <c r="E51" s="7">
-        <v>13377</v>
+        <v>13378</v>
       </c>
       <c r="F51" s="7">
         <v>7306</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H51" s="8">
         <f t="shared" si="4"/>
-        <v>13.377000000000001</v>
+        <v>13.378</v>
       </c>
       <c r="I51" s="9">
         <f t="shared" si="5"/>
@@ -2447,7 +2447,7 @@
         <v>7672</v>
       </c>
       <c r="D52" s="14">
-        <v>11569</v>
+        <v>11582</v>
       </c>
       <c r="E52" s="14">
         <v>7485</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="G52" s="15">
         <f t="shared" si="3"/>
-        <v>11.569000000000001</v>
+        <v>11.582000000000001</v>
       </c>
       <c r="H52" s="15">
         <f t="shared" si="4"/>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I52" s="16">
         <f t="shared" si="5"/>
-        <v>1.9621777476255089</v>
+        <v>1.96438263229308</v>
       </c>
       <c r="J52" s="17"/>
     </row>
@@ -2645,7 +2645,7 @@
         <v>5905</v>
       </c>
       <c r="D58" s="21">
-        <v>9611</v>
+        <v>9527</v>
       </c>
       <c r="E58" s="21">
         <v>6727</v>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="G58" s="22">
         <f t="shared" si="3"/>
-        <v>9.6110000000000007</v>
+        <v>9.5269999999999992</v>
       </c>
       <c r="H58" s="22">
         <f t="shared" si="4"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="I58" s="23">
         <f t="shared" si="5"/>
-        <v>3.6185993975903616</v>
+        <v>3.5869728915662651</v>
       </c>
       <c r="J58" s="24"/>
     </row>
@@ -2744,7 +2744,7 @@
         <v>2872</v>
       </c>
       <c r="D61" s="7">
-        <v>8048</v>
+        <v>8060</v>
       </c>
       <c r="E61" s="7">
         <v>6402</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="G61" s="8">
         <f t="shared" si="3"/>
-        <v>8.048</v>
+        <v>8.06</v>
       </c>
       <c r="H61" s="8">
         <f t="shared" si="4"/>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I61" s="9">
         <f t="shared" si="5"/>
-        <v>1.5470972702806614</v>
+        <v>1.5494040753556324</v>
       </c>
       <c r="J61" s="10"/>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="I76" s="33">
         <f>IFERROR(AVERAGE(I5:I74),"")</f>
-        <v>3.0568576954892626</v>
+        <v>3.0564646910026116</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED1BAE8-6B5C-4E0C-8E3F-D25C1F5907AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B788502D-BC5B-4954-BDCD-B4033741965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="108">
   <si>
     <t>FAZENDA TUCANO — distância dos talhões até a sede</t>
   </si>
@@ -243,6 +243,12 @@
     <t>T-16</t>
   </si>
   <si>
+    <t>T-05D</t>
+  </si>
+  <si>
+    <t>T-CON</t>
+  </si>
+  <si>
     <t>T-06A</t>
   </si>
   <si>
@@ -273,7 +279,7 @@
     <t>T-10</t>
   </si>
   <si>
-    <t>T-05D</t>
+    <t>T-40C</t>
   </si>
   <si>
     <t>sem acesso</t>
@@ -283,12 +289,6 @@
   </si>
   <si>
     <t>sem estrada até este talhão</t>
-  </si>
-  <si>
-    <t>T-40C</t>
-  </si>
-  <si>
-    <t>T-CON</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -1961,15 +1961,15 @@
         <v>10413</v>
       </c>
       <c r="G37" s="8">
-        <f t="shared" ref="G37:G71" si="3">D37/1000</f>
+        <f t="shared" ref="G37:G73" si="3">D37/1000</f>
         <v>18.309999999999999</v>
       </c>
       <c r="H37" s="8">
-        <f t="shared" ref="H37:H71" si="4">E37/1000</f>
+        <f t="shared" ref="H37:H73" si="4">E37/1000</f>
         <v>17.29</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" ref="I37:I71" si="5">IFERROR(D37/F37,"")</f>
+        <f t="shared" ref="I37:I73" si="5">IFERROR(D37/F37,"")</f>
         <v>1.7583789493901854</v>
       </c>
       <c r="J37" s="10"/>
@@ -2767,101 +2767,101 @@
       <c r="J61" s="10"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="18" t="s">
+      <c r="A62" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="19">
-        <v>39.74</v>
-      </c>
-      <c r="C62" s="20">
-        <v>3355</v>
-      </c>
-      <c r="D62" s="21">
-        <v>7579</v>
-      </c>
-      <c r="E62" s="21">
-        <v>6617</v>
-      </c>
-      <c r="F62" s="21">
-        <v>1816</v>
-      </c>
-      <c r="G62" s="22">
-        <f t="shared" si="3"/>
-        <v>7.5789999999999997</v>
-      </c>
-      <c r="H62" s="22">
-        <f t="shared" si="4"/>
-        <v>6.617</v>
-      </c>
-      <c r="I62" s="23">
-        <f t="shared" si="5"/>
-        <v>4.1734581497797354</v>
-      </c>
-      <c r="J62" s="24"/>
+      <c r="B62" s="12">
+        <v>33.869999999999997</v>
+      </c>
+      <c r="C62" s="13">
+        <v>2696</v>
+      </c>
+      <c r="D62" s="14">
+        <v>7715</v>
+      </c>
+      <c r="E62" s="14">
+        <v>7715</v>
+      </c>
+      <c r="F62" s="14">
+        <v>3966</v>
+      </c>
+      <c r="G62" s="15">
+        <f t="shared" si="3"/>
+        <v>7.7149999999999999</v>
+      </c>
+      <c r="H62" s="15">
+        <f t="shared" si="4"/>
+        <v>7.7149999999999999</v>
+      </c>
+      <c r="I62" s="16">
+        <f t="shared" si="5"/>
+        <v>1.9452849218356025</v>
+      </c>
+      <c r="J62" s="17"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="18" t="s">
+      <c r="A63" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B63" s="19">
-        <v>72.52</v>
-      </c>
-      <c r="C63" s="20">
-        <v>3558</v>
-      </c>
-      <c r="D63" s="21">
-        <v>7432</v>
-      </c>
-      <c r="E63" s="21">
-        <v>6033</v>
-      </c>
-      <c r="F63" s="21">
-        <v>1840</v>
-      </c>
-      <c r="G63" s="22">
-        <f t="shared" si="3"/>
-        <v>7.4320000000000004</v>
-      </c>
-      <c r="H63" s="22">
-        <f t="shared" si="4"/>
-        <v>6.0330000000000004</v>
-      </c>
-      <c r="I63" s="23">
-        <f t="shared" si="5"/>
-        <v>4.0391304347826091</v>
-      </c>
-      <c r="J63" s="24"/>
+      <c r="B63" s="5">
+        <v>3.24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>1056</v>
+      </c>
+      <c r="D63" s="7">
+        <v>7715</v>
+      </c>
+      <c r="E63" s="7">
+        <v>7715</v>
+      </c>
+      <c r="F63" s="7">
+        <v>3969</v>
+      </c>
+      <c r="G63" s="8">
+        <f t="shared" si="3"/>
+        <v>7.7149999999999999</v>
+      </c>
+      <c r="H63" s="8">
+        <f t="shared" si="4"/>
+        <v>7.7149999999999999</v>
+      </c>
+      <c r="I63" s="9">
+        <f t="shared" si="5"/>
+        <v>1.9438145628621819</v>
+      </c>
+      <c r="J63" s="10"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="18" t="s">
         <v>71</v>
       </c>
       <c r="B64" s="19">
-        <v>93.41</v>
+        <v>39.74</v>
       </c>
       <c r="C64" s="20">
-        <v>4212</v>
+        <v>3355</v>
       </c>
       <c r="D64" s="21">
-        <v>6651</v>
+        <v>7579</v>
       </c>
       <c r="E64" s="21">
-        <v>5303</v>
+        <v>6617</v>
       </c>
       <c r="F64" s="21">
-        <v>539</v>
+        <v>1816</v>
       </c>
       <c r="G64" s="22">
         <f t="shared" si="3"/>
-        <v>6.6509999999999998</v>
+        <v>7.5789999999999997</v>
       </c>
       <c r="H64" s="22">
         <f t="shared" si="4"/>
-        <v>5.3029999999999999</v>
+        <v>6.617</v>
       </c>
       <c r="I64" s="23">
         <f t="shared" si="5"/>
-        <v>12.339517625231911</v>
+        <v>4.1734581497797354</v>
       </c>
       <c r="J64" s="24"/>
     </row>
@@ -2870,31 +2870,31 @@
         <v>72</v>
       </c>
       <c r="B65" s="19">
-        <v>30.12</v>
+        <v>72.52</v>
       </c>
       <c r="C65" s="20">
-        <v>2592</v>
+        <v>3558</v>
       </c>
       <c r="D65" s="21">
-        <v>6617</v>
+        <v>7432</v>
       </c>
       <c r="E65" s="21">
-        <v>5688</v>
+        <v>6033</v>
       </c>
       <c r="F65" s="21">
-        <v>929</v>
+        <v>1840</v>
       </c>
       <c r="G65" s="22">
         <f t="shared" si="3"/>
-        <v>6.617</v>
+        <v>7.4320000000000004</v>
       </c>
       <c r="H65" s="22">
         <f t="shared" si="4"/>
-        <v>5.6879999999999997</v>
+        <v>6.0330000000000004</v>
       </c>
       <c r="I65" s="23">
         <f t="shared" si="5"/>
-        <v>7.1227125941872984</v>
+        <v>4.0391304347826091</v>
       </c>
       <c r="J65" s="24"/>
     </row>
@@ -2903,31 +2903,31 @@
         <v>73</v>
       </c>
       <c r="B66" s="19">
-        <v>159.81</v>
+        <v>93.41</v>
       </c>
       <c r="C66" s="20">
-        <v>5989</v>
+        <v>4212</v>
       </c>
       <c r="D66" s="21">
-        <v>6061</v>
+        <v>6651</v>
       </c>
       <c r="E66" s="21">
-        <v>3243</v>
+        <v>5303</v>
       </c>
       <c r="F66" s="21">
-        <v>623</v>
+        <v>539</v>
       </c>
       <c r="G66" s="22">
         <f t="shared" si="3"/>
-        <v>6.0609999999999999</v>
+        <v>6.6509999999999998</v>
       </c>
       <c r="H66" s="22">
         <f t="shared" si="4"/>
-        <v>3.2429999999999999</v>
+        <v>5.3029999999999999</v>
       </c>
       <c r="I66" s="23">
         <f t="shared" si="5"/>
-        <v>9.728731942215088</v>
+        <v>12.339517625231911</v>
       </c>
       <c r="J66" s="24"/>
     </row>
@@ -2936,31 +2936,31 @@
         <v>74</v>
       </c>
       <c r="B67" s="19">
-        <v>226.37</v>
+        <v>30.12</v>
       </c>
       <c r="C67" s="20">
-        <v>7413</v>
+        <v>2592</v>
       </c>
       <c r="D67" s="21">
-        <v>6005</v>
+        <v>6617</v>
       </c>
       <c r="E67" s="21">
-        <v>3122</v>
+        <v>5688</v>
       </c>
       <c r="F67" s="21">
-        <v>554</v>
+        <v>929</v>
       </c>
       <c r="G67" s="22">
         <f t="shared" si="3"/>
-        <v>6.0049999999999999</v>
+        <v>6.617</v>
       </c>
       <c r="H67" s="22">
         <f t="shared" si="4"/>
-        <v>3.1219999999999999</v>
+        <v>5.6879999999999997</v>
       </c>
       <c r="I67" s="23">
         <f t="shared" si="5"/>
-        <v>10.839350180505415</v>
+        <v>7.1227125941872984</v>
       </c>
       <c r="J67" s="24"/>
     </row>
@@ -2969,227 +2969,229 @@
         <v>75</v>
       </c>
       <c r="B68" s="19">
-        <v>127.8</v>
+        <v>159.81</v>
       </c>
       <c r="C68" s="20">
-        <v>5228</v>
+        <v>5989</v>
       </c>
       <c r="D68" s="21">
-        <v>5303</v>
+        <v>6061</v>
       </c>
       <c r="E68" s="21">
-        <v>1483</v>
+        <v>3243</v>
       </c>
       <c r="F68" s="21">
-        <v>289</v>
+        <v>623</v>
       </c>
       <c r="G68" s="22">
         <f t="shared" si="3"/>
-        <v>5.3029999999999999</v>
+        <v>6.0609999999999999</v>
       </c>
       <c r="H68" s="22">
         <f t="shared" si="4"/>
-        <v>1.4830000000000001</v>
+        <v>3.2429999999999999</v>
       </c>
       <c r="I68" s="23">
         <f t="shared" si="5"/>
-        <v>18.349480968858131</v>
+        <v>9.728731942215088</v>
       </c>
       <c r="J68" s="24"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="5">
-        <v>36.46</v>
-      </c>
-      <c r="C69" s="6">
-        <v>2605</v>
-      </c>
-      <c r="D69" s="7">
-        <v>4420</v>
-      </c>
-      <c r="E69" s="7">
-        <v>4380</v>
-      </c>
-      <c r="F69" s="7">
-        <v>3603</v>
-      </c>
-      <c r="G69" s="8">
-        <f t="shared" si="3"/>
-        <v>4.42</v>
-      </c>
-      <c r="H69" s="8">
-        <f t="shared" si="4"/>
-        <v>4.38</v>
-      </c>
-      <c r="I69" s="9">
-        <f t="shared" si="5"/>
-        <v>1.2267554815431585</v>
-      </c>
-      <c r="J69" s="10"/>
+      <c r="B69" s="19">
+        <v>226.37</v>
+      </c>
+      <c r="C69" s="20">
+        <v>7413</v>
+      </c>
+      <c r="D69" s="21">
+        <v>6005</v>
+      </c>
+      <c r="E69" s="21">
+        <v>3122</v>
+      </c>
+      <c r="F69" s="21">
+        <v>554</v>
+      </c>
+      <c r="G69" s="22">
+        <f t="shared" si="3"/>
+        <v>6.0049999999999999</v>
+      </c>
+      <c r="H69" s="22">
+        <f t="shared" si="4"/>
+        <v>3.1219999999999999</v>
+      </c>
+      <c r="I69" s="23">
+        <f t="shared" si="5"/>
+        <v>10.839350180505415</v>
+      </c>
+      <c r="J69" s="24"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
         <v>77</v>
       </c>
       <c r="B70" s="19">
-        <v>110.29</v>
+        <v>127.8</v>
       </c>
       <c r="C70" s="20">
-        <v>5351</v>
+        <v>5228</v>
       </c>
       <c r="D70" s="21">
-        <v>4395</v>
+        <v>5303</v>
       </c>
       <c r="E70" s="21">
-        <v>616</v>
+        <v>1483</v>
       </c>
       <c r="F70" s="21">
-        <v>172</v>
+        <v>289</v>
       </c>
       <c r="G70" s="22">
         <f t="shared" si="3"/>
-        <v>4.3949999999999996</v>
+        <v>5.3029999999999999</v>
       </c>
       <c r="H70" s="22">
         <f t="shared" si="4"/>
-        <v>0.61599999999999999</v>
+        <v>1.4830000000000001</v>
       </c>
       <c r="I70" s="23">
         <f t="shared" si="5"/>
-        <v>25.552325581395348</v>
+        <v>18.349480968858131</v>
       </c>
       <c r="J70" s="24"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="18" t="s">
+      <c r="A71" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B71" s="19">
-        <v>29.65</v>
-      </c>
-      <c r="C71" s="20">
-        <v>2527</v>
-      </c>
-      <c r="D71" s="21">
-        <v>1536</v>
-      </c>
-      <c r="E71" s="21">
-        <v>266</v>
-      </c>
-      <c r="F71" s="21">
-        <v>250</v>
-      </c>
-      <c r="G71" s="22">
-        <f t="shared" si="3"/>
-        <v>1.536</v>
-      </c>
-      <c r="H71" s="22">
-        <f t="shared" si="4"/>
-        <v>0.26600000000000001</v>
-      </c>
-      <c r="I71" s="23">
-        <f t="shared" si="5"/>
-        <v>6.1440000000000001</v>
-      </c>
-      <c r="J71" s="24"/>
+      <c r="B71" s="5">
+        <v>36.46</v>
+      </c>
+      <c r="C71" s="6">
+        <v>2605</v>
+      </c>
+      <c r="D71" s="7">
+        <v>4420</v>
+      </c>
+      <c r="E71" s="7">
+        <v>4380</v>
+      </c>
+      <c r="F71" s="7">
+        <v>3603</v>
+      </c>
+      <c r="G71" s="8">
+        <f t="shared" si="3"/>
+        <v>4.42</v>
+      </c>
+      <c r="H71" s="8">
+        <f t="shared" si="4"/>
+        <v>4.38</v>
+      </c>
+      <c r="I71" s="9">
+        <f t="shared" si="5"/>
+        <v>1.2267554815431585</v>
+      </c>
+      <c r="J71" s="10"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="18" t="s">
         <v>79</v>
       </c>
       <c r="B72" s="19">
-        <v>33.869999999999997</v>
+        <v>110.29</v>
       </c>
       <c r="C72" s="20">
-        <v>2696</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E72" s="25" t="s">
-        <v>80</v>
+        <v>5351</v>
+      </c>
+      <c r="D72" s="21">
+        <v>4395</v>
+      </c>
+      <c r="E72" s="21">
+        <v>616</v>
       </c>
       <c r="F72" s="21">
-        <v>3966</v>
-      </c>
-      <c r="G72" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="H72" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="I72" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="J72" s="28" t="s">
-        <v>82</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G72" s="22">
+        <f t="shared" si="3"/>
+        <v>4.3949999999999996</v>
+      </c>
+      <c r="H72" s="22">
+        <f t="shared" si="4"/>
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="I72" s="23">
+        <f t="shared" si="5"/>
+        <v>25.552325581395348</v>
+      </c>
+      <c r="J72" s="24"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B73" s="19">
-        <v>39.65</v>
+        <v>29.65</v>
       </c>
       <c r="C73" s="20">
-        <v>2528</v>
-      </c>
-      <c r="D73" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E73" s="25" t="s">
-        <v>80</v>
+        <v>2527</v>
+      </c>
+      <c r="D73" s="21">
+        <v>1536</v>
+      </c>
+      <c r="E73" s="21">
+        <v>266</v>
       </c>
       <c r="F73" s="21">
-        <v>13714</v>
-      </c>
-      <c r="G73" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="H73" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="I73" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="J73" s="28" t="s">
-        <v>82</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G73" s="22">
+        <f t="shared" si="3"/>
+        <v>1.536</v>
+      </c>
+      <c r="H73" s="22">
+        <f t="shared" si="4"/>
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="I73" s="23">
+        <f t="shared" si="5"/>
+        <v>6.1440000000000001</v>
+      </c>
+      <c r="J73" s="24"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="19">
+        <v>39.65</v>
+      </c>
+      <c r="C74" s="20">
+        <v>2528</v>
+      </c>
+      <c r="D74" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F74" s="21">
+        <v>13714</v>
+      </c>
+      <c r="G74" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H74" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="I74" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="J74" s="28" t="s">
         <v>84</v>
-      </c>
-      <c r="B74" s="19">
-        <v>3.24</v>
-      </c>
-      <c r="C74" s="20">
-        <v>1056</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="F74" s="21">
-        <v>3969</v>
-      </c>
-      <c r="G74" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="H74" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="I74" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="J74" s="28" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
@@ -3210,7 +3212,7 @@
       </c>
       <c r="I76" s="33">
         <f>IFERROR(AVERAGE(I5:I74),"")</f>
-        <v>3.0564646910026116</v>
+        <v>3.0242352722010546</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B788502D-BC5B-4954-BDCD-B4033741965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBB5387-36FD-4F12-B285-30C505E504DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -246,6 +246,9 @@
     <t>T-05D</t>
   </si>
   <si>
+    <t>T-06C</t>
+  </si>
+  <si>
     <t>T-CON</t>
   </si>
   <si>
@@ -268,9 +271,6 @@
   </si>
   <si>
     <t>T-10B</t>
-  </si>
-  <si>
-    <t>T-06C</t>
   </si>
   <si>
     <t>T-01</t>
@@ -2804,10 +2804,10 @@
         <v>70</v>
       </c>
       <c r="B63" s="5">
-        <v>3.24</v>
+        <v>36.46</v>
       </c>
       <c r="C63" s="6">
-        <v>1056</v>
+        <v>2605</v>
       </c>
       <c r="D63" s="7">
         <v>7715</v>
@@ -2816,85 +2816,85 @@
         <v>7715</v>
       </c>
       <c r="F63" s="7">
+        <v>3603</v>
+      </c>
+      <c r="G63" s="8">
+        <f t="shared" si="3"/>
+        <v>7.7149999999999999</v>
+      </c>
+      <c r="H63" s="8">
+        <f t="shared" si="4"/>
+        <v>7.7149999999999999</v>
+      </c>
+      <c r="I63" s="9">
+        <f t="shared" si="5"/>
+        <v>2.1412711629197889</v>
+      </c>
+      <c r="J63" s="10"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="12">
+        <v>3.24</v>
+      </c>
+      <c r="C64" s="13">
+        <v>1056</v>
+      </c>
+      <c r="D64" s="14">
+        <v>7715</v>
+      </c>
+      <c r="E64" s="14">
+        <v>7715</v>
+      </c>
+      <c r="F64" s="14">
         <v>3969</v>
       </c>
-      <c r="G63" s="8">
+      <c r="G64" s="15">
         <f t="shared" si="3"/>
         <v>7.7149999999999999</v>
       </c>
-      <c r="H63" s="8">
+      <c r="H64" s="15">
         <f t="shared" si="4"/>
         <v>7.7149999999999999</v>
       </c>
-      <c r="I63" s="9">
+      <c r="I64" s="16">
         <f t="shared" si="5"/>
         <v>1.9438145628621819</v>
       </c>
-      <c r="J63" s="10"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="19">
-        <v>39.74</v>
-      </c>
-      <c r="C64" s="20">
-        <v>3355</v>
-      </c>
-      <c r="D64" s="21">
-        <v>7579</v>
-      </c>
-      <c r="E64" s="21">
-        <v>6617</v>
-      </c>
-      <c r="F64" s="21">
-        <v>1816</v>
-      </c>
-      <c r="G64" s="22">
-        <f t="shared" si="3"/>
-        <v>7.5789999999999997</v>
-      </c>
-      <c r="H64" s="22">
-        <f t="shared" si="4"/>
-        <v>6.617</v>
-      </c>
-      <c r="I64" s="23">
-        <f t="shared" si="5"/>
-        <v>4.1734581497797354</v>
-      </c>
-      <c r="J64" s="24"/>
+      <c r="J64" s="17"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
         <v>72</v>
       </c>
       <c r="B65" s="19">
-        <v>72.52</v>
+        <v>39.74</v>
       </c>
       <c r="C65" s="20">
-        <v>3558</v>
+        <v>3355</v>
       </c>
       <c r="D65" s="21">
-        <v>7432</v>
+        <v>7579</v>
       </c>
       <c r="E65" s="21">
-        <v>6033</v>
+        <v>6617</v>
       </c>
       <c r="F65" s="21">
-        <v>1840</v>
+        <v>1816</v>
       </c>
       <c r="G65" s="22">
         <f t="shared" si="3"/>
-        <v>7.4320000000000004</v>
+        <v>7.5789999999999997</v>
       </c>
       <c r="H65" s="22">
         <f t="shared" si="4"/>
-        <v>6.0330000000000004</v>
+        <v>6.617</v>
       </c>
       <c r="I65" s="23">
         <f t="shared" si="5"/>
-        <v>4.0391304347826091</v>
+        <v>4.1734581497797354</v>
       </c>
       <c r="J65" s="24"/>
     </row>
@@ -2903,31 +2903,31 @@
         <v>73</v>
       </c>
       <c r="B66" s="19">
-        <v>93.41</v>
+        <v>72.52</v>
       </c>
       <c r="C66" s="20">
-        <v>4212</v>
+        <v>3558</v>
       </c>
       <c r="D66" s="21">
-        <v>6651</v>
+        <v>7432</v>
       </c>
       <c r="E66" s="21">
-        <v>5303</v>
+        <v>6033</v>
       </c>
       <c r="F66" s="21">
-        <v>539</v>
+        <v>1840</v>
       </c>
       <c r="G66" s="22">
         <f t="shared" si="3"/>
-        <v>6.6509999999999998</v>
+        <v>7.4320000000000004</v>
       </c>
       <c r="H66" s="22">
         <f t="shared" si="4"/>
-        <v>5.3029999999999999</v>
+        <v>6.0330000000000004</v>
       </c>
       <c r="I66" s="23">
         <f t="shared" si="5"/>
-        <v>12.339517625231911</v>
+        <v>4.0391304347826091</v>
       </c>
       <c r="J66" s="24"/>
     </row>
@@ -2936,31 +2936,31 @@
         <v>74</v>
       </c>
       <c r="B67" s="19">
-        <v>30.12</v>
+        <v>93.41</v>
       </c>
       <c r="C67" s="20">
-        <v>2592</v>
+        <v>4212</v>
       </c>
       <c r="D67" s="21">
-        <v>6617</v>
+        <v>6651</v>
       </c>
       <c r="E67" s="21">
-        <v>5688</v>
+        <v>5303</v>
       </c>
       <c r="F67" s="21">
-        <v>929</v>
+        <v>539</v>
       </c>
       <c r="G67" s="22">
         <f t="shared" si="3"/>
-        <v>6.617</v>
+        <v>6.6509999999999998</v>
       </c>
       <c r="H67" s="22">
         <f t="shared" si="4"/>
-        <v>5.6879999999999997</v>
+        <v>5.3029999999999999</v>
       </c>
       <c r="I67" s="23">
         <f t="shared" si="5"/>
-        <v>7.1227125941872984</v>
+        <v>12.339517625231911</v>
       </c>
       <c r="J67" s="24"/>
     </row>
@@ -2969,31 +2969,31 @@
         <v>75</v>
       </c>
       <c r="B68" s="19">
-        <v>159.81</v>
+        <v>30.12</v>
       </c>
       <c r="C68" s="20">
-        <v>5989</v>
+        <v>2592</v>
       </c>
       <c r="D68" s="21">
-        <v>6061</v>
+        <v>6617</v>
       </c>
       <c r="E68" s="21">
-        <v>3243</v>
+        <v>5688</v>
       </c>
       <c r="F68" s="21">
-        <v>623</v>
+        <v>929</v>
       </c>
       <c r="G68" s="22">
         <f t="shared" si="3"/>
-        <v>6.0609999999999999</v>
+        <v>6.617</v>
       </c>
       <c r="H68" s="22">
         <f t="shared" si="4"/>
-        <v>3.2429999999999999</v>
+        <v>5.6879999999999997</v>
       </c>
       <c r="I68" s="23">
         <f t="shared" si="5"/>
-        <v>9.728731942215088</v>
+        <v>7.1227125941872984</v>
       </c>
       <c r="J68" s="24"/>
     </row>
@@ -3002,31 +3002,31 @@
         <v>76</v>
       </c>
       <c r="B69" s="19">
-        <v>226.37</v>
+        <v>159.81</v>
       </c>
       <c r="C69" s="20">
-        <v>7413</v>
+        <v>5989</v>
       </c>
       <c r="D69" s="21">
-        <v>6005</v>
+        <v>6061</v>
       </c>
       <c r="E69" s="21">
-        <v>3122</v>
+        <v>3243</v>
       </c>
       <c r="F69" s="21">
-        <v>554</v>
+        <v>623</v>
       </c>
       <c r="G69" s="22">
         <f t="shared" si="3"/>
-        <v>6.0049999999999999</v>
+        <v>6.0609999999999999</v>
       </c>
       <c r="H69" s="22">
         <f t="shared" si="4"/>
-        <v>3.1219999999999999</v>
+        <v>3.2429999999999999</v>
       </c>
       <c r="I69" s="23">
         <f t="shared" si="5"/>
-        <v>10.839350180505415</v>
+        <v>9.728731942215088</v>
       </c>
       <c r="J69" s="24"/>
     </row>
@@ -3035,66 +3035,66 @@
         <v>77</v>
       </c>
       <c r="B70" s="19">
+        <v>226.37</v>
+      </c>
+      <c r="C70" s="20">
+        <v>7413</v>
+      </c>
+      <c r="D70" s="21">
+        <v>6005</v>
+      </c>
+      <c r="E70" s="21">
+        <v>3122</v>
+      </c>
+      <c r="F70" s="21">
+        <v>554</v>
+      </c>
+      <c r="G70" s="22">
+        <f t="shared" si="3"/>
+        <v>6.0049999999999999</v>
+      </c>
+      <c r="H70" s="22">
+        <f t="shared" si="4"/>
+        <v>3.1219999999999999</v>
+      </c>
+      <c r="I70" s="23">
+        <f t="shared" si="5"/>
+        <v>10.839350180505415</v>
+      </c>
+      <c r="J70" s="24"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="19">
         <v>127.8</v>
       </c>
-      <c r="C70" s="20">
+      <c r="C71" s="20">
         <v>5228</v>
       </c>
-      <c r="D70" s="21">
+      <c r="D71" s="21">
         <v>5303</v>
       </c>
-      <c r="E70" s="21">
+      <c r="E71" s="21">
         <v>1483</v>
       </c>
-      <c r="F70" s="21">
+      <c r="F71" s="21">
         <v>289</v>
       </c>
-      <c r="G70" s="22">
+      <c r="G71" s="22">
         <f t="shared" si="3"/>
         <v>5.3029999999999999</v>
       </c>
-      <c r="H70" s="22">
+      <c r="H71" s="22">
         <f t="shared" si="4"/>
         <v>1.4830000000000001</v>
       </c>
-      <c r="I70" s="23">
+      <c r="I71" s="23">
         <f t="shared" si="5"/>
         <v>18.349480968858131</v>
       </c>
-      <c r="J70" s="24"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="5">
-        <v>36.46</v>
-      </c>
-      <c r="C71" s="6">
-        <v>2605</v>
-      </c>
-      <c r="D71" s="7">
-        <v>4420</v>
-      </c>
-      <c r="E71" s="7">
-        <v>4380</v>
-      </c>
-      <c r="F71" s="7">
-        <v>3603</v>
-      </c>
-      <c r="G71" s="8">
-        <f t="shared" si="3"/>
-        <v>4.42</v>
-      </c>
-      <c r="H71" s="8">
-        <f t="shared" si="4"/>
-        <v>4.38</v>
-      </c>
-      <c r="I71" s="9">
-        <f t="shared" si="5"/>
-        <v>1.2267554815431585</v>
-      </c>
-      <c r="J71" s="10"/>
+      <c r="J71" s="24"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="18" t="s">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="I76" s="33">
         <f>IFERROR(AVERAGE(I5:I74),"")</f>
-        <v>3.0242352722010546</v>
+        <v>3.0374891226557881</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBB5387-36FD-4F12-B285-30C505E504DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6965E9E9-AEF0-4198-9EF8-1CA1F5F78CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>FAZENDA TUCANO — distância dos talhões até a sede</t>
   </si>
@@ -279,18 +279,6 @@
     <t>T-10</t>
   </si>
   <si>
-    <t>T-40C</t>
-  </si>
-  <si>
-    <t>sem acesso</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>sem estrada até este talhão</t>
-  </si>
-  <si>
     <t>TOTAL / MÁXIMO</t>
   </si>
   <si>
@@ -309,7 +297,7 @@
     <t>Talhões</t>
   </si>
   <si>
-    <t>70 polígonos da pasta FAZENDA TUCANO.</t>
+    <t>69 polígonos da pasta FAZENDA TUCANO.</t>
   </si>
   <si>
     <t>Malha de estradas</t>
@@ -367,7 +355,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -410,17 +398,6 @@
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -479,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -507,21 +484,13 @@
     <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -830,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3162,62 +3131,30 @@
       </c>
       <c r="J73" s="24"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="18" t="s">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="B74" s="19">
-        <v>39.65</v>
-      </c>
-      <c r="C74" s="20">
-        <v>2528</v>
-      </c>
-      <c r="D74" s="25" t="s">
+      <c r="B75" s="26">
+        <f>SUM(B5:B73)</f>
+        <v>5718.9599999999991</v>
+      </c>
+      <c r="D75" s="27">
+        <f>MAX(D5:D73)</f>
+        <v>25675</v>
+      </c>
+      <c r="G75" s="28">
+        <f>IFERROR(MAX(G5:G73),"")</f>
+        <v>25.675000000000001</v>
+      </c>
+      <c r="I75" s="29">
+        <f>IFERROR(AVERAGE(I5:I73),"")</f>
+        <v>3.0374891226557881</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="30" t="s">
         <v>82</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="F74" s="21">
-        <v>13714</v>
-      </c>
-      <c r="G74" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="H74" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="I74" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="J74" s="28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="B76" s="30">
-        <f>SUM(B5:B74)</f>
-        <v>5758.6099999999988</v>
-      </c>
-      <c r="D76" s="31">
-        <f>MAX(D5:D74)</f>
-        <v>25675</v>
-      </c>
-      <c r="G76" s="32">
-        <f>IFERROR(MAX(G5:G74),"")</f>
-        <v>25.675000000000001</v>
-      </c>
-      <c r="I76" s="33">
-        <f>IFERROR(AVERAGE(I5:I74),"")</f>
-        <v>3.0374891226557881</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="34" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3235,88 +3172,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="33" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B5" s="33" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B6" s="33" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B7" s="33" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B8" s="33" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B9" s="33" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B10" s="33" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B11" s="33" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36" t="s">
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B12" s="33" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6965E9E9-AEF0-4198-9EF8-1CA1F5F78CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A2588C-9AB0-4FBB-B6B0-D3C81D33555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A2588C-9AB0-4FBB-B6B0-D3C81D33555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92708C46-3F8D-4523-A357-0D50962CC199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92708C46-3F8D-4523-A357-0D50962CC199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD0CE03-2DF9-4ABA-8269-8806F36E8D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -367,49 +367,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD0CE03-2DF9-4ABA-8269-8806F36E8D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8780E3E1-9DCF-4AFB-9BC8-7D331BCABE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -367,58 +367,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8780E3E1-9DCF-4AFB-9BC8-7D331BCABE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2D8B5F-0883-480F-8EB9-7ED584995E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -367,49 +367,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2D8B5F-0883-480F-8EB9-7ED584995E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A321713-83B0-4B64-8206-CDFDA888B551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_TUCANO_distancias.xlsx
+++ b/FAZENDA_TUCANO_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A321713-83B0-4B64-8206-CDFDA888B551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D7BF41-8841-49F3-9EB8-6253A08C9418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -367,58 +367,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
